--- a/data/BD_Requerimientos_POs.xlsx
+++ b/data/BD_Requerimientos_POs.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="14">
   <si>
     <t>PO</t>
   </si>
@@ -29,6 +29,33 @@
   </si>
   <si>
     <t>Parcialidad</t>
+  </si>
+  <si>
+    <t>26083177</t>
+  </si>
+  <si>
+    <t>12-D-6013-01</t>
+  </si>
+  <si>
+    <t>PP14873-01</t>
+  </si>
+  <si>
+    <t>PP14873-02</t>
+  </si>
+  <si>
+    <t>96-6183-01</t>
+  </si>
+  <si>
+    <t>P20325-24</t>
+  </si>
+  <si>
+    <t>P20325-25</t>
+  </si>
+  <si>
+    <t>2026-08-30</t>
+  </si>
+  <si>
+    <t>P1</t>
   </si>
 </sst>
 </file>
@@ -360,7 +387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -380,6 +407,108 @@
         <v>4</v>
       </c>
     </row>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2">
+        <v>128</v>
+      </c>
+      <c r="E2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3">
+        <v>32</v>
+      </c>
+      <c r="E3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4">
+        <v>40</v>
+      </c>
+      <c r="E4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5">
+        <v>40</v>
+      </c>
+      <c r="E5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6">
+        <v>64</v>
+      </c>
+      <c r="E6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7">
+        <v>64</v>
+      </c>
+      <c r="E7" t="s">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/BD_Requerimientos_POs.xlsx
+++ b/data/BD_Requerimientos_POs.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="19">
   <si>
     <t>PO</t>
   </si>
@@ -34,6 +34,9 @@
     <t>26083177</t>
   </si>
   <si>
+    <t>26083235</t>
+  </si>
+  <si>
     <t>12-D-6013-01</t>
   </si>
   <si>
@@ -52,7 +55,19 @@
     <t>P20325-25</t>
   </si>
   <si>
+    <t>12-6355-03</t>
+  </si>
+  <si>
+    <t>12-6355-02</t>
+  </si>
+  <si>
+    <t>PP22114-05</t>
+  </si>
+  <si>
     <t>2026-08-30</t>
+  </si>
+  <si>
+    <t>2026-08-28</t>
   </si>
   <si>
     <t>P1</t>
@@ -387,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -412,16 +427,16 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D2">
         <v>128</v>
       </c>
       <c r="E2" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -429,16 +444,16 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D3">
         <v>32</v>
       </c>
       <c r="E3" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -446,16 +461,16 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D4">
         <v>40</v>
       </c>
       <c r="E4" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -463,16 +478,16 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C5" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D5">
         <v>40</v>
       </c>
       <c r="E5" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -480,16 +495,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D6">
         <v>64</v>
       </c>
       <c r="E6" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -497,16 +512,67 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C7" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D7">
         <v>64</v>
       </c>
       <c r="E7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
         <v>13</v>
+      </c>
+      <c r="C8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8">
+        <v>32</v>
+      </c>
+      <c r="E8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9">
+        <v>40</v>
+      </c>
+      <c r="E9" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10">
+        <v>40</v>
+      </c>
+      <c r="E10" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/data/BD_Requerimientos_POs.xlsx
+++ b/data/BD_Requerimientos_POs.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="24">
   <si>
     <t>PO</t>
   </si>
@@ -37,6 +37,9 @@
     <t>26083235</t>
   </si>
   <si>
+    <t>26083261</t>
+  </si>
+  <si>
     <t>12-D-6013-01</t>
   </si>
   <si>
@@ -64,10 +67,22 @@
     <t>PP22114-05</t>
   </si>
   <si>
+    <t>12-D-6091-08</t>
+  </si>
+  <si>
+    <t>PP7517-10</t>
+  </si>
+  <si>
+    <t>PP7517-01</t>
+  </si>
+  <si>
     <t>2026-08-30</t>
   </si>
   <si>
     <t>2026-08-28</t>
+  </si>
+  <si>
+    <t>2026-08-31</t>
   </si>
   <si>
     <t>P1</t>
@@ -402,7 +417,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -427,16 +442,16 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D2">
         <v>128</v>
       </c>
       <c r="E2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -444,16 +459,16 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D3">
         <v>32</v>
       </c>
       <c r="E3" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -461,16 +476,16 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D4">
         <v>40</v>
       </c>
       <c r="E4" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -478,16 +493,16 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D5">
         <v>40</v>
       </c>
       <c r="E5" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -495,16 +510,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D6">
         <v>64</v>
       </c>
       <c r="E6" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -512,16 +527,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D7">
         <v>64</v>
       </c>
       <c r="E7" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -529,16 +544,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D8">
         <v>32</v>
       </c>
       <c r="E8" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -546,16 +561,16 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C9" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D9">
         <v>40</v>
       </c>
       <c r="E9" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -563,16 +578,67 @@
         <v>6</v>
       </c>
       <c r="B10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C10" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D10">
         <v>40</v>
       </c>
       <c r="E10" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11">
+        <v>20</v>
+      </c>
+      <c r="E11" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12" t="s">
         <v>18</v>
+      </c>
+      <c r="C12" t="s">
+        <v>22</v>
+      </c>
+      <c r="D12">
+        <v>32</v>
+      </c>
+      <c r="E12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" t="s">
+        <v>22</v>
+      </c>
+      <c r="D13">
+        <v>64</v>
+      </c>
+      <c r="E13" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/data/BD_Requerimientos_POs.xlsx
+++ b/data/BD_Requerimientos_POs.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="38">
   <si>
     <t>PO</t>
   </si>
@@ -31,6 +31,18 @@
     <t>Parcialidad</t>
   </si>
   <si>
+    <t>26083186</t>
+  </si>
+  <si>
+    <t>26083189</t>
+  </si>
+  <si>
+    <t>26083190</t>
+  </si>
+  <si>
+    <t>26083191</t>
+  </si>
+  <si>
     <t>26083177</t>
   </si>
   <si>
@@ -40,6 +52,21 @@
     <t>26083261</t>
   </si>
   <si>
+    <t>26083358</t>
+  </si>
+  <si>
+    <t>PP19380-03</t>
+  </si>
+  <si>
+    <t>11-7761-02</t>
+  </si>
+  <si>
+    <t>11-A-6014-01</t>
+  </si>
+  <si>
+    <t>11-A-9836-01</t>
+  </si>
+  <si>
     <t>12-D-6013-01</t>
   </si>
   <si>
@@ -49,15 +76,15 @@
     <t>PP14873-02</t>
   </si>
   <si>
+    <t>P20325-25</t>
+  </si>
+  <si>
+    <t>P20325-24</t>
+  </si>
+  <si>
     <t>96-6183-01</t>
   </si>
   <si>
-    <t>P20325-24</t>
-  </si>
-  <si>
-    <t>P20325-25</t>
-  </si>
-  <si>
     <t>12-6355-03</t>
   </si>
   <si>
@@ -76,13 +103,28 @@
     <t>PP7517-01</t>
   </si>
   <si>
-    <t>2026-08-30</t>
+    <t>P9711-081 TRTO1</t>
+  </si>
+  <si>
+    <t>PP10218-13-TBC3</t>
+  </si>
+  <si>
+    <t>PP21139-081 TRTO</t>
+  </si>
+  <si>
+    <t>2026-08-25</t>
+  </si>
+  <si>
+    <t>2026-09-07</t>
   </si>
   <si>
     <t>2026-08-28</t>
   </si>
   <si>
     <t>2026-08-31</t>
+  </si>
+  <si>
+    <t>2026-09-08</t>
   </si>
   <si>
     <t>P1</t>
@@ -417,7 +459,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -442,203 +484,339 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="D2">
-        <v>128</v>
+        <v>32</v>
       </c>
       <c r="E2" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="D3">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="D4">
         <v>40</v>
       </c>
       <c r="E4" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="D5">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="D6">
-        <v>64</v>
+        <v>16</v>
       </c>
       <c r="E6" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="D7">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="E7" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="D8">
         <v>32</v>
       </c>
       <c r="E8" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C9" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="D9">
         <v>40</v>
       </c>
       <c r="E9" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C10" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="D10">
-        <v>40</v>
+        <v>64</v>
       </c>
       <c r="E10" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C11" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="D11">
-        <v>20</v>
+        <v>64</v>
       </c>
       <c r="E11" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C12" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="D12">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="E12" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C13" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="D13">
+        <v>32</v>
+      </c>
+      <c r="E13" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B14" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" t="s">
+        <v>34</v>
+      </c>
+      <c r="D14">
+        <v>40</v>
+      </c>
+      <c r="E14" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" t="s">
+        <v>10</v>
+      </c>
+      <c r="B15" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D15">
+        <v>40</v>
+      </c>
+      <c r="E15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" t="s">
+        <v>11</v>
+      </c>
+      <c r="B16" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16" t="s">
+        <v>35</v>
+      </c>
+      <c r="D16">
+        <v>20</v>
+      </c>
+      <c r="E16" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" t="s">
+        <v>11</v>
+      </c>
+      <c r="B17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C17" t="s">
+        <v>35</v>
+      </c>
+      <c r="D17">
+        <v>32</v>
+      </c>
+      <c r="E17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" t="s">
+        <v>11</v>
+      </c>
+      <c r="B18" t="s">
+        <v>28</v>
+      </c>
+      <c r="C18" t="s">
+        <v>35</v>
+      </c>
+      <c r="D18">
         <v>64</v>
       </c>
-      <c r="E13" t="s">
-        <v>23</v>
+      <c r="E18" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" t="s">
+        <v>12</v>
+      </c>
+      <c r="B19" t="s">
+        <v>29</v>
+      </c>
+      <c r="C19" t="s">
+        <v>36</v>
+      </c>
+      <c r="D19">
+        <v>1</v>
+      </c>
+      <c r="E19" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" t="s">
+        <v>12</v>
+      </c>
+      <c r="B20" t="s">
+        <v>30</v>
+      </c>
+      <c r="C20" t="s">
+        <v>36</v>
+      </c>
+      <c r="D20">
+        <v>1</v>
+      </c>
+      <c r="E20" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" t="s">
+        <v>12</v>
+      </c>
+      <c r="B21" t="s">
+        <v>31</v>
+      </c>
+      <c r="C21" t="s">
+        <v>36</v>
+      </c>
+      <c r="D21">
+        <v>12</v>
+      </c>
+      <c r="E21" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/data/BD_Requerimientos_POs.xlsx
+++ b/data/BD_Requerimientos_POs.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="73">
   <si>
     <t>PO</t>
   </si>
@@ -55,6 +55,9 @@
     <t>26083358</t>
   </si>
   <si>
+    <t>26083425</t>
+  </si>
+  <si>
     <t>PP19380-03</t>
   </si>
   <si>
@@ -110,6 +113,108 @@
   </si>
   <si>
     <t>PP21139-081 TRTO</t>
+  </si>
+  <si>
+    <t>11-D-6165-01</t>
+  </si>
+  <si>
+    <t>11-A-6037-01</t>
+  </si>
+  <si>
+    <t>12-6267-01</t>
+  </si>
+  <si>
+    <t>12-6265-01</t>
+  </si>
+  <si>
+    <t>PP14112-19</t>
+  </si>
+  <si>
+    <t>P17311-17</t>
+  </si>
+  <si>
+    <t>11-A-6030-01</t>
+  </si>
+  <si>
+    <t>PP20204-06</t>
+  </si>
+  <si>
+    <t>PP20203-06</t>
+  </si>
+  <si>
+    <t>P20153S-04</t>
+  </si>
+  <si>
+    <t>P20321S-05</t>
+  </si>
+  <si>
+    <t>P20321S-06</t>
+  </si>
+  <si>
+    <t>12-6383-01</t>
+  </si>
+  <si>
+    <t>12-D-6234-08</t>
+  </si>
+  <si>
+    <t>12-D-6234-06</t>
+  </si>
+  <si>
+    <t>12-D-6234-10</t>
+  </si>
+  <si>
+    <t>13-D-6195-01</t>
+  </si>
+  <si>
+    <t>13-D-6196-01</t>
+  </si>
+  <si>
+    <t>PP20204-12</t>
+  </si>
+  <si>
+    <t>PP20204-13</t>
+  </si>
+  <si>
+    <t>PP20203-12</t>
+  </si>
+  <si>
+    <t>PP20203-13</t>
+  </si>
+  <si>
+    <t>PP13949-04</t>
+  </si>
+  <si>
+    <t>PP13949-08</t>
+  </si>
+  <si>
+    <t>PP13949-09</t>
+  </si>
+  <si>
+    <t>PP13949-10</t>
+  </si>
+  <si>
+    <t>96-6183-02</t>
+  </si>
+  <si>
+    <t>P20321-15-11</t>
+  </si>
+  <si>
+    <t>P20321-15-12</t>
+  </si>
+  <si>
+    <t>P20512-06</t>
+  </si>
+  <si>
+    <t>P20512-07</t>
+  </si>
+  <si>
+    <t>P20512-08</t>
+  </si>
+  <si>
+    <t>P20512-09</t>
+  </si>
+  <si>
+    <t>P20512-18</t>
   </si>
   <si>
     <t>2026-08-25</t>
@@ -459,7 +564,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E56"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -484,16 +589,16 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>32</v>
+        <v>67</v>
       </c>
       <c r="D2">
         <v>32</v>
       </c>
       <c r="E2" t="s">
-        <v>37</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -501,16 +606,16 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>32</v>
+        <v>67</v>
       </c>
       <c r="D3">
         <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>37</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -518,16 +623,16 @@
         <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>32</v>
+        <v>67</v>
       </c>
       <c r="D4">
         <v>40</v>
       </c>
       <c r="E4" t="s">
-        <v>37</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -535,16 +640,16 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>32</v>
+        <v>67</v>
       </c>
       <c r="D5">
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>37</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -552,16 +657,16 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>33</v>
+        <v>68</v>
       </c>
       <c r="D6">
         <v>16</v>
       </c>
       <c r="E6" t="s">
-        <v>37</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -569,16 +674,16 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>33</v>
+        <v>68</v>
       </c>
       <c r="D7">
         <v>128</v>
       </c>
       <c r="E7" t="s">
-        <v>37</v>
+        <v>72</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -586,16 +691,16 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>33</v>
+        <v>68</v>
       </c>
       <c r="D8">
         <v>32</v>
       </c>
       <c r="E8" t="s">
-        <v>37</v>
+        <v>72</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -603,16 +708,16 @@
         <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C9" t="s">
-        <v>33</v>
+        <v>68</v>
       </c>
       <c r="D9">
         <v>40</v>
       </c>
       <c r="E9" t="s">
-        <v>37</v>
+        <v>72</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -620,16 +725,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C10" t="s">
-        <v>33</v>
+        <v>68</v>
       </c>
       <c r="D10">
         <v>64</v>
       </c>
       <c r="E10" t="s">
-        <v>37</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -637,16 +742,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C11" t="s">
-        <v>33</v>
+        <v>68</v>
       </c>
       <c r="D11">
         <v>64</v>
       </c>
       <c r="E11" t="s">
-        <v>37</v>
+        <v>72</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -654,16 +759,16 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C12" t="s">
-        <v>33</v>
+        <v>68</v>
       </c>
       <c r="D12">
         <v>40</v>
       </c>
       <c r="E12" t="s">
-        <v>37</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -671,16 +776,16 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C13" t="s">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="D13">
         <v>32</v>
       </c>
       <c r="E13" t="s">
-        <v>37</v>
+        <v>72</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -688,16 +793,16 @@
         <v>10</v>
       </c>
       <c r="B14" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C14" t="s">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="D14">
         <v>40</v>
       </c>
       <c r="E14" t="s">
-        <v>37</v>
+        <v>72</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -705,16 +810,16 @@
         <v>10</v>
       </c>
       <c r="B15" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C15" t="s">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="D15">
         <v>40</v>
       </c>
       <c r="E15" t="s">
-        <v>37</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -722,16 +827,16 @@
         <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C16" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="D16">
         <v>20</v>
       </c>
       <c r="E16" t="s">
-        <v>37</v>
+        <v>72</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -739,16 +844,16 @@
         <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C17" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="D17">
         <v>32</v>
       </c>
       <c r="E17" t="s">
-        <v>37</v>
+        <v>72</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -756,16 +861,16 @@
         <v>11</v>
       </c>
       <c r="B18" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C18" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="D18">
         <v>64</v>
       </c>
       <c r="E18" t="s">
-        <v>37</v>
+        <v>72</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -773,16 +878,16 @@
         <v>12</v>
       </c>
       <c r="B19" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C19" t="s">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="D19">
         <v>1</v>
       </c>
       <c r="E19" t="s">
-        <v>37</v>
+        <v>72</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -790,16 +895,16 @@
         <v>12</v>
       </c>
       <c r="B20" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C20" t="s">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="D20">
         <v>1</v>
       </c>
       <c r="E20" t="s">
-        <v>37</v>
+        <v>72</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -807,16 +912,611 @@
         <v>12</v>
       </c>
       <c r="B21" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C21" t="s">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="D21">
         <v>12</v>
       </c>
       <c r="E21" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" t="s">
+        <v>13</v>
+      </c>
+      <c r="B22" t="s">
+        <v>33</v>
+      </c>
+      <c r="C22" t="s">
+        <v>70</v>
+      </c>
+      <c r="D22">
+        <v>320</v>
+      </c>
+      <c r="E22" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" t="s">
+        <v>13</v>
+      </c>
+      <c r="B23" t="s">
+        <v>34</v>
+      </c>
+      <c r="C23" t="s">
+        <v>70</v>
+      </c>
+      <c r="D23">
+        <v>192</v>
+      </c>
+      <c r="E23" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" t="s">
+        <v>13</v>
+      </c>
+      <c r="B24" t="s">
+        <v>35</v>
+      </c>
+      <c r="C24" t="s">
+        <v>70</v>
+      </c>
+      <c r="D24">
+        <v>224</v>
+      </c>
+      <c r="E24" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" t="s">
+        <v>13</v>
+      </c>
+      <c r="B25" t="s">
+        <v>36</v>
+      </c>
+      <c r="C25" t="s">
+        <v>70</v>
+      </c>
+      <c r="D25">
+        <v>224</v>
+      </c>
+      <c r="E25" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" t="s">
+        <v>13</v>
+      </c>
+      <c r="B26" t="s">
         <v>37</v>
+      </c>
+      <c r="C26" t="s">
+        <v>70</v>
+      </c>
+      <c r="D26">
+        <v>160</v>
+      </c>
+      <c r="E26" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" t="s">
+        <v>13</v>
+      </c>
+      <c r="B27" t="s">
+        <v>38</v>
+      </c>
+      <c r="C27" t="s">
+        <v>70</v>
+      </c>
+      <c r="D27">
+        <v>160</v>
+      </c>
+      <c r="E27" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" t="s">
+        <v>13</v>
+      </c>
+      <c r="B28" t="s">
+        <v>39</v>
+      </c>
+      <c r="C28" t="s">
+        <v>70</v>
+      </c>
+      <c r="D28">
+        <v>160</v>
+      </c>
+      <c r="E28" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" t="s">
+        <v>13</v>
+      </c>
+      <c r="B29" t="s">
+        <v>40</v>
+      </c>
+      <c r="C29" t="s">
+        <v>70</v>
+      </c>
+      <c r="D29">
+        <v>80</v>
+      </c>
+      <c r="E29" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" t="s">
+        <v>13</v>
+      </c>
+      <c r="B30" t="s">
+        <v>41</v>
+      </c>
+      <c r="C30" t="s">
+        <v>70</v>
+      </c>
+      <c r="D30">
+        <v>80</v>
+      </c>
+      <c r="E30" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" t="s">
+        <v>13</v>
+      </c>
+      <c r="B31" t="s">
+        <v>42</v>
+      </c>
+      <c r="C31" t="s">
+        <v>70</v>
+      </c>
+      <c r="D31">
+        <v>120</v>
+      </c>
+      <c r="E31" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" t="s">
+        <v>13</v>
+      </c>
+      <c r="B32" t="s">
+        <v>43</v>
+      </c>
+      <c r="C32" t="s">
+        <v>70</v>
+      </c>
+      <c r="D32">
+        <v>120</v>
+      </c>
+      <c r="E32" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" t="s">
+        <v>13</v>
+      </c>
+      <c r="B33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C33" t="s">
+        <v>70</v>
+      </c>
+      <c r="D33">
+        <v>80</v>
+      </c>
+      <c r="E33" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" t="s">
+        <v>13</v>
+      </c>
+      <c r="B34" t="s">
+        <v>45</v>
+      </c>
+      <c r="C34" t="s">
+        <v>70</v>
+      </c>
+      <c r="D34">
+        <v>80</v>
+      </c>
+      <c r="E34" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B35" t="s">
+        <v>46</v>
+      </c>
+      <c r="C35" t="s">
+        <v>70</v>
+      </c>
+      <c r="D35">
+        <v>160</v>
+      </c>
+      <c r="E35" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" t="s">
+        <v>13</v>
+      </c>
+      <c r="B36" t="s">
+        <v>47</v>
+      </c>
+      <c r="C36" t="s">
+        <v>70</v>
+      </c>
+      <c r="D36">
+        <v>120</v>
+      </c>
+      <c r="E36" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" t="s">
+        <v>13</v>
+      </c>
+      <c r="B37" t="s">
+        <v>48</v>
+      </c>
+      <c r="C37" t="s">
+        <v>70</v>
+      </c>
+      <c r="D37">
+        <v>240</v>
+      </c>
+      <c r="E37" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" t="s">
+        <v>13</v>
+      </c>
+      <c r="B38" t="s">
+        <v>49</v>
+      </c>
+      <c r="C38" t="s">
+        <v>70</v>
+      </c>
+      <c r="D38">
+        <v>120</v>
+      </c>
+      <c r="E38" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" t="s">
+        <v>13</v>
+      </c>
+      <c r="B39" t="s">
+        <v>50</v>
+      </c>
+      <c r="C39" t="s">
+        <v>70</v>
+      </c>
+      <c r="D39">
+        <v>120</v>
+      </c>
+      <c r="E39" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" t="s">
+        <v>13</v>
+      </c>
+      <c r="B40" t="s">
+        <v>51</v>
+      </c>
+      <c r="C40" t="s">
+        <v>70</v>
+      </c>
+      <c r="D40">
+        <v>160</v>
+      </c>
+      <c r="E40" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" t="s">
+        <v>13</v>
+      </c>
+      <c r="B41" t="s">
+        <v>52</v>
+      </c>
+      <c r="C41" t="s">
+        <v>70</v>
+      </c>
+      <c r="D41">
+        <v>120</v>
+      </c>
+      <c r="E41" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" t="s">
+        <v>13</v>
+      </c>
+      <c r="B42" t="s">
+        <v>53</v>
+      </c>
+      <c r="C42" t="s">
+        <v>70</v>
+      </c>
+      <c r="D42">
+        <v>160</v>
+      </c>
+      <c r="E42" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" t="s">
+        <v>13</v>
+      </c>
+      <c r="B43" t="s">
+        <v>54</v>
+      </c>
+      <c r="C43" t="s">
+        <v>70</v>
+      </c>
+      <c r="D43">
+        <v>120</v>
+      </c>
+      <c r="E43" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" t="s">
+        <v>13</v>
+      </c>
+      <c r="B44" t="s">
+        <v>55</v>
+      </c>
+      <c r="C44" t="s">
+        <v>70</v>
+      </c>
+      <c r="D44">
+        <v>80</v>
+      </c>
+      <c r="E44" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" t="s">
+        <v>13</v>
+      </c>
+      <c r="B45" t="s">
+        <v>56</v>
+      </c>
+      <c r="C45" t="s">
+        <v>70</v>
+      </c>
+      <c r="D45">
+        <v>80</v>
+      </c>
+      <c r="E45" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" t="s">
+        <v>13</v>
+      </c>
+      <c r="B46" t="s">
+        <v>57</v>
+      </c>
+      <c r="C46" t="s">
+        <v>70</v>
+      </c>
+      <c r="D46">
+        <v>80</v>
+      </c>
+      <c r="E46" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" t="s">
+        <v>13</v>
+      </c>
+      <c r="B47" t="s">
+        <v>58</v>
+      </c>
+      <c r="C47" t="s">
+        <v>70</v>
+      </c>
+      <c r="D47">
+        <v>160</v>
+      </c>
+      <c r="E47" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" t="s">
+        <v>13</v>
+      </c>
+      <c r="B48" t="s">
+        <v>23</v>
+      </c>
+      <c r="C48" t="s">
+        <v>70</v>
+      </c>
+      <c r="D48">
+        <v>80</v>
+      </c>
+      <c r="E48" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" t="s">
+        <v>13</v>
+      </c>
+      <c r="B49" t="s">
+        <v>59</v>
+      </c>
+      <c r="C49" t="s">
+        <v>70</v>
+      </c>
+      <c r="D49">
+        <v>80</v>
+      </c>
+      <c r="E49" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" t="s">
+        <v>13</v>
+      </c>
+      <c r="B50" t="s">
+        <v>60</v>
+      </c>
+      <c r="C50" t="s">
+        <v>70</v>
+      </c>
+      <c r="D50">
+        <v>80</v>
+      </c>
+      <c r="E50" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" t="s">
+        <v>13</v>
+      </c>
+      <c r="B51" t="s">
+        <v>61</v>
+      </c>
+      <c r="C51" t="s">
+        <v>70</v>
+      </c>
+      <c r="D51">
+        <v>80</v>
+      </c>
+      <c r="E51" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" t="s">
+        <v>13</v>
+      </c>
+      <c r="B52" t="s">
+        <v>62</v>
+      </c>
+      <c r="C52" t="s">
+        <v>70</v>
+      </c>
+      <c r="D52">
+        <v>160</v>
+      </c>
+      <c r="E52" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" t="s">
+        <v>13</v>
+      </c>
+      <c r="B53" t="s">
+        <v>63</v>
+      </c>
+      <c r="C53" t="s">
+        <v>70</v>
+      </c>
+      <c r="D53">
+        <v>160</v>
+      </c>
+      <c r="E53" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" t="s">
+        <v>13</v>
+      </c>
+      <c r="B54" t="s">
+        <v>64</v>
+      </c>
+      <c r="C54" t="s">
+        <v>70</v>
+      </c>
+      <c r="D54">
+        <v>80</v>
+      </c>
+      <c r="E54" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" t="s">
+        <v>13</v>
+      </c>
+      <c r="B55" t="s">
+        <v>65</v>
+      </c>
+      <c r="C55" t="s">
+        <v>70</v>
+      </c>
+      <c r="D55">
+        <v>160</v>
+      </c>
+      <c r="E55" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" t="s">
+        <v>13</v>
+      </c>
+      <c r="B56" t="s">
+        <v>66</v>
+      </c>
+      <c r="C56" t="s">
+        <v>70</v>
+      </c>
+      <c r="D56">
+        <v>120</v>
+      </c>
+      <c r="E56" t="s">
+        <v>72</v>
       </c>
     </row>
   </sheetData>

--- a/data/BD_Requerimientos_POs.xlsx
+++ b/data/BD_Requerimientos_POs.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="83">
   <si>
     <t>PO</t>
   </si>
@@ -136,16 +136,88 @@
     <t>11-A-6030-01</t>
   </si>
   <si>
+    <t>12-D-6015-05</t>
+  </si>
+  <si>
+    <t>12-D-6017-02</t>
+  </si>
+  <si>
+    <t>12-D-6234-08</t>
+  </si>
+  <si>
+    <t>P20512-09</t>
+  </si>
+  <si>
+    <t>P20512-06</t>
+  </si>
+  <si>
+    <t>P20512-07</t>
+  </si>
+  <si>
+    <t>PP20205-121</t>
+  </si>
+  <si>
+    <t>PP20204-12</t>
+  </si>
+  <si>
+    <t>PP20203-12</t>
+  </si>
+  <si>
+    <t>P20321-12</t>
+  </si>
+  <si>
+    <t>P20346-04</t>
+  </si>
+  <si>
+    <t>13-D-6196-01</t>
+  </si>
+  <si>
+    <t>P20512-18</t>
+  </si>
+  <si>
+    <t>13-D-6195-01</t>
+  </si>
+  <si>
+    <t>P20153S-04</t>
+  </si>
+  <si>
+    <t>P20321S-05</t>
+  </si>
+  <si>
+    <t>12-D-6234-06</t>
+  </si>
+  <si>
+    <t>PP20204-13</t>
+  </si>
+  <si>
+    <t>PP20203-13</t>
+  </si>
+  <si>
+    <t>PP13949-10</t>
+  </si>
+  <si>
+    <t>P20321-13</t>
+  </si>
+  <si>
+    <t>P20321-15-11</t>
+  </si>
+  <si>
+    <t>P20321-15-12</t>
+  </si>
+  <si>
+    <t>P20512-08</t>
+  </si>
+  <si>
+    <t>P20321-21</t>
+  </si>
+  <si>
     <t>PP20204-06</t>
   </si>
   <si>
     <t>PP20203-06</t>
   </si>
   <si>
-    <t>P20153S-04</t>
-  </si>
-  <si>
-    <t>P20321S-05</t>
+    <t>PP20205-061</t>
   </si>
   <si>
     <t>P20321S-06</t>
@@ -154,67 +226,25 @@
     <t>12-6383-01</t>
   </si>
   <si>
-    <t>12-D-6234-08</t>
-  </si>
-  <si>
-    <t>12-D-6234-06</t>
-  </si>
-  <si>
-    <t>12-D-6234-10</t>
-  </si>
-  <si>
-    <t>13-D-6195-01</t>
-  </si>
-  <si>
-    <t>13-D-6196-01</t>
-  </si>
-  <si>
-    <t>PP20204-12</t>
-  </si>
-  <si>
-    <t>PP20204-13</t>
-  </si>
-  <si>
-    <t>PP20203-12</t>
-  </si>
-  <si>
-    <t>PP20203-13</t>
-  </si>
-  <si>
     <t>PP13949-04</t>
   </si>
   <si>
+    <t>PP13949-09</t>
+  </si>
+  <si>
+    <t>PP20205-131</t>
+  </si>
+  <si>
+    <t>PP20205-132</t>
+  </si>
+  <si>
     <t>PP13949-08</t>
   </si>
   <si>
-    <t>PP13949-09</t>
-  </si>
-  <si>
-    <t>PP13949-10</t>
-  </si>
-  <si>
     <t>96-6183-02</t>
   </si>
   <si>
-    <t>P20321-15-11</t>
-  </si>
-  <si>
-    <t>P20321-15-12</t>
-  </si>
-  <si>
-    <t>P20512-06</t>
-  </si>
-  <si>
-    <t>P20512-07</t>
-  </si>
-  <si>
-    <t>P20512-08</t>
-  </si>
-  <si>
-    <t>P20512-09</t>
-  </si>
-  <si>
-    <t>P20512-18</t>
+    <t>P19663-24</t>
   </si>
   <si>
     <t>2026-08-25</t>
@@ -564,7 +594,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E56"/>
+  <dimension ref="A1:E66"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -592,13 +622,13 @@
         <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="D2">
         <v>32</v>
       </c>
       <c r="E2" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -609,13 +639,13 @@
         <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="D3">
         <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -626,13 +656,13 @@
         <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="D4">
         <v>40</v>
       </c>
       <c r="E4" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -643,13 +673,13 @@
         <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="D5">
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -660,13 +690,13 @@
         <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="D6">
         <v>16</v>
       </c>
       <c r="E6" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -677,13 +707,13 @@
         <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="D7">
         <v>128</v>
       </c>
       <c r="E7" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -694,13 +724,13 @@
         <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="D8">
         <v>32</v>
       </c>
       <c r="E8" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -711,13 +741,13 @@
         <v>20</v>
       </c>
       <c r="C9" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="D9">
         <v>40</v>
       </c>
       <c r="E9" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -728,13 +758,13 @@
         <v>21</v>
       </c>
       <c r="C10" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="D10">
         <v>64</v>
       </c>
       <c r="E10" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -745,13 +775,13 @@
         <v>22</v>
       </c>
       <c r="C11" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="D11">
         <v>64</v>
       </c>
       <c r="E11" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -762,13 +792,13 @@
         <v>23</v>
       </c>
       <c r="C12" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="D12">
         <v>40</v>
       </c>
       <c r="E12" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -779,13 +809,13 @@
         <v>24</v>
       </c>
       <c r="C13" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D13">
         <v>32</v>
       </c>
       <c r="E13" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -796,13 +826,13 @@
         <v>25</v>
       </c>
       <c r="C14" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D14">
         <v>40</v>
       </c>
       <c r="E14" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -813,13 +843,13 @@
         <v>26</v>
       </c>
       <c r="C15" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D15">
         <v>40</v>
       </c>
       <c r="E15" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -830,13 +860,13 @@
         <v>27</v>
       </c>
       <c r="C16" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="D16">
         <v>20</v>
       </c>
       <c r="E16" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -847,13 +877,13 @@
         <v>28</v>
       </c>
       <c r="C17" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="D17">
         <v>32</v>
       </c>
       <c r="E17" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -864,13 +894,13 @@
         <v>29</v>
       </c>
       <c r="C18" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="D18">
         <v>64</v>
       </c>
       <c r="E18" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -881,13 +911,13 @@
         <v>30</v>
       </c>
       <c r="C19" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="D19">
         <v>1</v>
       </c>
       <c r="E19" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -898,13 +928,13 @@
         <v>31</v>
       </c>
       <c r="C20" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="D20">
         <v>1</v>
       </c>
       <c r="E20" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -915,13 +945,13 @@
         <v>32</v>
       </c>
       <c r="C21" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="D21">
         <v>12</v>
       </c>
       <c r="E21" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -932,13 +962,13 @@
         <v>33</v>
       </c>
       <c r="C22" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="D22">
         <v>320</v>
       </c>
       <c r="E22" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -949,13 +979,13 @@
         <v>34</v>
       </c>
       <c r="C23" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="D23">
         <v>192</v>
       </c>
       <c r="E23" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -966,13 +996,13 @@
         <v>35</v>
       </c>
       <c r="C24" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="D24">
         <v>224</v>
       </c>
       <c r="E24" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -983,13 +1013,13 @@
         <v>36</v>
       </c>
       <c r="C25" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="D25">
         <v>224</v>
       </c>
       <c r="E25" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1000,13 +1030,13 @@
         <v>37</v>
       </c>
       <c r="C26" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="D26">
         <v>160</v>
       </c>
       <c r="E26" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1017,13 +1047,13 @@
         <v>38</v>
       </c>
       <c r="C27" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="D27">
         <v>160</v>
       </c>
       <c r="E27" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1034,13 +1064,13 @@
         <v>39</v>
       </c>
       <c r="C28" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="D28">
         <v>160</v>
       </c>
       <c r="E28" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -1051,13 +1081,13 @@
         <v>40</v>
       </c>
       <c r="C29" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="D29">
-        <v>80</v>
+        <v>128</v>
       </c>
       <c r="E29" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -1068,13 +1098,13 @@
         <v>41</v>
       </c>
       <c r="C30" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="D30">
-        <v>80</v>
+        <v>160</v>
       </c>
       <c r="E30" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -1085,13 +1115,13 @@
         <v>42</v>
       </c>
       <c r="C31" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="D31">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="E31" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -1102,13 +1132,13 @@
         <v>43</v>
       </c>
       <c r="C32" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="D32">
-        <v>120</v>
+        <v>96</v>
       </c>
       <c r="E32" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -1119,13 +1149,13 @@
         <v>44</v>
       </c>
       <c r="C33" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="D33">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="E33" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -1136,13 +1166,13 @@
         <v>45</v>
       </c>
       <c r="C34" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="D34">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="E34" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -1153,13 +1183,13 @@
         <v>46</v>
       </c>
       <c r="C35" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="D35">
-        <v>160</v>
+        <v>112</v>
       </c>
       <c r="E35" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -1170,13 +1200,13 @@
         <v>47</v>
       </c>
       <c r="C36" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="D36">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="E36" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -1187,13 +1217,13 @@
         <v>48</v>
       </c>
       <c r="C37" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="D37">
-        <v>240</v>
+        <v>112</v>
       </c>
       <c r="E37" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -1204,13 +1234,13 @@
         <v>49</v>
       </c>
       <c r="C38" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="D38">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="E38" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -1221,13 +1251,13 @@
         <v>50</v>
       </c>
       <c r="C39" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="D39">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="E39" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -1238,13 +1268,13 @@
         <v>51</v>
       </c>
       <c r="C40" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="D40">
-        <v>160</v>
+        <v>80</v>
       </c>
       <c r="E40" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -1255,13 +1285,13 @@
         <v>52</v>
       </c>
       <c r="C41" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="D41">
-        <v>120</v>
+        <v>64</v>
       </c>
       <c r="E41" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -1272,13 +1302,13 @@
         <v>53</v>
       </c>
       <c r="C42" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="D42">
-        <v>160</v>
+        <v>80</v>
       </c>
       <c r="E42" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -1289,13 +1319,13 @@
         <v>54</v>
       </c>
       <c r="C43" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="D43">
-        <v>120</v>
+        <v>64</v>
       </c>
       <c r="E43" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -1306,13 +1336,13 @@
         <v>55</v>
       </c>
       <c r="C44" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="D44">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="E44" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -1323,13 +1353,13 @@
         <v>56</v>
       </c>
       <c r="C45" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="D45">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="E45" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -1340,13 +1370,13 @@
         <v>57</v>
       </c>
       <c r="C46" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="D46">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="E46" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -1357,13 +1387,13 @@
         <v>58</v>
       </c>
       <c r="C47" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="D47">
-        <v>160</v>
+        <v>64</v>
       </c>
       <c r="E47" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -1371,16 +1401,16 @@
         <v>13</v>
       </c>
       <c r="B48" t="s">
-        <v>23</v>
+        <v>59</v>
       </c>
       <c r="C48" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="D48">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="E48" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -1388,16 +1418,16 @@
         <v>13</v>
       </c>
       <c r="B49" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C49" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="D49">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="E49" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -1405,16 +1435,16 @@
         <v>13</v>
       </c>
       <c r="B50" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C50" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="D50">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="E50" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -1422,16 +1452,16 @@
         <v>13</v>
       </c>
       <c r="B51" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C51" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="D51">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="E51" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -1439,16 +1469,16 @@
         <v>13</v>
       </c>
       <c r="B52" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C52" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="D52">
-        <v>160</v>
+        <v>32</v>
       </c>
       <c r="E52" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -1456,16 +1486,16 @@
         <v>13</v>
       </c>
       <c r="B53" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C53" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="D53">
-        <v>160</v>
+        <v>40</v>
       </c>
       <c r="E53" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -1473,16 +1503,16 @@
         <v>13</v>
       </c>
       <c r="B54" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C54" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="D54">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="E54" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -1490,16 +1520,16 @@
         <v>13</v>
       </c>
       <c r="B55" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C55" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="D55">
-        <v>160</v>
+        <v>40</v>
       </c>
       <c r="E55" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -1507,16 +1537,186 @@
         <v>13</v>
       </c>
       <c r="B56" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C56" t="s">
+        <v>78</v>
+      </c>
+      <c r="D56">
+        <v>40</v>
+      </c>
+      <c r="E56" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" t="s">
+        <v>13</v>
+      </c>
+      <c r="B57" t="s">
+        <v>68</v>
+      </c>
+      <c r="C57" t="s">
+        <v>78</v>
+      </c>
+      <c r="D57">
+        <v>32</v>
+      </c>
+      <c r="E57" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" t="s">
+        <v>13</v>
+      </c>
+      <c r="B58" t="s">
+        <v>69</v>
+      </c>
+      <c r="C58" t="s">
+        <v>78</v>
+      </c>
+      <c r="D58">
+        <v>40</v>
+      </c>
+      <c r="E58" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" t="s">
+        <v>13</v>
+      </c>
+      <c r="B59" t="s">
         <v>70</v>
       </c>
-      <c r="D56">
-        <v>120</v>
-      </c>
-      <c r="E56" t="s">
+      <c r="C59" t="s">
+        <v>78</v>
+      </c>
+      <c r="D59">
+        <v>32</v>
+      </c>
+      <c r="E59" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" t="s">
+        <v>13</v>
+      </c>
+      <c r="B60" t="s">
+        <v>71</v>
+      </c>
+      <c r="C60" t="s">
+        <v>78</v>
+      </c>
+      <c r="D60">
+        <v>32</v>
+      </c>
+      <c r="E60" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" t="s">
+        <v>13</v>
+      </c>
+      <c r="B61" t="s">
         <v>72</v>
+      </c>
+      <c r="C61" t="s">
+        <v>78</v>
+      </c>
+      <c r="D61">
+        <v>32</v>
+      </c>
+      <c r="E61" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" t="s">
+        <v>13</v>
+      </c>
+      <c r="B62" t="s">
+        <v>73</v>
+      </c>
+      <c r="C62" t="s">
+        <v>78</v>
+      </c>
+      <c r="D62">
+        <v>32</v>
+      </c>
+      <c r="E62" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" t="s">
+        <v>13</v>
+      </c>
+      <c r="B63" t="s">
+        <v>74</v>
+      </c>
+      <c r="C63" t="s">
+        <v>78</v>
+      </c>
+      <c r="D63">
+        <v>32</v>
+      </c>
+      <c r="E63" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" t="s">
+        <v>13</v>
+      </c>
+      <c r="B64" t="s">
+        <v>23</v>
+      </c>
+      <c r="C64" t="s">
+        <v>78</v>
+      </c>
+      <c r="D64">
+        <v>40</v>
+      </c>
+      <c r="E64" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" t="s">
+        <v>13</v>
+      </c>
+      <c r="B65" t="s">
+        <v>75</v>
+      </c>
+      <c r="C65" t="s">
+        <v>78</v>
+      </c>
+      <c r="D65">
+        <v>32</v>
+      </c>
+      <c r="E65" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" t="s">
+        <v>13</v>
+      </c>
+      <c r="B66" t="s">
+        <v>76</v>
+      </c>
+      <c r="C66" t="s">
+        <v>78</v>
+      </c>
+      <c r="D66">
+        <v>32</v>
+      </c>
+      <c r="E66" t="s">
+        <v>82</v>
       </c>
     </row>
   </sheetData>

--- a/data/BD_Requerimientos_POs.xlsx
+++ b/data/BD_Requerimientos_POs.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="86">
   <si>
     <t>PO</t>
   </si>
@@ -58,6 +58,9 @@
     <t>26083425</t>
   </si>
   <si>
+    <t>26033022</t>
+  </si>
+  <si>
     <t>PP19380-03</t>
   </si>
   <si>
@@ -247,6 +250,9 @@
     <t>P19663-24</t>
   </si>
   <si>
+    <t>11-7761-03</t>
+  </si>
+  <si>
     <t>2026-08-25</t>
   </si>
   <si>
@@ -260,6 +266,9 @@
   </si>
   <si>
     <t>2026-09-08</t>
+  </si>
+  <si>
+    <t>2026-08-20</t>
   </si>
   <si>
     <t>P1</t>
@@ -594,7 +603,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E66"/>
+  <dimension ref="A1:E68"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -619,16 +628,16 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D2">
         <v>32</v>
       </c>
       <c r="E2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -636,16 +645,16 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D3">
         <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -653,16 +662,16 @@
         <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D4">
         <v>40</v>
       </c>
       <c r="E4" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -670,16 +679,16 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D5">
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -687,16 +696,16 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C6" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D6">
         <v>16</v>
       </c>
       <c r="E6" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -704,16 +713,16 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D7">
         <v>128</v>
       </c>
       <c r="E7" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -721,16 +730,16 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C8" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D8">
         <v>32</v>
       </c>
       <c r="E8" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -738,16 +747,16 @@
         <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C9" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D9">
         <v>40</v>
       </c>
       <c r="E9" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -755,16 +764,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C10" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D10">
         <v>64</v>
       </c>
       <c r="E10" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -772,16 +781,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C11" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D11">
         <v>64</v>
       </c>
       <c r="E11" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -789,16 +798,16 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C12" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D12">
         <v>40</v>
       </c>
       <c r="E12" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -806,16 +815,16 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C13" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D13">
         <v>32</v>
       </c>
       <c r="E13" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -823,16 +832,16 @@
         <v>10</v>
       </c>
       <c r="B14" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C14" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D14">
         <v>40</v>
       </c>
       <c r="E14" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -840,16 +849,16 @@
         <v>10</v>
       </c>
       <c r="B15" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C15" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D15">
         <v>40</v>
       </c>
       <c r="E15" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -857,16 +866,16 @@
         <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C16" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D16">
         <v>20</v>
       </c>
       <c r="E16" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -874,16 +883,16 @@
         <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C17" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D17">
         <v>32</v>
       </c>
       <c r="E17" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -891,16 +900,16 @@
         <v>11</v>
       </c>
       <c r="B18" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C18" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D18">
         <v>64</v>
       </c>
       <c r="E18" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -908,16 +917,16 @@
         <v>12</v>
       </c>
       <c r="B19" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C19" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D19">
         <v>1</v>
       </c>
       <c r="E19" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -925,16 +934,16 @@
         <v>12</v>
       </c>
       <c r="B20" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C20" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D20">
         <v>1</v>
       </c>
       <c r="E20" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -942,16 +951,16 @@
         <v>12</v>
       </c>
       <c r="B21" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C21" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D21">
         <v>12</v>
       </c>
       <c r="E21" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -959,16 +968,16 @@
         <v>13</v>
       </c>
       <c r="B22" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C22" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D22">
         <v>320</v>
       </c>
       <c r="E22" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -976,16 +985,16 @@
         <v>13</v>
       </c>
       <c r="B23" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C23" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D23">
         <v>192</v>
       </c>
       <c r="E23" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -993,16 +1002,16 @@
         <v>13</v>
       </c>
       <c r="B24" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C24" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D24">
         <v>224</v>
       </c>
       <c r="E24" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1010,16 +1019,16 @@
         <v>13</v>
       </c>
       <c r="B25" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C25" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D25">
         <v>224</v>
       </c>
       <c r="E25" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1027,16 +1036,16 @@
         <v>13</v>
       </c>
       <c r="B26" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C26" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D26">
         <v>160</v>
       </c>
       <c r="E26" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1044,16 +1053,16 @@
         <v>13</v>
       </c>
       <c r="B27" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C27" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D27">
         <v>160</v>
       </c>
       <c r="E27" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1061,16 +1070,16 @@
         <v>13</v>
       </c>
       <c r="B28" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C28" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D28">
         <v>160</v>
       </c>
       <c r="E28" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -1078,16 +1087,16 @@
         <v>13</v>
       </c>
       <c r="B29" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C29" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D29">
         <v>128</v>
       </c>
       <c r="E29" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -1095,16 +1104,16 @@
         <v>13</v>
       </c>
       <c r="B30" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C30" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D30">
         <v>160</v>
       </c>
       <c r="E30" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -1112,16 +1121,16 @@
         <v>13</v>
       </c>
       <c r="B31" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C31" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D31">
         <v>160</v>
       </c>
       <c r="E31" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -1129,16 +1138,16 @@
         <v>13</v>
       </c>
       <c r="B32" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C32" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D32">
         <v>96</v>
       </c>
       <c r="E32" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -1146,16 +1155,16 @@
         <v>13</v>
       </c>
       <c r="B33" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C33" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D33">
         <v>96</v>
       </c>
       <c r="E33" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -1163,16 +1172,16 @@
         <v>13</v>
       </c>
       <c r="B34" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C34" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D34">
         <v>96</v>
       </c>
       <c r="E34" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -1180,16 +1189,16 @@
         <v>13</v>
       </c>
       <c r="B35" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C35" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D35">
         <v>112</v>
       </c>
       <c r="E35" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -1197,16 +1206,16 @@
         <v>13</v>
       </c>
       <c r="B36" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C36" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D36">
         <v>112</v>
       </c>
       <c r="E36" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -1214,16 +1223,16 @@
         <v>13</v>
       </c>
       <c r="B37" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C37" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D37">
         <v>112</v>
       </c>
       <c r="E37" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -1231,16 +1240,16 @@
         <v>13</v>
       </c>
       <c r="B38" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C38" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D38">
         <v>80</v>
       </c>
       <c r="E38" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -1248,16 +1257,16 @@
         <v>13</v>
       </c>
       <c r="B39" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C39" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D39">
         <v>80</v>
       </c>
       <c r="E39" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -1265,16 +1274,16 @@
         <v>13</v>
       </c>
       <c r="B40" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C40" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D40">
         <v>80</v>
       </c>
       <c r="E40" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -1282,16 +1291,16 @@
         <v>13</v>
       </c>
       <c r="B41" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C41" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D41">
         <v>64</v>
       </c>
       <c r="E41" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -1299,16 +1308,16 @@
         <v>13</v>
       </c>
       <c r="B42" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C42" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D42">
         <v>80</v>
       </c>
       <c r="E42" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -1316,16 +1325,16 @@
         <v>13</v>
       </c>
       <c r="B43" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C43" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D43">
         <v>64</v>
       </c>
       <c r="E43" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -1333,16 +1342,16 @@
         <v>13</v>
       </c>
       <c r="B44" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C44" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D44">
         <v>64</v>
       </c>
       <c r="E44" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -1350,16 +1359,16 @@
         <v>13</v>
       </c>
       <c r="B45" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C45" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D45">
         <v>64</v>
       </c>
       <c r="E45" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -1367,16 +1376,16 @@
         <v>13</v>
       </c>
       <c r="B46" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C46" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D46">
         <v>64</v>
       </c>
       <c r="E46" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -1384,16 +1393,16 @@
         <v>13</v>
       </c>
       <c r="B47" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C47" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D47">
         <v>64</v>
       </c>
       <c r="E47" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -1401,16 +1410,16 @@
         <v>13</v>
       </c>
       <c r="B48" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C48" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D48">
         <v>64</v>
       </c>
       <c r="E48" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -1418,16 +1427,16 @@
         <v>13</v>
       </c>
       <c r="B49" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C49" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D49">
         <v>40</v>
       </c>
       <c r="E49" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -1435,16 +1444,16 @@
         <v>13</v>
       </c>
       <c r="B50" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C50" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D50">
         <v>40</v>
       </c>
       <c r="E50" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -1452,16 +1461,16 @@
         <v>13</v>
       </c>
       <c r="B51" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C51" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D51">
         <v>40</v>
       </c>
       <c r="E51" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -1469,16 +1478,16 @@
         <v>13</v>
       </c>
       <c r="B52" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C52" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D52">
         <v>32</v>
       </c>
       <c r="E52" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -1486,16 +1495,16 @@
         <v>13</v>
       </c>
       <c r="B53" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C53" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D53">
         <v>40</v>
       </c>
       <c r="E53" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -1503,16 +1512,16 @@
         <v>13</v>
       </c>
       <c r="B54" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C54" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D54">
         <v>40</v>
       </c>
       <c r="E54" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -1520,16 +1529,16 @@
         <v>13</v>
       </c>
       <c r="B55" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C55" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D55">
         <v>40</v>
       </c>
       <c r="E55" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -1537,16 +1546,16 @@
         <v>13</v>
       </c>
       <c r="B56" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C56" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D56">
         <v>40</v>
       </c>
       <c r="E56" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -1554,16 +1563,16 @@
         <v>13</v>
       </c>
       <c r="B57" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C57" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D57">
         <v>32</v>
       </c>
       <c r="E57" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -1571,16 +1580,16 @@
         <v>13</v>
       </c>
       <c r="B58" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C58" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D58">
         <v>40</v>
       </c>
       <c r="E58" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -1588,16 +1597,16 @@
         <v>13</v>
       </c>
       <c r="B59" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C59" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D59">
         <v>32</v>
       </c>
       <c r="E59" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -1605,16 +1614,16 @@
         <v>13</v>
       </c>
       <c r="B60" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C60" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D60">
         <v>32</v>
       </c>
       <c r="E60" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -1622,16 +1631,16 @@
         <v>13</v>
       </c>
       <c r="B61" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C61" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D61">
         <v>32</v>
       </c>
       <c r="E61" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -1639,16 +1648,16 @@
         <v>13</v>
       </c>
       <c r="B62" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C62" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D62">
         <v>32</v>
       </c>
       <c r="E62" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -1656,16 +1665,16 @@
         <v>13</v>
       </c>
       <c r="B63" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C63" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D63">
         <v>32</v>
       </c>
       <c r="E63" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -1673,16 +1682,16 @@
         <v>13</v>
       </c>
       <c r="B64" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C64" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D64">
         <v>40</v>
       </c>
       <c r="E64" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -1690,16 +1699,16 @@
         <v>13</v>
       </c>
       <c r="B65" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C65" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D65">
         <v>32</v>
       </c>
       <c r="E65" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -1707,16 +1716,50 @@
         <v>13</v>
       </c>
       <c r="B66" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C66" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D66">
         <v>32</v>
       </c>
       <c r="E66" t="s">
-        <v>82</v>
+        <v>85</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" t="s">
+        <v>14</v>
+      </c>
+      <c r="B67" t="s">
+        <v>16</v>
+      </c>
+      <c r="C67" t="s">
+        <v>84</v>
+      </c>
+      <c r="D67">
+        <v>73</v>
+      </c>
+      <c r="E67" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" t="s">
+        <v>14</v>
+      </c>
+      <c r="B68" t="s">
+        <v>78</v>
+      </c>
+      <c r="C68" t="s">
+        <v>84</v>
+      </c>
+      <c r="D68">
+        <v>4</v>
+      </c>
+      <c r="E68" t="s">
+        <v>85</v>
       </c>
     </row>
   </sheetData>

--- a/data/BD_Requerimientos_POs.xlsx
+++ b/data/BD_Requerimientos_POs.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1137" uniqueCount="273">
   <si>
     <t>PO</t>
   </si>
@@ -31,6 +31,15 @@
     <t>Parcialidad</t>
   </si>
   <si>
+    <t>26083425</t>
+  </si>
+  <si>
+    <t>26033022</t>
+  </si>
+  <si>
+    <t>26033086</t>
+  </si>
+  <si>
     <t>26083186</t>
   </si>
   <si>
@@ -55,220 +64,772 @@
     <t>26083358</t>
   </si>
   <si>
-    <t>26083425</t>
-  </si>
-  <si>
-    <t>26033022</t>
+    <t>26083373</t>
+  </si>
+  <si>
+    <t>26083382</t>
+  </si>
+  <si>
+    <t>26083394</t>
+  </si>
+  <si>
+    <t>26083428</t>
+  </si>
+  <si>
+    <t>11-D-6165-01</t>
+  </si>
+  <si>
+    <t>11-A-6037-01</t>
+  </si>
+  <si>
+    <t>12-6267-01</t>
+  </si>
+  <si>
+    <t>12-6265-01</t>
+  </si>
+  <si>
+    <t>PP14112-19</t>
+  </si>
+  <si>
+    <t>P17311-17</t>
+  </si>
+  <si>
+    <t>11-A-6030-01</t>
+  </si>
+  <si>
+    <t>12-D-6015-05</t>
+  </si>
+  <si>
+    <t>12-D-6017-02</t>
+  </si>
+  <si>
+    <t>12-D-6234-08</t>
+  </si>
+  <si>
+    <t>P20512-09</t>
+  </si>
+  <si>
+    <t>P20512-06</t>
+  </si>
+  <si>
+    <t>P20512-07</t>
+  </si>
+  <si>
+    <t>PP20205-121</t>
+  </si>
+  <si>
+    <t>PP20204-12</t>
+  </si>
+  <si>
+    <t>PP20203-12</t>
+  </si>
+  <si>
+    <t>P20321-12</t>
+  </si>
+  <si>
+    <t>P20346-04</t>
+  </si>
+  <si>
+    <t>13-D-6196-01</t>
+  </si>
+  <si>
+    <t>P20512-18</t>
+  </si>
+  <si>
+    <t>13-D-6195-01</t>
+  </si>
+  <si>
+    <t>P20153S-04</t>
+  </si>
+  <si>
+    <t>P20321S-05</t>
+  </si>
+  <si>
+    <t>12-D-6234-06</t>
+  </si>
+  <si>
+    <t>PP20204-13</t>
+  </si>
+  <si>
+    <t>PP20203-13</t>
+  </si>
+  <si>
+    <t>PP13949-10</t>
+  </si>
+  <si>
+    <t>P20321-13</t>
+  </si>
+  <si>
+    <t>P20321-15-11</t>
+  </si>
+  <si>
+    <t>P20321-15-12</t>
+  </si>
+  <si>
+    <t>P20512-08</t>
+  </si>
+  <si>
+    <t>P20321-21</t>
+  </si>
+  <si>
+    <t>PP20204-06</t>
+  </si>
+  <si>
+    <t>PP20203-06</t>
+  </si>
+  <si>
+    <t>PP20205-061</t>
+  </si>
+  <si>
+    <t>P20321S-06</t>
+  </si>
+  <si>
+    <t>12-6383-01</t>
+  </si>
+  <si>
+    <t>PP13949-04</t>
+  </si>
+  <si>
+    <t>PP13949-09</t>
+  </si>
+  <si>
+    <t>PP20205-131</t>
+  </si>
+  <si>
+    <t>PP20205-132</t>
+  </si>
+  <si>
+    <t>PP13949-08</t>
+  </si>
+  <si>
+    <t>96-6183-01</t>
+  </si>
+  <si>
+    <t>96-6183-02</t>
+  </si>
+  <si>
+    <t>P19663-24</t>
+  </si>
+  <si>
+    <t>11-7761-03</t>
+  </si>
+  <si>
+    <t>11-7761-02</t>
+  </si>
+  <si>
+    <t>11-A-6013-01</t>
+  </si>
+  <si>
+    <t>11-A-6013-03</t>
+  </si>
+  <si>
+    <t>11-A-6102-01</t>
+  </si>
+  <si>
+    <t>11-D-9297-01</t>
+  </si>
+  <si>
+    <t>11-D-9298-01</t>
+  </si>
+  <si>
+    <t>12-6010-08</t>
+  </si>
+  <si>
+    <t>12-6010-12</t>
+  </si>
+  <si>
+    <t>12-D-6047-09</t>
+  </si>
+  <si>
+    <t>12-D-6075-01</t>
+  </si>
+  <si>
+    <t>12-D-6079-05</t>
+  </si>
+  <si>
+    <t>13-D-6378-01</t>
+  </si>
+  <si>
+    <t>13-D-6394-01</t>
+  </si>
+  <si>
+    <t>16-A-6001-01</t>
+  </si>
+  <si>
+    <t>P15324-19</t>
+  </si>
+  <si>
+    <t>P15899-10</t>
+  </si>
+  <si>
+    <t>P20553-09</t>
+  </si>
+  <si>
+    <t>P20557-20</t>
+  </si>
+  <si>
+    <t>P20557-21</t>
+  </si>
+  <si>
+    <t>P20593-15</t>
+  </si>
+  <si>
+    <t>P20596-21</t>
+  </si>
+  <si>
+    <t>P20596-22</t>
+  </si>
+  <si>
+    <t>PP20825-02</t>
+  </si>
+  <si>
+    <t>PP6868-113</t>
   </si>
   <si>
     <t>PP19380-03</t>
   </si>
   <si>
-    <t>11-7761-02</t>
-  </si>
-  <si>
     <t>11-A-6014-01</t>
   </si>
   <si>
+    <t>12-D-6013-01</t>
+  </si>
+  <si>
+    <t>PP14873-01</t>
+  </si>
+  <si>
+    <t>PP14873-02</t>
+  </si>
+  <si>
+    <t>P20325-24</t>
+  </si>
+  <si>
+    <t>P20325-25</t>
+  </si>
+  <si>
+    <t>12-6355-03</t>
+  </si>
+  <si>
+    <t>12-6355-02</t>
+  </si>
+  <si>
+    <t>PP22114-05</t>
+  </si>
+  <si>
+    <t>12-D-6091-08</t>
+  </si>
+  <si>
+    <t>PP7517-10</t>
+  </si>
+  <si>
+    <t>PP7517-01</t>
+  </si>
+  <si>
+    <t>11-A-9843-01</t>
+  </si>
+  <si>
+    <t>11-A-9845-01</t>
+  </si>
+  <si>
+    <t>11-A-9847-01</t>
+  </si>
+  <si>
+    <t>11-A-9875-01</t>
+  </si>
+  <si>
+    <t>11-A-9875-03</t>
+  </si>
+  <si>
+    <t>11-A-9951-01</t>
+  </si>
+  <si>
+    <t>11-A-9960-01</t>
+  </si>
+  <si>
+    <t>11-A-9961-01</t>
+  </si>
+  <si>
+    <t>11-B-9086-01</t>
+  </si>
+  <si>
+    <t>11-B-9193-01</t>
+  </si>
+  <si>
+    <t>11-B-9194-03</t>
+  </si>
+  <si>
+    <t>11-B-9194-04</t>
+  </si>
+  <si>
+    <t>11-B-9195-01</t>
+  </si>
+  <si>
+    <t>11-B-9208-01 TRTO</t>
+  </si>
+  <si>
+    <t>11-B-9208-02 TRTO</t>
+  </si>
+  <si>
+    <t>11-B-9211-01</t>
+  </si>
+  <si>
+    <t>11-B-9310-01</t>
+  </si>
+  <si>
+    <t>11-B-9311-02</t>
+  </si>
+  <si>
+    <t>11-B-9743-01</t>
+  </si>
+  <si>
+    <t>11-B-9743-02</t>
+  </si>
+  <si>
+    <t>11-B-9753-01</t>
+  </si>
+  <si>
+    <t>11-B-9754-01</t>
+  </si>
+  <si>
+    <t>11-B-9754-02</t>
+  </si>
+  <si>
+    <t>11-C-9115-01</t>
+  </si>
+  <si>
+    <t>11-C-9115-02</t>
+  </si>
+  <si>
+    <t>11-C-9229-01</t>
+  </si>
+  <si>
+    <t>11-C-9230-01</t>
+  </si>
+  <si>
+    <t>11-C-9231-01</t>
+  </si>
+  <si>
+    <t>11-C-9232-01</t>
+  </si>
+  <si>
+    <t>11-C-9233-01</t>
+  </si>
+  <si>
+    <t>11-C-9233-02</t>
+  </si>
+  <si>
+    <t>11-C-9241-01</t>
+  </si>
+  <si>
+    <t>11-C-9241-02</t>
+  </si>
+  <si>
+    <t>11-C-9242-01</t>
+  </si>
+  <si>
+    <t>11-C-9242-02</t>
+  </si>
+  <si>
+    <t>11-C-9243-01</t>
+  </si>
+  <si>
+    <t>11-C-9244-01</t>
+  </si>
+  <si>
+    <t>11-C-9245-01</t>
+  </si>
+  <si>
+    <t>11-C-9246-01</t>
+  </si>
+  <si>
+    <t>11-C-9247-01</t>
+  </si>
+  <si>
+    <t>11-C-9248-01</t>
+  </si>
+  <si>
+    <t>11-C-9249-01</t>
+  </si>
+  <si>
+    <t>11-C-9250-01</t>
+  </si>
+  <si>
+    <t>11-C-9277-02</t>
+  </si>
+  <si>
+    <t>11-C-9280-01</t>
+  </si>
+  <si>
+    <t>11-C-9281-01</t>
+  </si>
+  <si>
+    <t>11-C-9282-01</t>
+  </si>
+  <si>
+    <t>11-C-9283-01</t>
+  </si>
+  <si>
+    <t>11-C-9284-01</t>
+  </si>
+  <si>
+    <t>11-C-9285-01</t>
+  </si>
+  <si>
+    <t>11-C-9352-01</t>
+  </si>
+  <si>
+    <t>11-C-9611-01</t>
+  </si>
+  <si>
+    <t>11-C-9612-01</t>
+  </si>
+  <si>
+    <t>11-C-9746-01</t>
+  </si>
+  <si>
+    <t>11-C-9747-01</t>
+  </si>
+  <si>
+    <t>11-C-9778-01 TRTO</t>
+  </si>
+  <si>
+    <t>11-C-9962-01</t>
+  </si>
+  <si>
+    <t>11-D-9534-01 TRTO</t>
+  </si>
+  <si>
+    <t>11-D-9535-01 TRTO</t>
+  </si>
+  <si>
+    <t>11-D-9812-01</t>
+  </si>
+  <si>
+    <t>11-D-9817-01</t>
+  </si>
+  <si>
+    <t>11-D-9820-01</t>
+  </si>
+  <si>
+    <t>11-D-9821-01</t>
+  </si>
+  <si>
+    <t>11-D-9824-01</t>
+  </si>
+  <si>
+    <t>11-D-9825-01</t>
+  </si>
+  <si>
+    <t>11-D-9828-01</t>
+  </si>
+  <si>
+    <t>11-D-9829-01</t>
+  </si>
+  <si>
+    <t>11-D-9978-202 TRTO</t>
+  </si>
+  <si>
+    <t>11-E-9246-01</t>
+  </si>
+  <si>
+    <t>11-E-9250-01</t>
+  </si>
+  <si>
+    <t>11-E-9256-01</t>
+  </si>
+  <si>
+    <t>11-E-9675-01</t>
+  </si>
+  <si>
+    <t>11-E-9676-01</t>
+  </si>
+  <si>
+    <t>11-E-9740-01</t>
+  </si>
+  <si>
+    <t>11-E-9740-04</t>
+  </si>
+  <si>
+    <t>11-E-9745-01</t>
+  </si>
+  <si>
+    <t>11-E-9745-04</t>
+  </si>
+  <si>
+    <t>11-E-9746-01</t>
+  </si>
+  <si>
+    <t>11-E-9749-01</t>
+  </si>
+  <si>
+    <t>11-E-9768-01</t>
+  </si>
+  <si>
+    <t>11-E-9769-01</t>
+  </si>
+  <si>
+    <t>11-E-9772-01</t>
+  </si>
+  <si>
+    <t>11-E-9773-01</t>
+  </si>
+  <si>
+    <t>11-E-9774-01</t>
+  </si>
+  <si>
+    <t>11-E-9846-01</t>
+  </si>
+  <si>
+    <t>11-E-9892-01</t>
+  </si>
+  <si>
+    <t>11-E-9892-03</t>
+  </si>
+  <si>
+    <t>11-E-9893-01</t>
+  </si>
+  <si>
+    <t>11-E-9893-03</t>
+  </si>
+  <si>
+    <t>11-E-9894-01</t>
+  </si>
+  <si>
+    <t>11-E-9894-03</t>
+  </si>
+  <si>
+    <t>11-E-9894-09</t>
+  </si>
+  <si>
+    <t>11-E-9895-01</t>
+  </si>
+  <si>
+    <t>11-E-9896-01</t>
+  </si>
+  <si>
+    <t>11-E-9897-01</t>
+  </si>
+  <si>
+    <t>11-E-9897-03</t>
+  </si>
+  <si>
+    <t>11-E-9898-01</t>
+  </si>
+  <si>
+    <t>11-E-9898-03</t>
+  </si>
+  <si>
+    <t>11-E-9899-01</t>
+  </si>
+  <si>
+    <t>11-E-9900-01</t>
+  </si>
+  <si>
+    <t>11-E-9900-03</t>
+  </si>
+  <si>
+    <t>11-E-9900-09</t>
+  </si>
+  <si>
+    <t>11-E-9901-01</t>
+  </si>
+  <si>
+    <t>11-E-9902-01</t>
+  </si>
+  <si>
+    <t>11-E-9903-01</t>
+  </si>
+  <si>
+    <t>11-E-9909-02</t>
+  </si>
+  <si>
+    <t>11-E-9909-02 TRTO</t>
+  </si>
+  <si>
+    <t>11-E-9910-02</t>
+  </si>
+  <si>
+    <t>11-E-9911-02</t>
+  </si>
+  <si>
+    <t>11-E-9969-01L</t>
+  </si>
+  <si>
+    <t>11-E-9969-01R</t>
+  </si>
+  <si>
+    <t>11-F-9276-01</t>
+  </si>
+  <si>
+    <t>P9711-081</t>
+  </si>
+  <si>
+    <t>P9711-08 TRTO</t>
+  </si>
+  <si>
+    <t>P9711-08 TRTO1</t>
+  </si>
+  <si>
+    <t>P9711-08 TRTO2</t>
+  </si>
+  <si>
+    <t>P9711-081 TRTO</t>
+  </si>
+  <si>
+    <t>P9711-081 TRTO1</t>
+  </si>
+  <si>
+    <t>PP10218-13-TBC3</t>
+  </si>
+  <si>
+    <t>PP21139-081 TRTO</t>
+  </si>
+  <si>
+    <t>PP21139-082 TRTO</t>
+  </si>
+  <si>
+    <t>PP21139-091 TRTO</t>
+  </si>
+  <si>
+    <t>PP21139-092 TRTO</t>
+  </si>
+  <si>
+    <t>PP8192-05 TRTO</t>
+  </si>
+  <si>
+    <t>PP8655</t>
+  </si>
+  <si>
+    <t>PP8655 TRT0</t>
+  </si>
+  <si>
+    <t>PP8655 TRT01</t>
+  </si>
+  <si>
     <t>11-A-9836-01</t>
   </si>
   <si>
-    <t>12-D-6013-01</t>
-  </si>
-  <si>
-    <t>PP14873-01</t>
-  </si>
-  <si>
-    <t>PP14873-02</t>
-  </si>
-  <si>
-    <t>P20325-25</t>
-  </si>
-  <si>
-    <t>P20325-24</t>
-  </si>
-  <si>
-    <t>96-6183-01</t>
-  </si>
-  <si>
-    <t>12-6355-03</t>
-  </si>
-  <si>
-    <t>12-6355-02</t>
-  </si>
-  <si>
-    <t>PP22114-05</t>
-  </si>
-  <si>
-    <t>12-D-6091-08</t>
-  </si>
-  <si>
-    <t>PP7517-10</t>
-  </si>
-  <si>
-    <t>PP7517-01</t>
-  </si>
-  <si>
-    <t>P9711-081 TRTO1</t>
-  </si>
-  <si>
-    <t>PP10218-13-TBC3</t>
-  </si>
-  <si>
-    <t>PP21139-081 TRTO</t>
-  </si>
-  <si>
-    <t>11-D-6165-01</t>
-  </si>
-  <si>
-    <t>11-A-6037-01</t>
-  </si>
-  <si>
-    <t>12-6267-01</t>
-  </si>
-  <si>
-    <t>12-6265-01</t>
-  </si>
-  <si>
-    <t>PP14112-19</t>
-  </si>
-  <si>
-    <t>P17311-17</t>
-  </si>
-  <si>
-    <t>11-A-6030-01</t>
-  </si>
-  <si>
-    <t>12-D-6015-05</t>
-  </si>
-  <si>
-    <t>12-D-6017-02</t>
-  </si>
-  <si>
-    <t>12-D-6234-08</t>
-  </si>
-  <si>
-    <t>P20512-09</t>
-  </si>
-  <si>
-    <t>P20512-06</t>
-  </si>
-  <si>
-    <t>P20512-07</t>
-  </si>
-  <si>
-    <t>PP20205-121</t>
-  </si>
-  <si>
-    <t>PP20204-12</t>
-  </si>
-  <si>
-    <t>PP20203-12</t>
-  </si>
-  <si>
-    <t>P20321-12</t>
-  </si>
-  <si>
-    <t>P20346-04</t>
-  </si>
-  <si>
-    <t>13-D-6196-01</t>
-  </si>
-  <si>
-    <t>P20512-18</t>
-  </si>
-  <si>
-    <t>13-D-6195-01</t>
-  </si>
-  <si>
-    <t>P20153S-04</t>
-  </si>
-  <si>
-    <t>P20321S-05</t>
-  </si>
-  <si>
-    <t>12-D-6234-06</t>
-  </si>
-  <si>
-    <t>PP20204-13</t>
-  </si>
-  <si>
-    <t>PP20203-13</t>
-  </si>
-  <si>
-    <t>PP13949-10</t>
-  </si>
-  <si>
-    <t>P20321-13</t>
-  </si>
-  <si>
-    <t>P20321-15-11</t>
-  </si>
-  <si>
-    <t>P20321-15-12</t>
-  </si>
-  <si>
-    <t>P20512-08</t>
-  </si>
-  <si>
-    <t>P20321-21</t>
-  </si>
-  <si>
-    <t>PP20204-06</t>
-  </si>
-  <si>
-    <t>PP20203-06</t>
-  </si>
-  <si>
-    <t>PP20205-061</t>
-  </si>
-  <si>
-    <t>P20321S-06</t>
-  </si>
-  <si>
-    <t>12-6383-01</t>
-  </si>
-  <si>
-    <t>PP13949-04</t>
-  </si>
-  <si>
-    <t>PP13949-09</t>
-  </si>
-  <si>
-    <t>PP20205-131</t>
-  </si>
-  <si>
-    <t>PP20205-132</t>
-  </si>
-  <si>
-    <t>PP13949-08</t>
-  </si>
-  <si>
-    <t>96-6183-02</t>
-  </si>
-  <si>
-    <t>P19663-24</t>
-  </si>
-  <si>
-    <t>11-7761-03</t>
-  </si>
-  <si>
-    <t>2026-08-25</t>
-  </si>
-  <si>
-    <t>2026-09-07</t>
-  </si>
-  <si>
-    <t>2026-08-28</t>
-  </si>
-  <si>
-    <t>2026-08-31</t>
-  </si>
-  <si>
-    <t>2026-09-08</t>
-  </si>
-  <si>
-    <t>2026-08-20</t>
+    <t>11-A-9837-01</t>
+  </si>
+  <si>
+    <t>11-A-9846-01</t>
+  </si>
+  <si>
+    <t>11-A-9958-01</t>
+  </si>
+  <si>
+    <t>11-A-9959-01</t>
+  </si>
+  <si>
+    <t>11-B-9034-01</t>
+  </si>
+  <si>
+    <t>11-B-9083-01</t>
+  </si>
+  <si>
+    <t>11-C-9617-01</t>
+  </si>
+  <si>
+    <t>11-C-9618-01</t>
+  </si>
+  <si>
+    <t>11-C-9620-01</t>
+  </si>
+  <si>
+    <t>11-C-9621-01</t>
+  </si>
+  <si>
+    <t>11-C-9709-01</t>
+  </si>
+  <si>
+    <t>11-C-9709-01 IRV</t>
+  </si>
+  <si>
+    <t>11-C-9779-01 IRV</t>
+  </si>
+  <si>
+    <t>11-C-9831-01 IRV2</t>
+  </si>
+  <si>
+    <t>11-C-9832-01 IRV1</t>
+  </si>
+  <si>
+    <t>11-D-9156-01</t>
+  </si>
+  <si>
+    <t>11-D-9643-01</t>
+  </si>
+  <si>
+    <t>11-D-9814-01</t>
+  </si>
+  <si>
+    <t>11-D-9819-01</t>
+  </si>
+  <si>
+    <t>11-D-9978-201 IRV</t>
+  </si>
+  <si>
+    <t>11-D-9978-201 IRV 2</t>
+  </si>
+  <si>
+    <t>11-C-9708-01 IRV</t>
+  </si>
+  <si>
+    <t>11-C-9779-01 IRV2</t>
+  </si>
+  <si>
+    <t>11-D-9156-04</t>
+  </si>
+  <si>
+    <t>P19500-16</t>
+  </si>
+  <si>
+    <t>P19500-19</t>
+  </si>
+  <si>
+    <t>12-D-6047-03</t>
+  </si>
+  <si>
+    <t>12-D-6106-08</t>
+  </si>
+  <si>
+    <t>PP14805-04</t>
+  </si>
+  <si>
+    <t>12-D-6030-10</t>
+  </si>
+  <si>
+    <t>PP9247</t>
+  </si>
+  <si>
+    <t>07/09/2026</t>
+  </si>
+  <si>
+    <t>17/08/2026</t>
+  </si>
+  <si>
+    <t>21/09/2026</t>
+  </si>
+  <si>
+    <t>18/08/2026</t>
+  </si>
+  <si>
+    <t>01/09/2026</t>
+  </si>
+  <si>
+    <t>30/08/2026</t>
+  </si>
+  <si>
+    <t>20/08/2026</t>
+  </si>
+  <si>
+    <t>21/08/2026</t>
+  </si>
+  <si>
+    <t>25/09/2026</t>
+  </si>
+  <si>
+    <t>31/08/2026</t>
   </si>
   <si>
     <t>P1</t>
@@ -603,7 +1164,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E68"/>
+  <dimension ref="A1:E284"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -628,1138 +1189,4810 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>79</v>
+        <v>262</v>
       </c>
       <c r="D2">
-        <v>32</v>
+        <v>320</v>
       </c>
       <c r="E2" t="s">
-        <v>85</v>
+        <v>272</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>79</v>
+        <v>262</v>
       </c>
       <c r="D3">
-        <v>8</v>
+        <v>192</v>
       </c>
       <c r="E3" t="s">
-        <v>85</v>
+        <v>272</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>79</v>
+        <v>262</v>
       </c>
       <c r="D4">
-        <v>40</v>
+        <v>224</v>
       </c>
       <c r="E4" t="s">
-        <v>85</v>
+        <v>272</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>79</v>
+        <v>262</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>224</v>
       </c>
       <c r="E5" t="s">
-        <v>85</v>
+        <v>272</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>80</v>
+        <v>262</v>
       </c>
       <c r="D6">
-        <v>16</v>
+        <v>160</v>
       </c>
       <c r="E6" t="s">
-        <v>85</v>
+        <v>272</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>80</v>
+        <v>262</v>
       </c>
       <c r="D7">
-        <v>128</v>
+        <v>160</v>
       </c>
       <c r="E7" t="s">
-        <v>85</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>80</v>
+        <v>262</v>
       </c>
       <c r="D8">
-        <v>32</v>
+        <v>160</v>
       </c>
       <c r="E8" t="s">
-        <v>85</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>80</v>
+        <v>262</v>
       </c>
       <c r="D9">
-        <v>40</v>
+        <v>128</v>
       </c>
       <c r="E9" t="s">
-        <v>85</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B10" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>80</v>
+        <v>262</v>
       </c>
       <c r="D10">
-        <v>64</v>
+        <v>160</v>
       </c>
       <c r="E10" t="s">
-        <v>85</v>
+        <v>272</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B11" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>80</v>
+        <v>262</v>
       </c>
       <c r="D11">
-        <v>64</v>
+        <v>160</v>
       </c>
       <c r="E11" t="s">
-        <v>85</v>
+        <v>272</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B12" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>80</v>
+        <v>262</v>
       </c>
       <c r="D12">
-        <v>40</v>
+        <v>96</v>
       </c>
       <c r="E12" t="s">
-        <v>85</v>
+        <v>272</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B13" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C13" t="s">
-        <v>81</v>
+        <v>262</v>
       </c>
       <c r="D13">
-        <v>32</v>
+        <v>96</v>
       </c>
       <c r="E13" t="s">
-        <v>85</v>
+        <v>272</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B14" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C14" t="s">
-        <v>81</v>
+        <v>262</v>
       </c>
       <c r="D14">
-        <v>40</v>
+        <v>96</v>
       </c>
       <c r="E14" t="s">
-        <v>85</v>
+        <v>272</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B15" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C15" t="s">
-        <v>81</v>
+        <v>262</v>
       </c>
       <c r="D15">
-        <v>40</v>
+        <v>112</v>
       </c>
       <c r="E15" t="s">
-        <v>85</v>
+        <v>272</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B16" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C16" t="s">
-        <v>82</v>
+        <v>262</v>
       </c>
       <c r="D16">
-        <v>20</v>
+        <v>112</v>
       </c>
       <c r="E16" t="s">
-        <v>85</v>
+        <v>272</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B17" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="C17" t="s">
-        <v>82</v>
+        <v>262</v>
       </c>
       <c r="D17">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="E17" t="s">
-        <v>85</v>
+        <v>272</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B18" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C18" t="s">
-        <v>82</v>
+        <v>262</v>
       </c>
       <c r="D18">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="E18" t="s">
-        <v>85</v>
+        <v>272</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="B19" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="C19" t="s">
-        <v>83</v>
+        <v>262</v>
       </c>
       <c r="D19">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="E19" t="s">
-        <v>85</v>
+        <v>272</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="B20" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C20" t="s">
-        <v>83</v>
+        <v>262</v>
       </c>
       <c r="D20">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="E20" t="s">
-        <v>85</v>
+        <v>272</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="B21" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="C21" t="s">
-        <v>83</v>
+        <v>262</v>
       </c>
       <c r="D21">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="E21" t="s">
-        <v>85</v>
+        <v>272</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B22" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C22" t="s">
+        <v>262</v>
+      </c>
+      <c r="D22">
         <v>80</v>
       </c>
-      <c r="D22">
-        <v>320</v>
-      </c>
       <c r="E22" t="s">
-        <v>85</v>
+        <v>272</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B23" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C23" t="s">
-        <v>80</v>
+        <v>262</v>
       </c>
       <c r="D23">
-        <v>192</v>
+        <v>64</v>
       </c>
       <c r="E23" t="s">
-        <v>85</v>
+        <v>272</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B24" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C24" t="s">
-        <v>80</v>
+        <v>262</v>
       </c>
       <c r="D24">
-        <v>224</v>
+        <v>64</v>
       </c>
       <c r="E24" t="s">
-        <v>85</v>
+        <v>272</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B25" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C25" t="s">
-        <v>80</v>
+        <v>262</v>
       </c>
       <c r="D25">
-        <v>224</v>
+        <v>64</v>
       </c>
       <c r="E25" t="s">
-        <v>85</v>
+        <v>272</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B26" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C26" t="s">
-        <v>80</v>
+        <v>262</v>
       </c>
       <c r="D26">
-        <v>160</v>
+        <v>64</v>
       </c>
       <c r="E26" t="s">
-        <v>85</v>
+        <v>272</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B27" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="C27" t="s">
-        <v>80</v>
+        <v>262</v>
       </c>
       <c r="D27">
-        <v>160</v>
+        <v>64</v>
       </c>
       <c r="E27" t="s">
-        <v>85</v>
+        <v>272</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B28" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C28" t="s">
-        <v>80</v>
+        <v>262</v>
       </c>
       <c r="D28">
-        <v>160</v>
+        <v>64</v>
       </c>
       <c r="E28" t="s">
-        <v>85</v>
+        <v>272</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B29" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C29" t="s">
-        <v>80</v>
+        <v>262</v>
       </c>
       <c r="D29">
-        <v>128</v>
+        <v>40</v>
       </c>
       <c r="E29" t="s">
-        <v>85</v>
+        <v>272</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B30" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C30" t="s">
-        <v>80</v>
+        <v>262</v>
       </c>
       <c r="D30">
-        <v>160</v>
+        <v>40</v>
       </c>
       <c r="E30" t="s">
-        <v>85</v>
+        <v>272</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B31" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="C31" t="s">
-        <v>80</v>
+        <v>262</v>
       </c>
       <c r="D31">
-        <v>160</v>
+        <v>40</v>
       </c>
       <c r="E31" t="s">
-        <v>85</v>
+        <v>272</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B32" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="C32" t="s">
-        <v>80</v>
+        <v>262</v>
       </c>
       <c r="D32">
-        <v>96</v>
+        <v>32</v>
       </c>
       <c r="E32" t="s">
-        <v>85</v>
+        <v>272</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B33" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C33" t="s">
-        <v>80</v>
+        <v>262</v>
       </c>
       <c r="D33">
-        <v>96</v>
+        <v>40</v>
       </c>
       <c r="E33" t="s">
-        <v>85</v>
+        <v>272</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B34" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C34" t="s">
-        <v>80</v>
+        <v>262</v>
       </c>
       <c r="D34">
-        <v>96</v>
+        <v>40</v>
       </c>
       <c r="E34" t="s">
-        <v>85</v>
+        <v>272</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B35" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C35" t="s">
-        <v>80</v>
+        <v>262</v>
       </c>
       <c r="D35">
-        <v>112</v>
+        <v>40</v>
       </c>
       <c r="E35" t="s">
-        <v>85</v>
+        <v>272</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B36" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="C36" t="s">
-        <v>80</v>
+        <v>262</v>
       </c>
       <c r="D36">
-        <v>112</v>
+        <v>40</v>
       </c>
       <c r="E36" t="s">
-        <v>85</v>
+        <v>272</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B37" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="C37" t="s">
-        <v>80</v>
+        <v>262</v>
       </c>
       <c r="D37">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="E37" t="s">
-        <v>85</v>
+        <v>272</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B38" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="C38" t="s">
-        <v>80</v>
+        <v>262</v>
       </c>
       <c r="D38">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="E38" t="s">
-        <v>85</v>
+        <v>272</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B39" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="C39" t="s">
-        <v>80</v>
+        <v>262</v>
       </c>
       <c r="D39">
-        <v>80</v>
+        <v>32</v>
       </c>
       <c r="E39" t="s">
-        <v>85</v>
+        <v>272</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B40" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="C40" t="s">
-        <v>80</v>
+        <v>262</v>
       </c>
       <c r="D40">
-        <v>80</v>
+        <v>32</v>
       </c>
       <c r="E40" t="s">
-        <v>85</v>
+        <v>272</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B41" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="C41" t="s">
-        <v>80</v>
+        <v>262</v>
       </c>
       <c r="D41">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="E41" t="s">
-        <v>85</v>
+        <v>272</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B42" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="C42" t="s">
-        <v>80</v>
+        <v>262</v>
       </c>
       <c r="D42">
-        <v>80</v>
+        <v>32</v>
       </c>
       <c r="E42" t="s">
-        <v>85</v>
+        <v>272</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B43" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="C43" t="s">
-        <v>80</v>
+        <v>262</v>
       </c>
       <c r="D43">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="E43" t="s">
-        <v>85</v>
+        <v>272</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B44" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="C44" t="s">
-        <v>80</v>
+        <v>262</v>
       </c>
       <c r="D44">
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="E44" t="s">
-        <v>85</v>
+        <v>272</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B45" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="C45" t="s">
-        <v>80</v>
+        <v>262</v>
       </c>
       <c r="D45">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="E45" t="s">
-        <v>85</v>
+        <v>272</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B46" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="C46" t="s">
-        <v>80</v>
+        <v>262</v>
       </c>
       <c r="D46">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="E46" t="s">
-        <v>85</v>
+        <v>272</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B47" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="C47" t="s">
-        <v>80</v>
+        <v>263</v>
       </c>
       <c r="D47">
-        <v>64</v>
+        <v>4</v>
       </c>
       <c r="E47" t="s">
-        <v>85</v>
+        <v>272</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B48" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="C48" t="s">
-        <v>80</v>
+        <v>263</v>
       </c>
       <c r="D48">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="E48" t="s">
-        <v>85</v>
+        <v>272</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B49" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="C49" t="s">
-        <v>80</v>
+        <v>264</v>
       </c>
       <c r="D49">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="E49" t="s">
-        <v>85</v>
+        <v>272</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B50" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="C50" t="s">
-        <v>80</v>
+        <v>264</v>
       </c>
       <c r="D50">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="E50" t="s">
-        <v>85</v>
+        <v>272</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B51" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="C51" t="s">
-        <v>80</v>
+        <v>264</v>
       </c>
       <c r="D51">
-        <v>40</v>
+        <v>81</v>
       </c>
       <c r="E51" t="s">
-        <v>85</v>
+        <v>272</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B52" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C52" t="s">
-        <v>80</v>
+        <v>264</v>
       </c>
       <c r="D52">
-        <v>32</v>
+        <v>85</v>
       </c>
       <c r="E52" t="s">
-        <v>85</v>
+        <v>272</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B53" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="C53" t="s">
-        <v>80</v>
+        <v>264</v>
       </c>
       <c r="D53">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="E53" t="s">
-        <v>85</v>
+        <v>272</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B54" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C54" t="s">
-        <v>80</v>
+        <v>264</v>
       </c>
       <c r="D54">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="E54" t="s">
-        <v>85</v>
+        <v>272</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B55" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C55" t="s">
-        <v>80</v>
+        <v>264</v>
       </c>
       <c r="D55">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="E55" t="s">
-        <v>85</v>
+        <v>272</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B56" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C56" t="s">
-        <v>80</v>
+        <v>264</v>
       </c>
       <c r="D56">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="E56" t="s">
-        <v>85</v>
+        <v>272</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B57" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C57" t="s">
-        <v>80</v>
+        <v>264</v>
       </c>
       <c r="D57">
-        <v>32</v>
+        <v>154</v>
       </c>
       <c r="E57" t="s">
-        <v>85</v>
+        <v>272</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B58" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="C58" t="s">
-        <v>80</v>
+        <v>264</v>
       </c>
       <c r="D58">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="E58" t="s">
-        <v>85</v>
+        <v>272</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B59" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="C59" t="s">
-        <v>80</v>
+        <v>264</v>
       </c>
       <c r="D59">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="E59" t="s">
-        <v>85</v>
+        <v>272</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B60" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="C60" t="s">
-        <v>80</v>
+        <v>264</v>
       </c>
       <c r="D60">
-        <v>32</v>
+        <v>73</v>
       </c>
       <c r="E60" t="s">
-        <v>85</v>
+        <v>272</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B61" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C61" t="s">
-        <v>80</v>
+        <v>264</v>
       </c>
       <c r="D61">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="E61" t="s">
-        <v>85</v>
+        <v>272</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B62" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C62" t="s">
-        <v>80</v>
+        <v>264</v>
       </c>
       <c r="D62">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="E62" t="s">
-        <v>85</v>
+        <v>272</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B63" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="C63" t="s">
-        <v>80</v>
+        <v>264</v>
       </c>
       <c r="D63">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="E63" t="s">
-        <v>85</v>
+        <v>272</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B64" t="s">
-        <v>24</v>
+        <v>82</v>
       </c>
       <c r="C64" t="s">
-        <v>80</v>
+        <v>264</v>
       </c>
       <c r="D64">
-        <v>40</v>
+        <v>73</v>
       </c>
       <c r="E64" t="s">
-        <v>85</v>
+        <v>272</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B65" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="C65" t="s">
-        <v>80</v>
+        <v>264</v>
       </c>
       <c r="D65">
-        <v>32</v>
+        <v>73</v>
       </c>
       <c r="E65" t="s">
-        <v>85</v>
+        <v>272</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B66" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="C66" t="s">
-        <v>80</v>
+        <v>264</v>
       </c>
       <c r="D66">
-        <v>32</v>
+        <v>73</v>
       </c>
       <c r="E66" t="s">
-        <v>85</v>
+        <v>272</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B67" t="s">
-        <v>16</v>
+        <v>85</v>
       </c>
       <c r="C67" t="s">
-        <v>84</v>
+        <v>264</v>
       </c>
       <c r="D67">
-        <v>73</v>
+        <v>4</v>
       </c>
       <c r="E67" t="s">
-        <v>85</v>
+        <v>272</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" t="s">
+        <v>7</v>
+      </c>
+      <c r="B68" t="s">
+        <v>86</v>
+      </c>
+      <c r="C68" t="s">
+        <v>264</v>
+      </c>
+      <c r="D68">
+        <v>8</v>
+      </c>
+      <c r="E68" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" t="s">
+        <v>7</v>
+      </c>
+      <c r="B69" t="s">
+        <v>87</v>
+      </c>
+      <c r="C69" t="s">
+        <v>264</v>
+      </c>
+      <c r="D69">
+        <v>8</v>
+      </c>
+      <c r="E69" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" t="s">
+        <v>7</v>
+      </c>
+      <c r="B70" t="s">
+        <v>88</v>
+      </c>
+      <c r="C70" t="s">
+        <v>264</v>
+      </c>
+      <c r="D70">
+        <v>73</v>
+      </c>
+      <c r="E70" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" t="s">
+        <v>7</v>
+      </c>
+      <c r="B71" t="s">
+        <v>89</v>
+      </c>
+      <c r="C71" t="s">
+        <v>264</v>
+      </c>
+      <c r="D71">
+        <v>150</v>
+      </c>
+      <c r="E71" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" t="s">
+        <v>8</v>
+      </c>
+      <c r="B72" t="s">
+        <v>90</v>
+      </c>
+      <c r="C72" t="s">
+        <v>265</v>
+      </c>
+      <c r="D72">
+        <v>32</v>
+      </c>
+      <c r="E72" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" t="s">
+        <v>9</v>
+      </c>
+      <c r="B73" t="s">
+        <v>66</v>
+      </c>
+      <c r="C73" t="s">
+        <v>266</v>
+      </c>
+      <c r="D73">
+        <v>8</v>
+      </c>
+      <c r="E73" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" t="s">
+        <v>10</v>
+      </c>
+      <c r="B74" t="s">
+        <v>66</v>
+      </c>
+      <c r="C74" t="s">
+        <v>265</v>
+      </c>
+      <c r="D74">
+        <v>40</v>
+      </c>
+      <c r="E74" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" t="s">
+        <v>11</v>
+      </c>
+      <c r="B75" t="s">
+        <v>91</v>
+      </c>
+      <c r="C75" t="s">
+        <v>265</v>
+      </c>
+      <c r="D75">
+        <v>1</v>
+      </c>
+      <c r="E75" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" t="s">
+        <v>12</v>
+      </c>
+      <c r="B76" t="s">
+        <v>92</v>
+      </c>
+      <c r="C76" t="s">
+        <v>267</v>
+      </c>
+      <c r="D76">
+        <v>128</v>
+      </c>
+      <c r="E76" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" t="s">
+        <v>12</v>
+      </c>
+      <c r="B77" t="s">
+        <v>93</v>
+      </c>
+      <c r="C77" t="s">
+        <v>267</v>
+      </c>
+      <c r="D77">
+        <v>32</v>
+      </c>
+      <c r="E77" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" t="s">
+        <v>12</v>
+      </c>
+      <c r="B78" t="s">
+        <v>94</v>
+      </c>
+      <c r="C78" t="s">
+        <v>267</v>
+      </c>
+      <c r="D78">
+        <v>40</v>
+      </c>
+      <c r="E78" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" t="s">
+        <v>12</v>
+      </c>
+      <c r="B79" t="s">
+        <v>62</v>
+      </c>
+      <c r="C79" t="s">
+        <v>267</v>
+      </c>
+      <c r="D79">
+        <v>40</v>
+      </c>
+      <c r="E79" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" t="s">
+        <v>12</v>
+      </c>
+      <c r="B80" t="s">
+        <v>95</v>
+      </c>
+      <c r="C80" t="s">
+        <v>267</v>
+      </c>
+      <c r="D80">
+        <v>64</v>
+      </c>
+      <c r="E80" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" t="s">
+        <v>12</v>
+      </c>
+      <c r="B81" t="s">
+        <v>96</v>
+      </c>
+      <c r="C81" t="s">
+        <v>267</v>
+      </c>
+      <c r="D81">
+        <v>64</v>
+      </c>
+      <c r="E81" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" t="s">
+        <v>13</v>
+      </c>
+      <c r="B82" t="s">
+        <v>97</v>
+      </c>
+      <c r="C82" t="s">
+        <v>268</v>
+      </c>
+      <c r="D82">
+        <v>32</v>
+      </c>
+      <c r="E82" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="A83" t="s">
+        <v>13</v>
+      </c>
+      <c r="B83" t="s">
+        <v>98</v>
+      </c>
+      <c r="C83" t="s">
+        <v>268</v>
+      </c>
+      <c r="D83">
+        <v>40</v>
+      </c>
+      <c r="E83" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5">
+      <c r="A84" t="s">
+        <v>13</v>
+      </c>
+      <c r="B84" t="s">
+        <v>99</v>
+      </c>
+      <c r="C84" t="s">
+        <v>268</v>
+      </c>
+      <c r="D84">
+        <v>40</v>
+      </c>
+      <c r="E84" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5">
+      <c r="A85" t="s">
         <v>14</v>
       </c>
-      <c r="B68" t="s">
-        <v>78</v>
-      </c>
-      <c r="C68" t="s">
-        <v>84</v>
-      </c>
-      <c r="D68">
+      <c r="B85" t="s">
+        <v>100</v>
+      </c>
+      <c r="C85" t="s">
+        <v>269</v>
+      </c>
+      <c r="D85">
+        <v>20</v>
+      </c>
+      <c r="E85" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5">
+      <c r="A86" t="s">
+        <v>14</v>
+      </c>
+      <c r="B86" t="s">
+        <v>101</v>
+      </c>
+      <c r="C86" t="s">
+        <v>269</v>
+      </c>
+      <c r="D86">
+        <v>32</v>
+      </c>
+      <c r="E86" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5">
+      <c r="A87" t="s">
+        <v>14</v>
+      </c>
+      <c r="B87" t="s">
+        <v>102</v>
+      </c>
+      <c r="C87" t="s">
+        <v>269</v>
+      </c>
+      <c r="D87">
+        <v>64</v>
+      </c>
+      <c r="E87" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5">
+      <c r="A88" t="s">
+        <v>15</v>
+      </c>
+      <c r="B88" t="s">
+        <v>103</v>
+      </c>
+      <c r="C88" t="s">
+        <v>270</v>
+      </c>
+      <c r="D88">
+        <v>2</v>
+      </c>
+      <c r="E88" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5">
+      <c r="A89" t="s">
+        <v>15</v>
+      </c>
+      <c r="B89" t="s">
+        <v>104</v>
+      </c>
+      <c r="C89" t="s">
+        <v>270</v>
+      </c>
+      <c r="D89">
+        <v>2</v>
+      </c>
+      <c r="E89" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5">
+      <c r="A90" t="s">
+        <v>15</v>
+      </c>
+      <c r="B90" t="s">
+        <v>105</v>
+      </c>
+      <c r="C90" t="s">
+        <v>270</v>
+      </c>
+      <c r="D90">
+        <v>2</v>
+      </c>
+      <c r="E90" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5">
+      <c r="A91" t="s">
+        <v>15</v>
+      </c>
+      <c r="B91" t="s">
+        <v>106</v>
+      </c>
+      <c r="C91" t="s">
+        <v>270</v>
+      </c>
+      <c r="D91">
+        <v>6</v>
+      </c>
+      <c r="E91" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5">
+      <c r="A92" t="s">
+        <v>15</v>
+      </c>
+      <c r="B92" t="s">
+        <v>107</v>
+      </c>
+      <c r="C92" t="s">
+        <v>270</v>
+      </c>
+      <c r="D92">
+        <v>2</v>
+      </c>
+      <c r="E92" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5">
+      <c r="A93" t="s">
+        <v>15</v>
+      </c>
+      <c r="B93" t="s">
+        <v>108</v>
+      </c>
+      <c r="C93" t="s">
+        <v>270</v>
+      </c>
+      <c r="D93">
+        <v>9</v>
+      </c>
+      <c r="E93" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5">
+      <c r="A94" t="s">
+        <v>15</v>
+      </c>
+      <c r="B94" t="s">
+        <v>109</v>
+      </c>
+      <c r="C94" t="s">
+        <v>270</v>
+      </c>
+      <c r="D94">
+        <v>8</v>
+      </c>
+      <c r="E94" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5">
+      <c r="A95" t="s">
+        <v>15</v>
+      </c>
+      <c r="B95" t="s">
+        <v>110</v>
+      </c>
+      <c r="C95" t="s">
+        <v>270</v>
+      </c>
+      <c r="D95">
+        <v>8</v>
+      </c>
+      <c r="E95" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5">
+      <c r="A96" t="s">
+        <v>15</v>
+      </c>
+      <c r="B96" t="s">
+        <v>111</v>
+      </c>
+      <c r="C96" t="s">
+        <v>270</v>
+      </c>
+      <c r="D96">
+        <v>2</v>
+      </c>
+      <c r="E96" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5">
+      <c r="A97" t="s">
+        <v>15</v>
+      </c>
+      <c r="B97" t="s">
+        <v>112</v>
+      </c>
+      <c r="C97" t="s">
+        <v>270</v>
+      </c>
+      <c r="D97">
+        <v>2</v>
+      </c>
+      <c r="E97" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5">
+      <c r="A98" t="s">
+        <v>15</v>
+      </c>
+      <c r="B98" t="s">
+        <v>113</v>
+      </c>
+      <c r="C98" t="s">
+        <v>270</v>
+      </c>
+      <c r="D98">
+        <v>2</v>
+      </c>
+      <c r="E98" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5">
+      <c r="A99" t="s">
+        <v>15</v>
+      </c>
+      <c r="B99" t="s">
+        <v>114</v>
+      </c>
+      <c r="C99" t="s">
+        <v>270</v>
+      </c>
+      <c r="D99">
+        <v>2</v>
+      </c>
+      <c r="E99" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5">
+      <c r="A100" t="s">
+        <v>15</v>
+      </c>
+      <c r="B100" t="s">
+        <v>115</v>
+      </c>
+      <c r="C100" t="s">
+        <v>270</v>
+      </c>
+      <c r="D100">
+        <v>1</v>
+      </c>
+      <c r="E100" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5">
+      <c r="A101" t="s">
+        <v>15</v>
+      </c>
+      <c r="B101" t="s">
+        <v>116</v>
+      </c>
+      <c r="C101" t="s">
+        <v>270</v>
+      </c>
+      <c r="D101">
+        <v>1</v>
+      </c>
+      <c r="E101" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5">
+      <c r="A102" t="s">
+        <v>15</v>
+      </c>
+      <c r="B102" t="s">
+        <v>117</v>
+      </c>
+      <c r="C102" t="s">
+        <v>270</v>
+      </c>
+      <c r="D102">
+        <v>1</v>
+      </c>
+      <c r="E102" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5">
+      <c r="A103" t="s">
+        <v>15</v>
+      </c>
+      <c r="B103" t="s">
+        <v>118</v>
+      </c>
+      <c r="C103" t="s">
+        <v>270</v>
+      </c>
+      <c r="D103">
+        <v>2</v>
+      </c>
+      <c r="E103" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5">
+      <c r="A104" t="s">
+        <v>15</v>
+      </c>
+      <c r="B104" t="s">
+        <v>119</v>
+      </c>
+      <c r="C104" t="s">
+        <v>270</v>
+      </c>
+      <c r="D104">
+        <v>6</v>
+      </c>
+      <c r="E104" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5">
+      <c r="A105" t="s">
+        <v>15</v>
+      </c>
+      <c r="B105" t="s">
+        <v>120</v>
+      </c>
+      <c r="C105" t="s">
+        <v>270</v>
+      </c>
+      <c r="D105">
+        <v>2</v>
+      </c>
+      <c r="E105" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5">
+      <c r="A106" t="s">
+        <v>15</v>
+      </c>
+      <c r="B106" t="s">
+        <v>121</v>
+      </c>
+      <c r="C106" t="s">
+        <v>270</v>
+      </c>
+      <c r="D106">
+        <v>1</v>
+      </c>
+      <c r="E106" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5">
+      <c r="A107" t="s">
+        <v>15</v>
+      </c>
+      <c r="B107" t="s">
+        <v>122</v>
+      </c>
+      <c r="C107" t="s">
+        <v>270</v>
+      </c>
+      <c r="D107">
+        <v>1</v>
+      </c>
+      <c r="E107" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5">
+      <c r="A108" t="s">
+        <v>15</v>
+      </c>
+      <c r="B108" t="s">
+        <v>123</v>
+      </c>
+      <c r="C108" t="s">
+        <v>270</v>
+      </c>
+      <c r="D108">
+        <v>1</v>
+      </c>
+      <c r="E108" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5">
+      <c r="A109" t="s">
+        <v>15</v>
+      </c>
+      <c r="B109" t="s">
+        <v>124</v>
+      </c>
+      <c r="C109" t="s">
+        <v>270</v>
+      </c>
+      <c r="D109">
+        <v>1</v>
+      </c>
+      <c r="E109" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5">
+      <c r="A110" t="s">
+        <v>15</v>
+      </c>
+      <c r="B110" t="s">
+        <v>125</v>
+      </c>
+      <c r="C110" t="s">
+        <v>270</v>
+      </c>
+      <c r="D110">
+        <v>1</v>
+      </c>
+      <c r="E110" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5">
+      <c r="A111" t="s">
+        <v>15</v>
+      </c>
+      <c r="B111" t="s">
+        <v>126</v>
+      </c>
+      <c r="C111" t="s">
+        <v>270</v>
+      </c>
+      <c r="D111">
+        <v>18</v>
+      </c>
+      <c r="E111" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5">
+      <c r="A112" t="s">
+        <v>15</v>
+      </c>
+      <c r="B112" t="s">
+        <v>127</v>
+      </c>
+      <c r="C112" t="s">
+        <v>270</v>
+      </c>
+      <c r="D112">
+        <v>6</v>
+      </c>
+      <c r="E112" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5">
+      <c r="A113" t="s">
+        <v>15</v>
+      </c>
+      <c r="B113" t="s">
+        <v>128</v>
+      </c>
+      <c r="C113" t="s">
+        <v>270</v>
+      </c>
+      <c r="D113">
+        <v>2</v>
+      </c>
+      <c r="E113" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5">
+      <c r="A114" t="s">
+        <v>15</v>
+      </c>
+      <c r="B114" t="s">
+        <v>129</v>
+      </c>
+      <c r="C114" t="s">
+        <v>270</v>
+      </c>
+      <c r="D114">
+        <v>2</v>
+      </c>
+      <c r="E114" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5">
+      <c r="A115" t="s">
+        <v>15</v>
+      </c>
+      <c r="B115" t="s">
+        <v>130</v>
+      </c>
+      <c r="C115" t="s">
+        <v>270</v>
+      </c>
+      <c r="D115">
+        <v>2</v>
+      </c>
+      <c r="E115" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5">
+      <c r="A116" t="s">
+        <v>15</v>
+      </c>
+      <c r="B116" t="s">
+        <v>131</v>
+      </c>
+      <c r="C116" t="s">
+        <v>270</v>
+      </c>
+      <c r="D116">
+        <v>6</v>
+      </c>
+      <c r="E116" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5">
+      <c r="A117" t="s">
+        <v>15</v>
+      </c>
+      <c r="B117" t="s">
+        <v>132</v>
+      </c>
+      <c r="C117" t="s">
+        <v>270</v>
+      </c>
+      <c r="D117">
+        <v>6</v>
+      </c>
+      <c r="E117" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5">
+      <c r="A118" t="s">
+        <v>15</v>
+      </c>
+      <c r="B118" t="s">
+        <v>133</v>
+      </c>
+      <c r="C118" t="s">
+        <v>270</v>
+      </c>
+      <c r="D118">
+        <v>2</v>
+      </c>
+      <c r="E118" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5">
+      <c r="A119" t="s">
+        <v>15</v>
+      </c>
+      <c r="B119" t="s">
+        <v>134</v>
+      </c>
+      <c r="C119" t="s">
+        <v>270</v>
+      </c>
+      <c r="D119">
+        <v>156</v>
+      </c>
+      <c r="E119" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5">
+      <c r="A120" t="s">
+        <v>15</v>
+      </c>
+      <c r="B120" t="s">
+        <v>135</v>
+      </c>
+      <c r="C120" t="s">
+        <v>270</v>
+      </c>
+      <c r="D120">
+        <v>52</v>
+      </c>
+      <c r="E120" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5">
+      <c r="A121" t="s">
+        <v>15</v>
+      </c>
+      <c r="B121" t="s">
+        <v>136</v>
+      </c>
+      <c r="C121" t="s">
+        <v>270</v>
+      </c>
+      <c r="D121">
+        <v>24</v>
+      </c>
+      <c r="E121" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5">
+      <c r="A122" t="s">
+        <v>15</v>
+      </c>
+      <c r="B122" t="s">
+        <v>137</v>
+      </c>
+      <c r="C122" t="s">
+        <v>270</v>
+      </c>
+      <c r="D122">
+        <v>8</v>
+      </c>
+      <c r="E122" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5">
+      <c r="A123" t="s">
+        <v>15</v>
+      </c>
+      <c r="B123" t="s">
+        <v>138</v>
+      </c>
+      <c r="C123" t="s">
+        <v>270</v>
+      </c>
+      <c r="D123">
+        <v>16</v>
+      </c>
+      <c r="E123" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5">
+      <c r="A124" t="s">
+        <v>15</v>
+      </c>
+      <c r="B124" t="s">
+        <v>139</v>
+      </c>
+      <c r="C124" t="s">
+        <v>270</v>
+      </c>
+      <c r="D124">
+        <v>16</v>
+      </c>
+      <c r="E124" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5">
+      <c r="A125" t="s">
+        <v>15</v>
+      </c>
+      <c r="B125" t="s">
+        <v>140</v>
+      </c>
+      <c r="C125" t="s">
+        <v>270</v>
+      </c>
+      <c r="D125">
+        <v>6</v>
+      </c>
+      <c r="E125" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5">
+      <c r="A126" t="s">
+        <v>15</v>
+      </c>
+      <c r="B126" t="s">
+        <v>141</v>
+      </c>
+      <c r="C126" t="s">
+        <v>270</v>
+      </c>
+      <c r="D126">
+        <v>6</v>
+      </c>
+      <c r="E126" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5">
+      <c r="A127" t="s">
+        <v>15</v>
+      </c>
+      <c r="B127" t="s">
+        <v>142</v>
+      </c>
+      <c r="C127" t="s">
+        <v>270</v>
+      </c>
+      <c r="D127">
+        <v>16</v>
+      </c>
+      <c r="E127" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5">
+      <c r="A128" t="s">
+        <v>15</v>
+      </c>
+      <c r="B128" t="s">
+        <v>143</v>
+      </c>
+      <c r="C128" t="s">
+        <v>270</v>
+      </c>
+      <c r="D128">
+        <v>16</v>
+      </c>
+      <c r="E128" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5">
+      <c r="A129" t="s">
+        <v>15</v>
+      </c>
+      <c r="B129" t="s">
+        <v>144</v>
+      </c>
+      <c r="C129" t="s">
+        <v>270</v>
+      </c>
+      <c r="D129">
+        <v>2</v>
+      </c>
+      <c r="E129" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5">
+      <c r="A130" t="s">
+        <v>15</v>
+      </c>
+      <c r="B130" t="s">
+        <v>145</v>
+      </c>
+      <c r="C130" t="s">
+        <v>270</v>
+      </c>
+      <c r="D130">
+        <v>2</v>
+      </c>
+      <c r="E130" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5">
+      <c r="A131" t="s">
+        <v>15</v>
+      </c>
+      <c r="B131" t="s">
+        <v>146</v>
+      </c>
+      <c r="C131" t="s">
+        <v>270</v>
+      </c>
+      <c r="D131">
+        <v>6</v>
+      </c>
+      <c r="E131" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5">
+      <c r="A132" t="s">
+        <v>15</v>
+      </c>
+      <c r="B132" t="s">
+        <v>147</v>
+      </c>
+      <c r="C132" t="s">
+        <v>270</v>
+      </c>
+      <c r="D132">
+        <v>10</v>
+      </c>
+      <c r="E132" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5">
+      <c r="A133" t="s">
+        <v>15</v>
+      </c>
+      <c r="B133" t="s">
+        <v>148</v>
+      </c>
+      <c r="C133" t="s">
+        <v>270</v>
+      </c>
+      <c r="D133">
+        <v>8</v>
+      </c>
+      <c r="E133" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5">
+      <c r="A134" t="s">
+        <v>15</v>
+      </c>
+      <c r="B134" t="s">
+        <v>149</v>
+      </c>
+      <c r="C134" t="s">
+        <v>270</v>
+      </c>
+      <c r="D134">
+        <v>6</v>
+      </c>
+      <c r="E134" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5">
+      <c r="A135" t="s">
+        <v>15</v>
+      </c>
+      <c r="B135" t="s">
+        <v>150</v>
+      </c>
+      <c r="C135" t="s">
+        <v>270</v>
+      </c>
+      <c r="D135">
+        <v>6</v>
+      </c>
+      <c r="E135" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5">
+      <c r="A136" t="s">
+        <v>15</v>
+      </c>
+      <c r="B136" t="s">
+        <v>151</v>
+      </c>
+      <c r="C136" t="s">
+        <v>270</v>
+      </c>
+      <c r="D136">
+        <v>2</v>
+      </c>
+      <c r="E136" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5">
+      <c r="A137" t="s">
+        <v>15</v>
+      </c>
+      <c r="B137" t="s">
+        <v>152</v>
+      </c>
+      <c r="C137" t="s">
+        <v>270</v>
+      </c>
+      <c r="D137">
         <v>4</v>
       </c>
-      <c r="E68" t="s">
-        <v>85</v>
+      <c r="E137" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5">
+      <c r="A138" t="s">
+        <v>15</v>
+      </c>
+      <c r="B138" t="s">
+        <v>153</v>
+      </c>
+      <c r="C138" t="s">
+        <v>270</v>
+      </c>
+      <c r="D138">
+        <v>6</v>
+      </c>
+      <c r="E138" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5">
+      <c r="A139" t="s">
+        <v>15</v>
+      </c>
+      <c r="B139" t="s">
+        <v>154</v>
+      </c>
+      <c r="C139" t="s">
+        <v>270</v>
+      </c>
+      <c r="D139">
+        <v>6</v>
+      </c>
+      <c r="E139" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5">
+      <c r="A140" t="s">
+        <v>15</v>
+      </c>
+      <c r="B140" t="s">
+        <v>155</v>
+      </c>
+      <c r="C140" t="s">
+        <v>270</v>
+      </c>
+      <c r="D140">
+        <v>2</v>
+      </c>
+      <c r="E140" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5">
+      <c r="A141" t="s">
+        <v>15</v>
+      </c>
+      <c r="B141" t="s">
+        <v>156</v>
+      </c>
+      <c r="C141" t="s">
+        <v>270</v>
+      </c>
+      <c r="D141">
+        <v>8</v>
+      </c>
+      <c r="E141" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5">
+      <c r="A142" t="s">
+        <v>15</v>
+      </c>
+      <c r="B142" t="s">
+        <v>157</v>
+      </c>
+      <c r="C142" t="s">
+        <v>270</v>
+      </c>
+      <c r="D142">
+        <v>8</v>
+      </c>
+      <c r="E142" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5">
+      <c r="A143" t="s">
+        <v>15</v>
+      </c>
+      <c r="B143" t="s">
+        <v>158</v>
+      </c>
+      <c r="C143" t="s">
+        <v>270</v>
+      </c>
+      <c r="D143">
+        <v>2</v>
+      </c>
+      <c r="E143" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5">
+      <c r="A144" t="s">
+        <v>15</v>
+      </c>
+      <c r="B144" t="s">
+        <v>159</v>
+      </c>
+      <c r="C144" t="s">
+        <v>270</v>
+      </c>
+      <c r="D144">
+        <v>4</v>
+      </c>
+      <c r="E144" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5">
+      <c r="A145" t="s">
+        <v>15</v>
+      </c>
+      <c r="B145" t="s">
+        <v>160</v>
+      </c>
+      <c r="C145" t="s">
+        <v>270</v>
+      </c>
+      <c r="D145">
+        <v>2</v>
+      </c>
+      <c r="E145" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5">
+      <c r="A146" t="s">
+        <v>15</v>
+      </c>
+      <c r="B146" t="s">
+        <v>161</v>
+      </c>
+      <c r="C146" t="s">
+        <v>270</v>
+      </c>
+      <c r="D146">
+        <v>6</v>
+      </c>
+      <c r="E146" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5">
+      <c r="A147" t="s">
+        <v>15</v>
+      </c>
+      <c r="B147" t="s">
+        <v>162</v>
+      </c>
+      <c r="C147" t="s">
+        <v>270</v>
+      </c>
+      <c r="D147">
+        <v>6</v>
+      </c>
+      <c r="E147" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5">
+      <c r="A148" t="s">
+        <v>15</v>
+      </c>
+      <c r="B148" t="s">
+        <v>163</v>
+      </c>
+      <c r="C148" t="s">
+        <v>270</v>
+      </c>
+      <c r="D148">
+        <v>10</v>
+      </c>
+      <c r="E148" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5">
+      <c r="A149" t="s">
+        <v>15</v>
+      </c>
+      <c r="B149" t="s">
+        <v>164</v>
+      </c>
+      <c r="C149" t="s">
+        <v>270</v>
+      </c>
+      <c r="D149">
+        <v>6</v>
+      </c>
+      <c r="E149" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5">
+      <c r="A150" t="s">
+        <v>15</v>
+      </c>
+      <c r="B150" t="s">
+        <v>165</v>
+      </c>
+      <c r="C150" t="s">
+        <v>270</v>
+      </c>
+      <c r="D150">
+        <v>2</v>
+      </c>
+      <c r="E150" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5">
+      <c r="A151" t="s">
+        <v>15</v>
+      </c>
+      <c r="B151" t="s">
+        <v>166</v>
+      </c>
+      <c r="C151" t="s">
+        <v>270</v>
+      </c>
+      <c r="D151">
+        <v>6</v>
+      </c>
+      <c r="E151" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5">
+      <c r="A152" t="s">
+        <v>15</v>
+      </c>
+      <c r="B152" t="s">
+        <v>167</v>
+      </c>
+      <c r="C152" t="s">
+        <v>270</v>
+      </c>
+      <c r="D152">
+        <v>2</v>
+      </c>
+      <c r="E152" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5">
+      <c r="A153" t="s">
+        <v>15</v>
+      </c>
+      <c r="B153" t="s">
+        <v>168</v>
+      </c>
+      <c r="C153" t="s">
+        <v>270</v>
+      </c>
+      <c r="D153">
+        <v>6</v>
+      </c>
+      <c r="E153" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5">
+      <c r="A154" t="s">
+        <v>15</v>
+      </c>
+      <c r="B154" t="s">
+        <v>169</v>
+      </c>
+      <c r="C154" t="s">
+        <v>270</v>
+      </c>
+      <c r="D154">
+        <v>2</v>
+      </c>
+      <c r="E154" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5">
+      <c r="A155" t="s">
+        <v>15</v>
+      </c>
+      <c r="B155" t="s">
+        <v>170</v>
+      </c>
+      <c r="C155" t="s">
+        <v>270</v>
+      </c>
+      <c r="D155">
+        <v>9</v>
+      </c>
+      <c r="E155" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5">
+      <c r="A156" t="s">
+        <v>15</v>
+      </c>
+      <c r="B156" t="s">
+        <v>171</v>
+      </c>
+      <c r="C156" t="s">
+        <v>270</v>
+      </c>
+      <c r="D156">
+        <v>2</v>
+      </c>
+      <c r="E156" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5">
+      <c r="A157" t="s">
+        <v>15</v>
+      </c>
+      <c r="B157" t="s">
+        <v>172</v>
+      </c>
+      <c r="C157" t="s">
+        <v>270</v>
+      </c>
+      <c r="D157">
+        <v>7</v>
+      </c>
+      <c r="E157" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5">
+      <c r="A158" t="s">
+        <v>15</v>
+      </c>
+      <c r="B158" t="s">
+        <v>173</v>
+      </c>
+      <c r="C158" t="s">
+        <v>270</v>
+      </c>
+      <c r="D158">
+        <v>2</v>
+      </c>
+      <c r="E158" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5">
+      <c r="A159" t="s">
+        <v>15</v>
+      </c>
+      <c r="B159" t="s">
+        <v>174</v>
+      </c>
+      <c r="C159" t="s">
+        <v>270</v>
+      </c>
+      <c r="D159">
+        <v>3</v>
+      </c>
+      <c r="E159" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5">
+      <c r="A160" t="s">
+        <v>15</v>
+      </c>
+      <c r="B160" t="s">
+        <v>175</v>
+      </c>
+      <c r="C160" t="s">
+        <v>270</v>
+      </c>
+      <c r="D160">
+        <v>3</v>
+      </c>
+      <c r="E160" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5">
+      <c r="A161" t="s">
+        <v>15</v>
+      </c>
+      <c r="B161" t="s">
+        <v>176</v>
+      </c>
+      <c r="C161" t="s">
+        <v>270</v>
+      </c>
+      <c r="D161">
+        <v>6</v>
+      </c>
+      <c r="E161" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5">
+      <c r="A162" t="s">
+        <v>15</v>
+      </c>
+      <c r="B162" t="s">
+        <v>177</v>
+      </c>
+      <c r="C162" t="s">
+        <v>270</v>
+      </c>
+      <c r="D162">
+        <v>2</v>
+      </c>
+      <c r="E162" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5">
+      <c r="A163" t="s">
+        <v>15</v>
+      </c>
+      <c r="B163" t="s">
+        <v>178</v>
+      </c>
+      <c r="C163" t="s">
+        <v>270</v>
+      </c>
+      <c r="D163">
+        <v>6</v>
+      </c>
+      <c r="E163" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5">
+      <c r="A164" t="s">
+        <v>15</v>
+      </c>
+      <c r="B164" t="s">
+        <v>179</v>
+      </c>
+      <c r="C164" t="s">
+        <v>270</v>
+      </c>
+      <c r="D164">
+        <v>2</v>
+      </c>
+      <c r="E164" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5">
+      <c r="A165" t="s">
+        <v>15</v>
+      </c>
+      <c r="B165" t="s">
+        <v>180</v>
+      </c>
+      <c r="C165" t="s">
+        <v>270</v>
+      </c>
+      <c r="D165">
+        <v>6</v>
+      </c>
+      <c r="E165" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5">
+      <c r="A166" t="s">
+        <v>15</v>
+      </c>
+      <c r="B166" t="s">
+        <v>181</v>
+      </c>
+      <c r="C166" t="s">
+        <v>270</v>
+      </c>
+      <c r="D166">
+        <v>2</v>
+      </c>
+      <c r="E166" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5">
+      <c r="A167" t="s">
+        <v>15</v>
+      </c>
+      <c r="B167" t="s">
+        <v>182</v>
+      </c>
+      <c r="C167" t="s">
+        <v>270</v>
+      </c>
+      <c r="D167">
+        <v>4</v>
+      </c>
+      <c r="E167" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5">
+      <c r="A168" t="s">
+        <v>15</v>
+      </c>
+      <c r="B168" t="s">
+        <v>183</v>
+      </c>
+      <c r="C168" t="s">
+        <v>270</v>
+      </c>
+      <c r="D168">
+        <v>4</v>
+      </c>
+      <c r="E168" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5">
+      <c r="A169" t="s">
+        <v>15</v>
+      </c>
+      <c r="B169" t="s">
+        <v>184</v>
+      </c>
+      <c r="C169" t="s">
+        <v>270</v>
+      </c>
+      <c r="D169">
+        <v>8</v>
+      </c>
+      <c r="E169" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5">
+      <c r="A170" t="s">
+        <v>15</v>
+      </c>
+      <c r="B170" t="s">
+        <v>185</v>
+      </c>
+      <c r="C170" t="s">
+        <v>270</v>
+      </c>
+      <c r="D170">
+        <v>8</v>
+      </c>
+      <c r="E170" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5">
+      <c r="A171" t="s">
+        <v>15</v>
+      </c>
+      <c r="B171" t="s">
+        <v>186</v>
+      </c>
+      <c r="C171" t="s">
+        <v>270</v>
+      </c>
+      <c r="D171">
+        <v>4</v>
+      </c>
+      <c r="E171" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5">
+      <c r="A172" t="s">
+        <v>15</v>
+      </c>
+      <c r="B172" t="s">
+        <v>187</v>
+      </c>
+      <c r="C172" t="s">
+        <v>270</v>
+      </c>
+      <c r="D172">
+        <v>6</v>
+      </c>
+      <c r="E172" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5">
+      <c r="A173" t="s">
+        <v>15</v>
+      </c>
+      <c r="B173" t="s">
+        <v>188</v>
+      </c>
+      <c r="C173" t="s">
+        <v>270</v>
+      </c>
+      <c r="D173">
+        <v>6</v>
+      </c>
+      <c r="E173" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5">
+      <c r="A174" t="s">
+        <v>15</v>
+      </c>
+      <c r="B174" t="s">
+        <v>189</v>
+      </c>
+      <c r="C174" t="s">
+        <v>270</v>
+      </c>
+      <c r="D174">
+        <v>2</v>
+      </c>
+      <c r="E174" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5">
+      <c r="A175" t="s">
+        <v>15</v>
+      </c>
+      <c r="B175" t="s">
+        <v>190</v>
+      </c>
+      <c r="C175" t="s">
+        <v>270</v>
+      </c>
+      <c r="D175">
+        <v>6</v>
+      </c>
+      <c r="E175" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5">
+      <c r="A176" t="s">
+        <v>15</v>
+      </c>
+      <c r="B176" t="s">
+        <v>191</v>
+      </c>
+      <c r="C176" t="s">
+        <v>270</v>
+      </c>
+      <c r="D176">
+        <v>2</v>
+      </c>
+      <c r="E176" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5">
+      <c r="A177" t="s">
+        <v>15</v>
+      </c>
+      <c r="B177" t="s">
+        <v>192</v>
+      </c>
+      <c r="C177" t="s">
+        <v>270</v>
+      </c>
+      <c r="D177">
+        <v>6</v>
+      </c>
+      <c r="E177" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5">
+      <c r="A178" t="s">
+        <v>15</v>
+      </c>
+      <c r="B178" t="s">
+        <v>193</v>
+      </c>
+      <c r="C178" t="s">
+        <v>270</v>
+      </c>
+      <c r="D178">
+        <v>2</v>
+      </c>
+      <c r="E178" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5">
+      <c r="A179" t="s">
+        <v>15</v>
+      </c>
+      <c r="B179" t="s">
+        <v>194</v>
+      </c>
+      <c r="C179" t="s">
+        <v>270</v>
+      </c>
+      <c r="D179">
+        <v>4</v>
+      </c>
+      <c r="E179" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5">
+      <c r="A180" t="s">
+        <v>15</v>
+      </c>
+      <c r="B180" t="s">
+        <v>195</v>
+      </c>
+      <c r="C180" t="s">
+        <v>270</v>
+      </c>
+      <c r="D180">
+        <v>8</v>
+      </c>
+      <c r="E180" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5">
+      <c r="A181" t="s">
+        <v>15</v>
+      </c>
+      <c r="B181" t="s">
+        <v>196</v>
+      </c>
+      <c r="C181" t="s">
+        <v>270</v>
+      </c>
+      <c r="D181">
+        <v>8</v>
+      </c>
+      <c r="E181" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5">
+      <c r="A182" t="s">
+        <v>15</v>
+      </c>
+      <c r="B182" t="s">
+        <v>197</v>
+      </c>
+      <c r="C182" t="s">
+        <v>270</v>
+      </c>
+      <c r="D182">
+        <v>6</v>
+      </c>
+      <c r="E182" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5">
+      <c r="A183" t="s">
+        <v>15</v>
+      </c>
+      <c r="B183" t="s">
+        <v>198</v>
+      </c>
+      <c r="C183" t="s">
+        <v>270</v>
+      </c>
+      <c r="D183">
+        <v>2</v>
+      </c>
+      <c r="E183" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5">
+      <c r="A184" t="s">
+        <v>15</v>
+      </c>
+      <c r="B184" t="s">
+        <v>199</v>
+      </c>
+      <c r="C184" t="s">
+        <v>270</v>
+      </c>
+      <c r="D184">
+        <v>6</v>
+      </c>
+      <c r="E184" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5">
+      <c r="A185" t="s">
+        <v>15</v>
+      </c>
+      <c r="B185" t="s">
+        <v>200</v>
+      </c>
+      <c r="C185" t="s">
+        <v>270</v>
+      </c>
+      <c r="D185">
+        <v>2</v>
+      </c>
+      <c r="E185" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5">
+      <c r="A186" t="s">
+        <v>15</v>
+      </c>
+      <c r="B186" t="s">
+        <v>201</v>
+      </c>
+      <c r="C186" t="s">
+        <v>270</v>
+      </c>
+      <c r="D186">
+        <v>20</v>
+      </c>
+      <c r="E186" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5">
+      <c r="A187" t="s">
+        <v>15</v>
+      </c>
+      <c r="B187" t="s">
+        <v>202</v>
+      </c>
+      <c r="C187" t="s">
+        <v>270</v>
+      </c>
+      <c r="D187">
+        <v>6</v>
+      </c>
+      <c r="E187" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5">
+      <c r="A188" t="s">
+        <v>15</v>
+      </c>
+      <c r="B188" t="s">
+        <v>203</v>
+      </c>
+      <c r="C188" t="s">
+        <v>270</v>
+      </c>
+      <c r="D188">
+        <v>2</v>
+      </c>
+      <c r="E188" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5">
+      <c r="A189" t="s">
+        <v>15</v>
+      </c>
+      <c r="B189" t="s">
+        <v>204</v>
+      </c>
+      <c r="C189" t="s">
+        <v>270</v>
+      </c>
+      <c r="D189">
+        <v>4</v>
+      </c>
+      <c r="E189" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5">
+      <c r="A190" t="s">
+        <v>15</v>
+      </c>
+      <c r="B190" t="s">
+        <v>205</v>
+      </c>
+      <c r="C190" t="s">
+        <v>270</v>
+      </c>
+      <c r="D190">
+        <v>10</v>
+      </c>
+      <c r="E190" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5">
+      <c r="A191" t="s">
+        <v>15</v>
+      </c>
+      <c r="B191" t="s">
+        <v>206</v>
+      </c>
+      <c r="C191" t="s">
+        <v>270</v>
+      </c>
+      <c r="D191">
+        <v>8</v>
+      </c>
+      <c r="E191" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5">
+      <c r="A192" t="s">
+        <v>15</v>
+      </c>
+      <c r="B192" t="s">
+        <v>207</v>
+      </c>
+      <c r="C192" t="s">
+        <v>270</v>
+      </c>
+      <c r="D192">
+        <v>4</v>
+      </c>
+      <c r="E192" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="193" spans="1:5">
+      <c r="A193" t="s">
+        <v>15</v>
+      </c>
+      <c r="B193" t="s">
+        <v>208</v>
+      </c>
+      <c r="C193" t="s">
+        <v>270</v>
+      </c>
+      <c r="D193">
+        <v>4</v>
+      </c>
+      <c r="E193" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5">
+      <c r="A194" t="s">
+        <v>15</v>
+      </c>
+      <c r="B194" t="s">
+        <v>209</v>
+      </c>
+      <c r="C194" t="s">
+        <v>270</v>
+      </c>
+      <c r="D194">
+        <v>2</v>
+      </c>
+      <c r="E194" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5">
+      <c r="A195" t="s">
+        <v>15</v>
+      </c>
+      <c r="B195" t="s">
+        <v>210</v>
+      </c>
+      <c r="C195" t="s">
+        <v>270</v>
+      </c>
+      <c r="D195">
+        <v>1</v>
+      </c>
+      <c r="E195" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5">
+      <c r="A196" t="s">
+        <v>15</v>
+      </c>
+      <c r="B196" t="s">
+        <v>211</v>
+      </c>
+      <c r="C196" t="s">
+        <v>270</v>
+      </c>
+      <c r="D196">
+        <v>1</v>
+      </c>
+      <c r="E196" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5">
+      <c r="A197" t="s">
+        <v>15</v>
+      </c>
+      <c r="B197" t="s">
+        <v>212</v>
+      </c>
+      <c r="C197" t="s">
+        <v>270</v>
+      </c>
+      <c r="D197">
+        <v>18</v>
+      </c>
+      <c r="E197" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5">
+      <c r="A198" t="s">
+        <v>15</v>
+      </c>
+      <c r="B198" t="s">
+        <v>213</v>
+      </c>
+      <c r="C198" t="s">
+        <v>270</v>
+      </c>
+      <c r="D198">
+        <v>18</v>
+      </c>
+      <c r="E198" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5">
+      <c r="A199" t="s">
+        <v>15</v>
+      </c>
+      <c r="B199" t="s">
+        <v>214</v>
+      </c>
+      <c r="C199" t="s">
+        <v>270</v>
+      </c>
+      <c r="D199">
+        <v>48</v>
+      </c>
+      <c r="E199" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5">
+      <c r="A200" t="s">
+        <v>15</v>
+      </c>
+      <c r="B200" t="s">
+        <v>215</v>
+      </c>
+      <c r="C200" t="s">
+        <v>270</v>
+      </c>
+      <c r="D200">
+        <v>1</v>
+      </c>
+      <c r="E200" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5">
+      <c r="A201" t="s">
+        <v>15</v>
+      </c>
+      <c r="B201" t="s">
+        <v>216</v>
+      </c>
+      <c r="C201" t="s">
+        <v>270</v>
+      </c>
+      <c r="D201">
+        <v>1</v>
+      </c>
+      <c r="E201" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5">
+      <c r="A202" t="s">
+        <v>15</v>
+      </c>
+      <c r="B202" t="s">
+        <v>217</v>
+      </c>
+      <c r="C202" t="s">
+        <v>270</v>
+      </c>
+      <c r="D202">
+        <v>1</v>
+      </c>
+      <c r="E202" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5">
+      <c r="A203" t="s">
+        <v>15</v>
+      </c>
+      <c r="B203" t="s">
+        <v>218</v>
+      </c>
+      <c r="C203" t="s">
+        <v>270</v>
+      </c>
+      <c r="D203">
+        <v>1</v>
+      </c>
+      <c r="E203" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="204" spans="1:5">
+      <c r="A204" t="s">
+        <v>15</v>
+      </c>
+      <c r="B204" t="s">
+        <v>219</v>
+      </c>
+      <c r="C204" t="s">
+        <v>270</v>
+      </c>
+      <c r="D204">
+        <v>2</v>
+      </c>
+      <c r="E204" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5">
+      <c r="A205" t="s">
+        <v>15</v>
+      </c>
+      <c r="B205" t="s">
+        <v>220</v>
+      </c>
+      <c r="C205" t="s">
+        <v>270</v>
+      </c>
+      <c r="D205">
+        <v>1</v>
+      </c>
+      <c r="E205" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5">
+      <c r="A206" t="s">
+        <v>15</v>
+      </c>
+      <c r="B206" t="s">
+        <v>221</v>
+      </c>
+      <c r="C206" t="s">
+        <v>270</v>
+      </c>
+      <c r="D206">
+        <v>1</v>
+      </c>
+      <c r="E206" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="207" spans="1:5">
+      <c r="A207" t="s">
+        <v>15</v>
+      </c>
+      <c r="B207" t="s">
+        <v>222</v>
+      </c>
+      <c r="C207" t="s">
+        <v>270</v>
+      </c>
+      <c r="D207">
+        <v>12</v>
+      </c>
+      <c r="E207" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5">
+      <c r="A208" t="s">
+        <v>15</v>
+      </c>
+      <c r="B208" t="s">
+        <v>223</v>
+      </c>
+      <c r="C208" t="s">
+        <v>270</v>
+      </c>
+      <c r="D208">
+        <v>1</v>
+      </c>
+      <c r="E208" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="209" spans="1:5">
+      <c r="A209" t="s">
+        <v>15</v>
+      </c>
+      <c r="B209" t="s">
+        <v>224</v>
+      </c>
+      <c r="C209" t="s">
+        <v>270</v>
+      </c>
+      <c r="D209">
+        <v>3</v>
+      </c>
+      <c r="E209" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="210" spans="1:5">
+      <c r="A210" t="s">
+        <v>15</v>
+      </c>
+      <c r="B210" t="s">
+        <v>225</v>
+      </c>
+      <c r="C210" t="s">
+        <v>270</v>
+      </c>
+      <c r="D210">
+        <v>2</v>
+      </c>
+      <c r="E210" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="211" spans="1:5">
+      <c r="A211" t="s">
+        <v>15</v>
+      </c>
+      <c r="B211" t="s">
+        <v>226</v>
+      </c>
+      <c r="C211" t="s">
+        <v>270</v>
+      </c>
+      <c r="D211">
+        <v>1</v>
+      </c>
+      <c r="E211" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="212" spans="1:5">
+      <c r="A212" t="s">
+        <v>15</v>
+      </c>
+      <c r="B212" t="s">
+        <v>227</v>
+      </c>
+      <c r="C212" t="s">
+        <v>270</v>
+      </c>
+      <c r="D212">
+        <v>1</v>
+      </c>
+      <c r="E212" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="213" spans="1:5">
+      <c r="A213" t="s">
+        <v>15</v>
+      </c>
+      <c r="B213" t="s">
+        <v>228</v>
+      </c>
+      <c r="C213" t="s">
+        <v>270</v>
+      </c>
+      <c r="D213">
+        <v>1</v>
+      </c>
+      <c r="E213" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="214" spans="1:5">
+      <c r="A214" t="s">
+        <v>15</v>
+      </c>
+      <c r="B214" t="s">
+        <v>229</v>
+      </c>
+      <c r="C214" t="s">
+        <v>270</v>
+      </c>
+      <c r="D214">
+        <v>1</v>
+      </c>
+      <c r="E214" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="215" spans="1:5">
+      <c r="A215" t="s">
+        <v>16</v>
+      </c>
+      <c r="B215" t="s">
+        <v>230</v>
+      </c>
+      <c r="C215" t="s">
+        <v>262</v>
+      </c>
+      <c r="D215">
+        <v>16</v>
+      </c>
+      <c r="E215" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="216" spans="1:5">
+      <c r="A216" t="s">
+        <v>16</v>
+      </c>
+      <c r="B216" t="s">
+        <v>231</v>
+      </c>
+      <c r="C216" t="s">
+        <v>262</v>
+      </c>
+      <c r="D216">
+        <v>8</v>
+      </c>
+      <c r="E216" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="217" spans="1:5">
+      <c r="A217" t="s">
+        <v>16</v>
+      </c>
+      <c r="B217" t="s">
+        <v>103</v>
+      </c>
+      <c r="C217" t="s">
+        <v>262</v>
+      </c>
+      <c r="D217">
+        <v>16</v>
+      </c>
+      <c r="E217" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="218" spans="1:5">
+      <c r="A218" t="s">
+        <v>16</v>
+      </c>
+      <c r="B218" t="s">
+        <v>104</v>
+      </c>
+      <c r="C218" t="s">
+        <v>262</v>
+      </c>
+      <c r="D218">
+        <v>16</v>
+      </c>
+      <c r="E218" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="219" spans="1:5">
+      <c r="A219" t="s">
+        <v>16</v>
+      </c>
+      <c r="B219" t="s">
+        <v>232</v>
+      </c>
+      <c r="C219" t="s">
+        <v>262</v>
+      </c>
+      <c r="D219">
+        <v>14</v>
+      </c>
+      <c r="E219" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="220" spans="1:5">
+      <c r="A220" t="s">
+        <v>16</v>
+      </c>
+      <c r="B220" t="s">
+        <v>106</v>
+      </c>
+      <c r="C220" t="s">
+        <v>262</v>
+      </c>
+      <c r="D220">
+        <v>16</v>
+      </c>
+      <c r="E220" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="221" spans="1:5">
+      <c r="A221" t="s">
+        <v>16</v>
+      </c>
+      <c r="B221" t="s">
+        <v>107</v>
+      </c>
+      <c r="C221" t="s">
+        <v>262</v>
+      </c>
+      <c r="D221">
+        <v>8</v>
+      </c>
+      <c r="E221" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="222" spans="1:5">
+      <c r="A222" t="s">
+        <v>16</v>
+      </c>
+      <c r="B222" t="s">
+        <v>108</v>
+      </c>
+      <c r="C222" t="s">
+        <v>262</v>
+      </c>
+      <c r="D222">
+        <v>45</v>
+      </c>
+      <c r="E222" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="223" spans="1:5">
+      <c r="A223" t="s">
+        <v>16</v>
+      </c>
+      <c r="B223" t="s">
+        <v>233</v>
+      </c>
+      <c r="C223" t="s">
+        <v>262</v>
+      </c>
+      <c r="D223">
+        <v>16</v>
+      </c>
+      <c r="E223" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="224" spans="1:5">
+      <c r="A224" t="s">
+        <v>16</v>
+      </c>
+      <c r="B224" t="s">
+        <v>234</v>
+      </c>
+      <c r="C224" t="s">
+        <v>262</v>
+      </c>
+      <c r="D224">
+        <v>8</v>
+      </c>
+      <c r="E224" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="225" spans="1:5">
+      <c r="A225" t="s">
+        <v>16</v>
+      </c>
+      <c r="B225" t="s">
+        <v>109</v>
+      </c>
+      <c r="C225" t="s">
+        <v>262</v>
+      </c>
+      <c r="D225">
+        <v>24</v>
+      </c>
+      <c r="E225" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="226" spans="1:5">
+      <c r="A226" t="s">
+        <v>16</v>
+      </c>
+      <c r="B226" t="s">
+        <v>110</v>
+      </c>
+      <c r="C226" t="s">
+        <v>262</v>
+      </c>
+      <c r="D226">
+        <v>24</v>
+      </c>
+      <c r="E226" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="227" spans="1:5">
+      <c r="A227" t="s">
+        <v>16</v>
+      </c>
+      <c r="B227" t="s">
+        <v>235</v>
+      </c>
+      <c r="C227" t="s">
+        <v>262</v>
+      </c>
+      <c r="D227">
+        <v>15</v>
+      </c>
+      <c r="E227" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="228" spans="1:5">
+      <c r="A228" t="s">
+        <v>16</v>
+      </c>
+      <c r="B228" t="s">
+        <v>236</v>
+      </c>
+      <c r="C228" t="s">
+        <v>262</v>
+      </c>
+      <c r="D228">
+        <v>24</v>
+      </c>
+      <c r="E228" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="229" spans="1:5">
+      <c r="A229" t="s">
+        <v>16</v>
+      </c>
+      <c r="B229" t="s">
+        <v>153</v>
+      </c>
+      <c r="C229" t="s">
+        <v>262</v>
+      </c>
+      <c r="D229">
+        <v>24</v>
+      </c>
+      <c r="E229" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="230" spans="1:5">
+      <c r="A230" t="s">
+        <v>16</v>
+      </c>
+      <c r="B230" t="s">
+        <v>154</v>
+      </c>
+      <c r="C230" t="s">
+        <v>262</v>
+      </c>
+      <c r="D230">
+        <v>16</v>
+      </c>
+      <c r="E230" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="231" spans="1:5">
+      <c r="A231" t="s">
+        <v>16</v>
+      </c>
+      <c r="B231" t="s">
+        <v>155</v>
+      </c>
+      <c r="C231" t="s">
+        <v>262</v>
+      </c>
+      <c r="D231">
+        <v>8</v>
+      </c>
+      <c r="E231" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="232" spans="1:5">
+      <c r="A232" t="s">
+        <v>16</v>
+      </c>
+      <c r="B232" t="s">
+        <v>237</v>
+      </c>
+      <c r="C232" t="s">
+        <v>262</v>
+      </c>
+      <c r="D232">
+        <v>48</v>
+      </c>
+      <c r="E232" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="233" spans="1:5">
+      <c r="A233" t="s">
+        <v>16</v>
+      </c>
+      <c r="B233" t="s">
+        <v>238</v>
+      </c>
+      <c r="C233" t="s">
+        <v>262</v>
+      </c>
+      <c r="D233">
+        <v>24</v>
+      </c>
+      <c r="E233" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="234" spans="1:5">
+      <c r="A234" t="s">
+        <v>16</v>
+      </c>
+      <c r="B234" t="s">
+        <v>239</v>
+      </c>
+      <c r="C234" t="s">
+        <v>262</v>
+      </c>
+      <c r="D234">
+        <v>16</v>
+      </c>
+      <c r="E234" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="235" spans="1:5">
+      <c r="A235" t="s">
+        <v>16</v>
+      </c>
+      <c r="B235" t="s">
+        <v>240</v>
+      </c>
+      <c r="C235" t="s">
+        <v>262</v>
+      </c>
+      <c r="D235">
+        <v>8</v>
+      </c>
+      <c r="E235" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="236" spans="1:5">
+      <c r="A236" t="s">
+        <v>16</v>
+      </c>
+      <c r="B236" t="s">
+        <v>241</v>
+      </c>
+      <c r="C236" t="s">
+        <v>262</v>
+      </c>
+      <c r="D236">
+        <v>7</v>
+      </c>
+      <c r="E236" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="237" spans="1:5">
+      <c r="A237" t="s">
+        <v>16</v>
+      </c>
+      <c r="B237" t="s">
+        <v>242</v>
+      </c>
+      <c r="C237" t="s">
+        <v>262</v>
+      </c>
+      <c r="D237">
+        <v>7</v>
+      </c>
+      <c r="E237" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="238" spans="1:5">
+      <c r="A238" t="s">
+        <v>16</v>
+      </c>
+      <c r="B238" t="s">
+        <v>156</v>
+      </c>
+      <c r="C238" t="s">
+        <v>262</v>
+      </c>
+      <c r="D238">
+        <v>24</v>
+      </c>
+      <c r="E238" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="239" spans="1:5">
+      <c r="A239" t="s">
+        <v>16</v>
+      </c>
+      <c r="B239" t="s">
+        <v>157</v>
+      </c>
+      <c r="C239" t="s">
+        <v>262</v>
+      </c>
+      <c r="D239">
+        <v>24</v>
+      </c>
+      <c r="E239" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="240" spans="1:5">
+      <c r="A240" t="s">
+        <v>16</v>
+      </c>
+      <c r="B240" t="s">
+        <v>243</v>
+      </c>
+      <c r="C240" t="s">
+        <v>262</v>
+      </c>
+      <c r="D240">
+        <v>8</v>
+      </c>
+      <c r="E240" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="241" spans="1:5">
+      <c r="A241" t="s">
+        <v>16</v>
+      </c>
+      <c r="B241" t="s">
+        <v>244</v>
+      </c>
+      <c r="C241" t="s">
+        <v>262</v>
+      </c>
+      <c r="D241">
+        <v>16</v>
+      </c>
+      <c r="E241" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="242" spans="1:5">
+      <c r="A242" t="s">
+        <v>16</v>
+      </c>
+      <c r="B242" t="s">
+        <v>245</v>
+      </c>
+      <c r="C242" t="s">
+        <v>262</v>
+      </c>
+      <c r="D242">
+        <v>8</v>
+      </c>
+      <c r="E242" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="243" spans="1:5">
+      <c r="A243" t="s">
+        <v>16</v>
+      </c>
+      <c r="B243" t="s">
+        <v>246</v>
+      </c>
+      <c r="C243" t="s">
+        <v>262</v>
+      </c>
+      <c r="D243">
+        <v>52</v>
+      </c>
+      <c r="E243" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="244" spans="1:5">
+      <c r="A244" t="s">
+        <v>16</v>
+      </c>
+      <c r="B244" t="s">
+        <v>247</v>
+      </c>
+      <c r="C244" t="s">
+        <v>262</v>
+      </c>
+      <c r="D244">
+        <v>13</v>
+      </c>
+      <c r="E244" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="245" spans="1:5">
+      <c r="A245" t="s">
+        <v>16</v>
+      </c>
+      <c r="B245" t="s">
+        <v>248</v>
+      </c>
+      <c r="C245" t="s">
+        <v>262</v>
+      </c>
+      <c r="D245">
+        <v>13</v>
+      </c>
+      <c r="E245" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="246" spans="1:5">
+      <c r="A246" t="s">
+        <v>16</v>
+      </c>
+      <c r="B246" t="s">
+        <v>249</v>
+      </c>
+      <c r="C246" t="s">
+        <v>262</v>
+      </c>
+      <c r="D246">
+        <v>27</v>
+      </c>
+      <c r="E246" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="247" spans="1:5">
+      <c r="A247" t="s">
+        <v>16</v>
+      </c>
+      <c r="B247" t="s">
+        <v>164</v>
+      </c>
+      <c r="C247" t="s">
+        <v>262</v>
+      </c>
+      <c r="D247">
+        <v>16</v>
+      </c>
+      <c r="E247" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="248" spans="1:5">
+      <c r="A248" t="s">
+        <v>16</v>
+      </c>
+      <c r="B248" t="s">
+        <v>165</v>
+      </c>
+      <c r="C248" t="s">
+        <v>262</v>
+      </c>
+      <c r="D248">
+        <v>8</v>
+      </c>
+      <c r="E248" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="249" spans="1:5">
+      <c r="A249" t="s">
+        <v>16</v>
+      </c>
+      <c r="B249" t="s">
+        <v>166</v>
+      </c>
+      <c r="C249" t="s">
+        <v>262</v>
+      </c>
+      <c r="D249">
+        <v>16</v>
+      </c>
+      <c r="E249" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="250" spans="1:5">
+      <c r="A250" t="s">
+        <v>16</v>
+      </c>
+      <c r="B250" t="s">
+        <v>167</v>
+      </c>
+      <c r="C250" t="s">
+        <v>262</v>
+      </c>
+      <c r="D250">
+        <v>8</v>
+      </c>
+      <c r="E250" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="251" spans="1:5">
+      <c r="A251" t="s">
+        <v>16</v>
+      </c>
+      <c r="B251" t="s">
+        <v>168</v>
+      </c>
+      <c r="C251" t="s">
+        <v>262</v>
+      </c>
+      <c r="D251">
+        <v>16</v>
+      </c>
+      <c r="E251" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="252" spans="1:5">
+      <c r="A252" t="s">
+        <v>16</v>
+      </c>
+      <c r="B252" t="s">
+        <v>169</v>
+      </c>
+      <c r="C252" t="s">
+        <v>262</v>
+      </c>
+      <c r="D252">
+        <v>8</v>
+      </c>
+      <c r="E252" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="253" spans="1:5">
+      <c r="A253" t="s">
+        <v>16</v>
+      </c>
+      <c r="B253" t="s">
+        <v>250</v>
+      </c>
+      <c r="C253" t="s">
+        <v>262</v>
+      </c>
+      <c r="D253">
+        <v>53</v>
+      </c>
+      <c r="E253" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="254" spans="1:5">
+      <c r="A254" t="s">
+        <v>16</v>
+      </c>
+      <c r="B254" t="s">
+        <v>251</v>
+      </c>
+      <c r="C254" t="s">
+        <v>262</v>
+      </c>
+      <c r="D254">
+        <v>8</v>
+      </c>
+      <c r="E254" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="255" spans="1:5">
+      <c r="A255" t="s">
+        <v>16</v>
+      </c>
+      <c r="B255" t="s">
+        <v>176</v>
+      </c>
+      <c r="C255" t="s">
+        <v>262</v>
+      </c>
+      <c r="D255">
+        <v>16</v>
+      </c>
+      <c r="E255" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="256" spans="1:5">
+      <c r="A256" t="s">
+        <v>16</v>
+      </c>
+      <c r="B256" t="s">
+        <v>177</v>
+      </c>
+      <c r="C256" t="s">
+        <v>262</v>
+      </c>
+      <c r="D256">
+        <v>8</v>
+      </c>
+      <c r="E256" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="257" spans="1:5">
+      <c r="A257" t="s">
+        <v>16</v>
+      </c>
+      <c r="B257" t="s">
+        <v>178</v>
+      </c>
+      <c r="C257" t="s">
+        <v>262</v>
+      </c>
+      <c r="D257">
+        <v>16</v>
+      </c>
+      <c r="E257" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="258" spans="1:5">
+      <c r="A258" t="s">
+        <v>16</v>
+      </c>
+      <c r="B258" t="s">
+        <v>179</v>
+      </c>
+      <c r="C258" t="s">
+        <v>262</v>
+      </c>
+      <c r="D258">
+        <v>8</v>
+      </c>
+      <c r="E258" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="259" spans="1:5">
+      <c r="A259" t="s">
+        <v>16</v>
+      </c>
+      <c r="B259" t="s">
+        <v>180</v>
+      </c>
+      <c r="C259" t="s">
+        <v>262</v>
+      </c>
+      <c r="D259">
+        <v>16</v>
+      </c>
+      <c r="E259" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="260" spans="1:5">
+      <c r="A260" t="s">
+        <v>16</v>
+      </c>
+      <c r="B260" t="s">
+        <v>181</v>
+      </c>
+      <c r="C260" t="s">
+        <v>262</v>
+      </c>
+      <c r="D260">
+        <v>8</v>
+      </c>
+      <c r="E260" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="261" spans="1:5">
+      <c r="A261" t="s">
+        <v>16</v>
+      </c>
+      <c r="B261" t="s">
+        <v>182</v>
+      </c>
+      <c r="C261" t="s">
+        <v>262</v>
+      </c>
+      <c r="D261">
+        <v>16</v>
+      </c>
+      <c r="E261" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="262" spans="1:5">
+      <c r="A262" t="s">
+        <v>16</v>
+      </c>
+      <c r="B262" t="s">
+        <v>183</v>
+      </c>
+      <c r="C262" t="s">
+        <v>262</v>
+      </c>
+      <c r="D262">
+        <v>16</v>
+      </c>
+      <c r="E262" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="263" spans="1:5">
+      <c r="A263" t="s">
+        <v>16</v>
+      </c>
+      <c r="B263" t="s">
+        <v>184</v>
+      </c>
+      <c r="C263" t="s">
+        <v>262</v>
+      </c>
+      <c r="D263">
+        <v>24</v>
+      </c>
+      <c r="E263" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="264" spans="1:5">
+      <c r="A264" t="s">
+        <v>16</v>
+      </c>
+      <c r="B264" t="s">
+        <v>185</v>
+      </c>
+      <c r="C264" t="s">
+        <v>262</v>
+      </c>
+      <c r="D264">
+        <v>24</v>
+      </c>
+      <c r="E264" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="265" spans="1:5">
+      <c r="A265" t="s">
+        <v>16</v>
+      </c>
+      <c r="B265" t="s">
+        <v>186</v>
+      </c>
+      <c r="C265" t="s">
+        <v>262</v>
+      </c>
+      <c r="D265">
+        <v>16</v>
+      </c>
+      <c r="E265" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="266" spans="1:5">
+      <c r="A266" t="s">
+        <v>16</v>
+      </c>
+      <c r="B266" t="s">
+        <v>187</v>
+      </c>
+      <c r="C266" t="s">
+        <v>262</v>
+      </c>
+      <c r="D266">
+        <v>13</v>
+      </c>
+      <c r="E266" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="267" spans="1:5">
+      <c r="A267" t="s">
+        <v>16</v>
+      </c>
+      <c r="B267" t="s">
+        <v>212</v>
+      </c>
+      <c r="C267" t="s">
+        <v>262</v>
+      </c>
+      <c r="D267">
+        <v>61</v>
+      </c>
+      <c r="E267" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="268" spans="1:5">
+      <c r="A268" t="s">
+        <v>16</v>
+      </c>
+      <c r="B268" t="s">
+        <v>213</v>
+      </c>
+      <c r="C268" t="s">
+        <v>262</v>
+      </c>
+      <c r="D268">
+        <v>61</v>
+      </c>
+      <c r="E268" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="269" spans="1:5">
+      <c r="A269" t="s">
+        <v>16</v>
+      </c>
+      <c r="B269" t="s">
+        <v>105</v>
+      </c>
+      <c r="C269" t="s">
+        <v>262</v>
+      </c>
+      <c r="D269">
+        <v>2</v>
+      </c>
+      <c r="E269" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="270" spans="1:5">
+      <c r="A270" t="s">
+        <v>16</v>
+      </c>
+      <c r="B270" t="s">
+        <v>252</v>
+      </c>
+      <c r="C270" t="s">
+        <v>262</v>
+      </c>
+      <c r="D270">
+        <v>3</v>
+      </c>
+      <c r="E270" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="271" spans="1:5">
+      <c r="A271" t="s">
+        <v>16</v>
+      </c>
+      <c r="B271" t="s">
+        <v>253</v>
+      </c>
+      <c r="C271" t="s">
+        <v>262</v>
+      </c>
+      <c r="D271">
+        <v>1</v>
+      </c>
+      <c r="E271" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="272" spans="1:5">
+      <c r="A272" t="s">
+        <v>16</v>
+      </c>
+      <c r="B272" t="s">
+        <v>254</v>
+      </c>
+      <c r="C272" t="s">
+        <v>262</v>
+      </c>
+      <c r="D272">
+        <v>9</v>
+      </c>
+      <c r="E272" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="273" spans="1:5">
+      <c r="A273" t="s">
+        <v>16</v>
+      </c>
+      <c r="B273" t="s">
+        <v>162</v>
+      </c>
+      <c r="C273" t="s">
+        <v>262</v>
+      </c>
+      <c r="D273">
+        <v>3</v>
+      </c>
+      <c r="E273" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="274" spans="1:5">
+      <c r="A274" t="s">
+        <v>16</v>
+      </c>
+      <c r="B274" t="s">
+        <v>163</v>
+      </c>
+      <c r="C274" t="s">
+        <v>262</v>
+      </c>
+      <c r="D274">
+        <v>5</v>
+      </c>
+      <c r="E274" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="275" spans="1:5">
+      <c r="A275" t="s">
+        <v>16</v>
+      </c>
+      <c r="B275" t="s">
+        <v>172</v>
+      </c>
+      <c r="C275" t="s">
+        <v>262</v>
+      </c>
+      <c r="D275">
+        <v>3</v>
+      </c>
+      <c r="E275" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="276" spans="1:5">
+      <c r="A276" t="s">
+        <v>16</v>
+      </c>
+      <c r="B276" t="s">
+        <v>187</v>
+      </c>
+      <c r="C276" t="s">
+        <v>262</v>
+      </c>
+      <c r="D276">
+        <v>3</v>
+      </c>
+      <c r="E276" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="277" spans="1:5">
+      <c r="A277" t="s">
+        <v>17</v>
+      </c>
+      <c r="B277" t="s">
+        <v>255</v>
+      </c>
+      <c r="C277" t="s">
+        <v>271</v>
+      </c>
+      <c r="D277">
+        <v>1</v>
+      </c>
+      <c r="E277" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="278" spans="1:5">
+      <c r="A278" t="s">
+        <v>17</v>
+      </c>
+      <c r="B278" t="s">
+        <v>256</v>
+      </c>
+      <c r="C278" t="s">
+        <v>271</v>
+      </c>
+      <c r="D278">
+        <v>1</v>
+      </c>
+      <c r="E278" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="279" spans="1:5">
+      <c r="A279" t="s">
+        <v>17</v>
+      </c>
+      <c r="B279" t="s">
+        <v>91</v>
+      </c>
+      <c r="C279" t="s">
+        <v>271</v>
+      </c>
+      <c r="D279">
+        <v>4</v>
+      </c>
+      <c r="E279" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="280" spans="1:5">
+      <c r="A280" t="s">
+        <v>17</v>
+      </c>
+      <c r="B280" t="s">
+        <v>257</v>
+      </c>
+      <c r="C280" t="s">
+        <v>271</v>
+      </c>
+      <c r="D280">
+        <v>1</v>
+      </c>
+      <c r="E280" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="281" spans="1:5">
+      <c r="A281" t="s">
+        <v>17</v>
+      </c>
+      <c r="B281" t="s">
+        <v>258</v>
+      </c>
+      <c r="C281" t="s">
+        <v>271</v>
+      </c>
+      <c r="D281">
+        <v>3</v>
+      </c>
+      <c r="E281" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="282" spans="1:5">
+      <c r="A282" t="s">
+        <v>17</v>
+      </c>
+      <c r="B282" t="s">
+        <v>259</v>
+      </c>
+      <c r="C282" t="s">
+        <v>271</v>
+      </c>
+      <c r="D282">
+        <v>1</v>
+      </c>
+      <c r="E282" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="283" spans="1:5">
+      <c r="A283" t="s">
+        <v>18</v>
+      </c>
+      <c r="B283" t="s">
+        <v>260</v>
+      </c>
+      <c r="C283" t="s">
+        <v>271</v>
+      </c>
+      <c r="D283">
+        <v>1</v>
+      </c>
+      <c r="E283" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="284" spans="1:5">
+      <c r="A284" t="s">
+        <v>19</v>
+      </c>
+      <c r="B284" t="s">
+        <v>261</v>
+      </c>
+      <c r="C284" t="s">
+        <v>266</v>
+      </c>
+      <c r="D284">
+        <v>200</v>
+      </c>
+      <c r="E284" t="s">
+        <v>272</v>
       </c>
     </row>
   </sheetData>

--- a/data/BD_Requerimientos_POs.xlsx
+++ b/data/BD_Requerimientos_POs.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1137" uniqueCount="273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1129" uniqueCount="269">
   <si>
     <t>PO</t>
   </si>
@@ -70,12 +70,6 @@
     <t>26083382</t>
   </si>
   <si>
-    <t>26083394</t>
-  </si>
-  <si>
-    <t>26083428</t>
-  </si>
-  <si>
     <t>11-D-6165-01</t>
   </si>
   <si>
@@ -794,12 +788,6 @@
   </si>
   <si>
     <t>PP14805-04</t>
-  </si>
-  <si>
-    <t>12-D-6030-10</t>
-  </si>
-  <si>
-    <t>PP9247</t>
   </si>
   <si>
     <t>07/09/2026</t>
@@ -1164,7 +1152,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E284"/>
+  <dimension ref="A1:E282"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1189,16 +1177,16 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D2">
         <v>320</v>
       </c>
       <c r="E2" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1206,16 +1194,16 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D3">
         <v>192</v>
       </c>
       <c r="E3" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1223,16 +1211,16 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D4">
         <v>224</v>
       </c>
       <c r="E4" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1240,16 +1228,16 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D5">
         <v>224</v>
       </c>
       <c r="E5" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1257,16 +1245,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D6">
         <v>160</v>
       </c>
       <c r="E6" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1274,16 +1262,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D7">
         <v>160</v>
       </c>
       <c r="E7" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1291,16 +1279,16 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C8" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D8">
         <v>160</v>
       </c>
       <c r="E8" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -1308,16 +1296,16 @@
         <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C9" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D9">
         <v>128</v>
       </c>
       <c r="E9" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -1325,16 +1313,16 @@
         <v>5</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C10" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D10">
         <v>160</v>
       </c>
       <c r="E10" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -1342,16 +1330,16 @@
         <v>5</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C11" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D11">
         <v>160</v>
       </c>
       <c r="E11" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -1359,16 +1347,16 @@
         <v>5</v>
       </c>
       <c r="B12" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C12" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D12">
         <v>96</v>
       </c>
       <c r="E12" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -1376,16 +1364,16 @@
         <v>5</v>
       </c>
       <c r="B13" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C13" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D13">
         <v>96</v>
       </c>
       <c r="E13" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -1393,16 +1381,16 @@
         <v>5</v>
       </c>
       <c r="B14" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C14" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D14">
         <v>96</v>
       </c>
       <c r="E14" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -1410,16 +1398,16 @@
         <v>5</v>
       </c>
       <c r="B15" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C15" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D15">
         <v>112</v>
       </c>
       <c r="E15" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -1427,16 +1415,16 @@
         <v>5</v>
       </c>
       <c r="B16" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C16" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D16">
         <v>112</v>
       </c>
       <c r="E16" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1444,16 +1432,16 @@
         <v>5</v>
       </c>
       <c r="B17" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C17" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D17">
         <v>112</v>
       </c>
       <c r="E17" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1461,16 +1449,16 @@
         <v>5</v>
       </c>
       <c r="B18" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C18" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D18">
         <v>80</v>
       </c>
       <c r="E18" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1478,16 +1466,16 @@
         <v>5</v>
       </c>
       <c r="B19" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C19" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D19">
         <v>80</v>
       </c>
       <c r="E19" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1495,16 +1483,16 @@
         <v>5</v>
       </c>
       <c r="B20" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C20" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D20">
         <v>80</v>
       </c>
       <c r="E20" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1512,16 +1500,16 @@
         <v>5</v>
       </c>
       <c r="B21" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C21" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D21">
         <v>64</v>
       </c>
       <c r="E21" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1529,16 +1517,16 @@
         <v>5</v>
       </c>
       <c r="B22" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C22" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D22">
         <v>80</v>
       </c>
       <c r="E22" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1546,16 +1534,16 @@
         <v>5</v>
       </c>
       <c r="B23" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C23" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D23">
         <v>64</v>
       </c>
       <c r="E23" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1563,16 +1551,16 @@
         <v>5</v>
       </c>
       <c r="B24" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C24" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D24">
         <v>64</v>
       </c>
       <c r="E24" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1580,16 +1568,16 @@
         <v>5</v>
       </c>
       <c r="B25" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C25" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D25">
         <v>64</v>
       </c>
       <c r="E25" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1597,16 +1585,16 @@
         <v>5</v>
       </c>
       <c r="B26" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C26" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D26">
         <v>64</v>
       </c>
       <c r="E26" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1614,16 +1602,16 @@
         <v>5</v>
       </c>
       <c r="B27" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C27" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D27">
         <v>64</v>
       </c>
       <c r="E27" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1631,16 +1619,16 @@
         <v>5</v>
       </c>
       <c r="B28" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C28" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D28">
         <v>64</v>
       </c>
       <c r="E28" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -1648,16 +1636,16 @@
         <v>5</v>
       </c>
       <c r="B29" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C29" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D29">
         <v>40</v>
       </c>
       <c r="E29" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -1665,16 +1653,16 @@
         <v>5</v>
       </c>
       <c r="B30" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C30" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D30">
         <v>40</v>
       </c>
       <c r="E30" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -1682,16 +1670,16 @@
         <v>5</v>
       </c>
       <c r="B31" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C31" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D31">
         <v>40</v>
       </c>
       <c r="E31" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -1699,16 +1687,16 @@
         <v>5</v>
       </c>
       <c r="B32" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C32" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D32">
         <v>32</v>
       </c>
       <c r="E32" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -1716,16 +1704,16 @@
         <v>5</v>
       </c>
       <c r="B33" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C33" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D33">
         <v>40</v>
       </c>
       <c r="E33" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -1733,16 +1721,16 @@
         <v>5</v>
       </c>
       <c r="B34" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C34" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D34">
         <v>40</v>
       </c>
       <c r="E34" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -1750,16 +1738,16 @@
         <v>5</v>
       </c>
       <c r="B35" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C35" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D35">
         <v>40</v>
       </c>
       <c r="E35" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -1767,16 +1755,16 @@
         <v>5</v>
       </c>
       <c r="B36" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C36" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D36">
         <v>40</v>
       </c>
       <c r="E36" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -1784,16 +1772,16 @@
         <v>5</v>
       </c>
       <c r="B37" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C37" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D37">
         <v>32</v>
       </c>
       <c r="E37" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -1801,16 +1789,16 @@
         <v>5</v>
       </c>
       <c r="B38" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C38" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D38">
         <v>40</v>
       </c>
       <c r="E38" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -1818,16 +1806,16 @@
         <v>5</v>
       </c>
       <c r="B39" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C39" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D39">
         <v>32</v>
       </c>
       <c r="E39" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -1835,16 +1823,16 @@
         <v>5</v>
       </c>
       <c r="B40" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C40" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D40">
         <v>32</v>
       </c>
       <c r="E40" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -1852,16 +1840,16 @@
         <v>5</v>
       </c>
       <c r="B41" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C41" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D41">
         <v>32</v>
       </c>
       <c r="E41" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -1869,16 +1857,16 @@
         <v>5</v>
       </c>
       <c r="B42" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C42" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D42">
         <v>32</v>
       </c>
       <c r="E42" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -1886,16 +1874,16 @@
         <v>5</v>
       </c>
       <c r="B43" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C43" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D43">
         <v>32</v>
       </c>
       <c r="E43" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -1903,16 +1891,16 @@
         <v>5</v>
       </c>
       <c r="B44" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C44" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D44">
         <v>40</v>
       </c>
       <c r="E44" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -1920,16 +1908,16 @@
         <v>5</v>
       </c>
       <c r="B45" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C45" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D45">
         <v>32</v>
       </c>
       <c r="E45" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -1937,16 +1925,16 @@
         <v>5</v>
       </c>
       <c r="B46" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C46" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D46">
         <v>32</v>
       </c>
       <c r="E46" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -1954,16 +1942,16 @@
         <v>6</v>
       </c>
       <c r="B47" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C47" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D47">
         <v>4</v>
       </c>
       <c r="E47" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -1971,16 +1959,16 @@
         <v>6</v>
       </c>
       <c r="B48" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C48" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D48">
         <v>73</v>
       </c>
       <c r="E48" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -1988,16 +1976,16 @@
         <v>7</v>
       </c>
       <c r="B49" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C49" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="D49">
         <v>32</v>
       </c>
       <c r="E49" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -2005,16 +1993,16 @@
         <v>7</v>
       </c>
       <c r="B50" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C50" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="D50">
         <v>32</v>
       </c>
       <c r="E50" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -2022,16 +2010,16 @@
         <v>7</v>
       </c>
       <c r="B51" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C51" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="D51">
         <v>81</v>
       </c>
       <c r="E51" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -2039,16 +2027,16 @@
         <v>7</v>
       </c>
       <c r="B52" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C52" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="D52">
         <v>85</v>
       </c>
       <c r="E52" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -2056,16 +2044,16 @@
         <v>7</v>
       </c>
       <c r="B53" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C53" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="D53">
         <v>85</v>
       </c>
       <c r="E53" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -2073,16 +2061,16 @@
         <v>7</v>
       </c>
       <c r="B54" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C54" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="D54">
         <v>4</v>
       </c>
       <c r="E54" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -2090,16 +2078,16 @@
         <v>7</v>
       </c>
       <c r="B55" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C55" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="D55">
         <v>4</v>
       </c>
       <c r="E55" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -2107,16 +2095,16 @@
         <v>7</v>
       </c>
       <c r="B56" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C56" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="D56">
         <v>16</v>
       </c>
       <c r="E56" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -2124,16 +2112,16 @@
         <v>7</v>
       </c>
       <c r="B57" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C57" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="D57">
         <v>154</v>
       </c>
       <c r="E57" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -2141,16 +2129,16 @@
         <v>7</v>
       </c>
       <c r="B58" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C58" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="D58">
         <v>8</v>
       </c>
       <c r="E58" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -2158,16 +2146,16 @@
         <v>7</v>
       </c>
       <c r="B59" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C59" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="D59">
         <v>8</v>
       </c>
       <c r="E59" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -2175,16 +2163,16 @@
         <v>7</v>
       </c>
       <c r="B60" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C60" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="D60">
         <v>73</v>
       </c>
       <c r="E60" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -2192,16 +2180,16 @@
         <v>7</v>
       </c>
       <c r="B61" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C61" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="D61">
         <v>16</v>
       </c>
       <c r="E61" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -2209,16 +2197,16 @@
         <v>7</v>
       </c>
       <c r="B62" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C62" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="D62">
         <v>8</v>
       </c>
       <c r="E62" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -2226,16 +2214,16 @@
         <v>7</v>
       </c>
       <c r="B63" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C63" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="D63">
         <v>4</v>
       </c>
       <c r="E63" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -2243,16 +2231,16 @@
         <v>7</v>
       </c>
       <c r="B64" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C64" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="D64">
         <v>73</v>
       </c>
       <c r="E64" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -2260,16 +2248,16 @@
         <v>7</v>
       </c>
       <c r="B65" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C65" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="D65">
         <v>73</v>
       </c>
       <c r="E65" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -2277,16 +2265,16 @@
         <v>7</v>
       </c>
       <c r="B66" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C66" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="D66">
         <v>73</v>
       </c>
       <c r="E66" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -2294,16 +2282,16 @@
         <v>7</v>
       </c>
       <c r="B67" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C67" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="D67">
         <v>4</v>
       </c>
       <c r="E67" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -2311,16 +2299,16 @@
         <v>7</v>
       </c>
       <c r="B68" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C68" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="D68">
         <v>8</v>
       </c>
       <c r="E68" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -2328,16 +2316,16 @@
         <v>7</v>
       </c>
       <c r="B69" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C69" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="D69">
         <v>8</v>
       </c>
       <c r="E69" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -2345,16 +2333,16 @@
         <v>7</v>
       </c>
       <c r="B70" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C70" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="D70">
         <v>73</v>
       </c>
       <c r="E70" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="71" spans="1:5">
@@ -2362,16 +2350,16 @@
         <v>7</v>
       </c>
       <c r="B71" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C71" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="D71">
         <v>150</v>
       </c>
       <c r="E71" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -2379,16 +2367,16 @@
         <v>8</v>
       </c>
       <c r="B72" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C72" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="D72">
         <v>32</v>
       </c>
       <c r="E72" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="73" spans="1:5">
@@ -2396,16 +2384,16 @@
         <v>9</v>
       </c>
       <c r="B73" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C73" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="D73">
         <v>8</v>
       </c>
       <c r="E73" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="74" spans="1:5">
@@ -2413,16 +2401,16 @@
         <v>10</v>
       </c>
       <c r="B74" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C74" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="D74">
         <v>40</v>
       </c>
       <c r="E74" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -2430,16 +2418,16 @@
         <v>11</v>
       </c>
       <c r="B75" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C75" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="D75">
         <v>1</v>
       </c>
       <c r="E75" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="76" spans="1:5">
@@ -2447,16 +2435,16 @@
         <v>12</v>
       </c>
       <c r="B76" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C76" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="D76">
         <v>128</v>
       </c>
       <c r="E76" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="77" spans="1:5">
@@ -2464,16 +2452,16 @@
         <v>12</v>
       </c>
       <c r="B77" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C77" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="D77">
         <v>32</v>
       </c>
       <c r="E77" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="78" spans="1:5">
@@ -2481,16 +2469,16 @@
         <v>12</v>
       </c>
       <c r="B78" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C78" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="D78">
         <v>40</v>
       </c>
       <c r="E78" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="79" spans="1:5">
@@ -2498,16 +2486,16 @@
         <v>12</v>
       </c>
       <c r="B79" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C79" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="D79">
         <v>40</v>
       </c>
       <c r="E79" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="80" spans="1:5">
@@ -2515,16 +2503,16 @@
         <v>12</v>
       </c>
       <c r="B80" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C80" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="D80">
         <v>64</v>
       </c>
       <c r="E80" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="81" spans="1:5">
@@ -2532,16 +2520,16 @@
         <v>12</v>
       </c>
       <c r="B81" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C81" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="D81">
         <v>64</v>
       </c>
       <c r="E81" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="82" spans="1:5">
@@ -2549,16 +2537,16 @@
         <v>13</v>
       </c>
       <c r="B82" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C82" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="D82">
         <v>32</v>
       </c>
       <c r="E82" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="83" spans="1:5">
@@ -2566,16 +2554,16 @@
         <v>13</v>
       </c>
       <c r="B83" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C83" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="D83">
         <v>40</v>
       </c>
       <c r="E83" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="84" spans="1:5">
@@ -2583,16 +2571,16 @@
         <v>13</v>
       </c>
       <c r="B84" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C84" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="D84">
         <v>40</v>
       </c>
       <c r="E84" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="85" spans="1:5">
@@ -2600,16 +2588,16 @@
         <v>14</v>
       </c>
       <c r="B85" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C85" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="D85">
         <v>20</v>
       </c>
       <c r="E85" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="86" spans="1:5">
@@ -2617,16 +2605,16 @@
         <v>14</v>
       </c>
       <c r="B86" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C86" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="D86">
         <v>32</v>
       </c>
       <c r="E86" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="87" spans="1:5">
@@ -2634,16 +2622,16 @@
         <v>14</v>
       </c>
       <c r="B87" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C87" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="D87">
         <v>64</v>
       </c>
       <c r="E87" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="88" spans="1:5">
@@ -2651,16 +2639,16 @@
         <v>15</v>
       </c>
       <c r="B88" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C88" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D88">
         <v>2</v>
       </c>
       <c r="E88" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="89" spans="1:5">
@@ -2668,16 +2656,16 @@
         <v>15</v>
       </c>
       <c r="B89" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C89" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D89">
         <v>2</v>
       </c>
       <c r="E89" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="90" spans="1:5">
@@ -2685,16 +2673,16 @@
         <v>15</v>
       </c>
       <c r="B90" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C90" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D90">
         <v>2</v>
       </c>
       <c r="E90" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="91" spans="1:5">
@@ -2702,16 +2690,16 @@
         <v>15</v>
       </c>
       <c r="B91" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C91" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D91">
         <v>6</v>
       </c>
       <c r="E91" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="92" spans="1:5">
@@ -2719,16 +2707,16 @@
         <v>15</v>
       </c>
       <c r="B92" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C92" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D92">
         <v>2</v>
       </c>
       <c r="E92" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="93" spans="1:5">
@@ -2736,16 +2724,16 @@
         <v>15</v>
       </c>
       <c r="B93" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C93" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D93">
         <v>9</v>
       </c>
       <c r="E93" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="94" spans="1:5">
@@ -2753,16 +2741,16 @@
         <v>15</v>
       </c>
       <c r="B94" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C94" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D94">
         <v>8</v>
       </c>
       <c r="E94" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="95" spans="1:5">
@@ -2770,16 +2758,16 @@
         <v>15</v>
       </c>
       <c r="B95" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C95" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D95">
         <v>8</v>
       </c>
       <c r="E95" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="96" spans="1:5">
@@ -2787,16 +2775,16 @@
         <v>15</v>
       </c>
       <c r="B96" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C96" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D96">
         <v>2</v>
       </c>
       <c r="E96" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="97" spans="1:5">
@@ -2804,16 +2792,16 @@
         <v>15</v>
       </c>
       <c r="B97" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C97" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D97">
         <v>2</v>
       </c>
       <c r="E97" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="98" spans="1:5">
@@ -2821,16 +2809,16 @@
         <v>15</v>
       </c>
       <c r="B98" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C98" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D98">
         <v>2</v>
       </c>
       <c r="E98" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="99" spans="1:5">
@@ -2838,16 +2826,16 @@
         <v>15</v>
       </c>
       <c r="B99" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C99" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D99">
         <v>2</v>
       </c>
       <c r="E99" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="100" spans="1:5">
@@ -2855,16 +2843,16 @@
         <v>15</v>
       </c>
       <c r="B100" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C100" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D100">
         <v>1</v>
       </c>
       <c r="E100" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="101" spans="1:5">
@@ -2872,16 +2860,16 @@
         <v>15</v>
       </c>
       <c r="B101" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C101" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D101">
         <v>1</v>
       </c>
       <c r="E101" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="102" spans="1:5">
@@ -2889,16 +2877,16 @@
         <v>15</v>
       </c>
       <c r="B102" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C102" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D102">
         <v>1</v>
       </c>
       <c r="E102" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="103" spans="1:5">
@@ -2906,16 +2894,16 @@
         <v>15</v>
       </c>
       <c r="B103" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C103" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D103">
         <v>2</v>
       </c>
       <c r="E103" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="104" spans="1:5">
@@ -2923,16 +2911,16 @@
         <v>15</v>
       </c>
       <c r="B104" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C104" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D104">
         <v>6</v>
       </c>
       <c r="E104" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="105" spans="1:5">
@@ -2940,16 +2928,16 @@
         <v>15</v>
       </c>
       <c r="B105" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C105" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D105">
         <v>2</v>
       </c>
       <c r="E105" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="106" spans="1:5">
@@ -2957,16 +2945,16 @@
         <v>15</v>
       </c>
       <c r="B106" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C106" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D106">
         <v>1</v>
       </c>
       <c r="E106" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="107" spans="1:5">
@@ -2974,16 +2962,16 @@
         <v>15</v>
       </c>
       <c r="B107" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C107" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D107">
         <v>1</v>
       </c>
       <c r="E107" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="108" spans="1:5">
@@ -2991,16 +2979,16 @@
         <v>15</v>
       </c>
       <c r="B108" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C108" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D108">
         <v>1</v>
       </c>
       <c r="E108" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="109" spans="1:5">
@@ -3008,16 +2996,16 @@
         <v>15</v>
       </c>
       <c r="B109" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C109" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D109">
         <v>1</v>
       </c>
       <c r="E109" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="110" spans="1:5">
@@ -3025,16 +3013,16 @@
         <v>15</v>
       </c>
       <c r="B110" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C110" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D110">
         <v>1</v>
       </c>
       <c r="E110" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="111" spans="1:5">
@@ -3042,16 +3030,16 @@
         <v>15</v>
       </c>
       <c r="B111" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C111" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D111">
         <v>18</v>
       </c>
       <c r="E111" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="112" spans="1:5">
@@ -3059,16 +3047,16 @@
         <v>15</v>
       </c>
       <c r="B112" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C112" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D112">
         <v>6</v>
       </c>
       <c r="E112" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="113" spans="1:5">
@@ -3076,16 +3064,16 @@
         <v>15</v>
       </c>
       <c r="B113" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C113" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D113">
         <v>2</v>
       </c>
       <c r="E113" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="114" spans="1:5">
@@ -3093,16 +3081,16 @@
         <v>15</v>
       </c>
       <c r="B114" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C114" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D114">
         <v>2</v>
       </c>
       <c r="E114" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="115" spans="1:5">
@@ -3110,16 +3098,16 @@
         <v>15</v>
       </c>
       <c r="B115" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C115" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D115">
         <v>2</v>
       </c>
       <c r="E115" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="116" spans="1:5">
@@ -3127,16 +3115,16 @@
         <v>15</v>
       </c>
       <c r="B116" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C116" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D116">
         <v>6</v>
       </c>
       <c r="E116" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="117" spans="1:5">
@@ -3144,16 +3132,16 @@
         <v>15</v>
       </c>
       <c r="B117" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C117" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D117">
         <v>6</v>
       </c>
       <c r="E117" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="118" spans="1:5">
@@ -3161,16 +3149,16 @@
         <v>15</v>
       </c>
       <c r="B118" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C118" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D118">
         <v>2</v>
       </c>
       <c r="E118" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="119" spans="1:5">
@@ -3178,16 +3166,16 @@
         <v>15</v>
       </c>
       <c r="B119" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C119" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D119">
         <v>156</v>
       </c>
       <c r="E119" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="120" spans="1:5">
@@ -3195,16 +3183,16 @@
         <v>15</v>
       </c>
       <c r="B120" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C120" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D120">
         <v>52</v>
       </c>
       <c r="E120" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="121" spans="1:5">
@@ -3212,16 +3200,16 @@
         <v>15</v>
       </c>
       <c r="B121" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C121" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D121">
         <v>24</v>
       </c>
       <c r="E121" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="122" spans="1:5">
@@ -3229,16 +3217,16 @@
         <v>15</v>
       </c>
       <c r="B122" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C122" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D122">
         <v>8</v>
       </c>
       <c r="E122" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="123" spans="1:5">
@@ -3246,16 +3234,16 @@
         <v>15</v>
       </c>
       <c r="B123" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C123" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D123">
         <v>16</v>
       </c>
       <c r="E123" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="124" spans="1:5">
@@ -3263,16 +3251,16 @@
         <v>15</v>
       </c>
       <c r="B124" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C124" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D124">
         <v>16</v>
       </c>
       <c r="E124" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="125" spans="1:5">
@@ -3280,16 +3268,16 @@
         <v>15</v>
       </c>
       <c r="B125" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C125" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D125">
         <v>6</v>
       </c>
       <c r="E125" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="126" spans="1:5">
@@ -3297,16 +3285,16 @@
         <v>15</v>
       </c>
       <c r="B126" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C126" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D126">
         <v>6</v>
       </c>
       <c r="E126" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="127" spans="1:5">
@@ -3314,16 +3302,16 @@
         <v>15</v>
       </c>
       <c r="B127" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C127" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D127">
         <v>16</v>
       </c>
       <c r="E127" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="128" spans="1:5">
@@ -3331,16 +3319,16 @@
         <v>15</v>
       </c>
       <c r="B128" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C128" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D128">
         <v>16</v>
       </c>
       <c r="E128" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="129" spans="1:5">
@@ -3348,16 +3336,16 @@
         <v>15</v>
       </c>
       <c r="B129" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C129" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D129">
         <v>2</v>
       </c>
       <c r="E129" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="130" spans="1:5">
@@ -3365,16 +3353,16 @@
         <v>15</v>
       </c>
       <c r="B130" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C130" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D130">
         <v>2</v>
       </c>
       <c r="E130" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="131" spans="1:5">
@@ -3382,16 +3370,16 @@
         <v>15</v>
       </c>
       <c r="B131" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C131" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D131">
         <v>6</v>
       </c>
       <c r="E131" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="132" spans="1:5">
@@ -3399,16 +3387,16 @@
         <v>15</v>
       </c>
       <c r="B132" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C132" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D132">
         <v>10</v>
       </c>
       <c r="E132" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="133" spans="1:5">
@@ -3416,16 +3404,16 @@
         <v>15</v>
       </c>
       <c r="B133" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C133" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D133">
         <v>8</v>
       </c>
       <c r="E133" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="134" spans="1:5">
@@ -3433,16 +3421,16 @@
         <v>15</v>
       </c>
       <c r="B134" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C134" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D134">
         <v>6</v>
       </c>
       <c r="E134" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="135" spans="1:5">
@@ -3450,16 +3438,16 @@
         <v>15</v>
       </c>
       <c r="B135" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C135" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D135">
         <v>6</v>
       </c>
       <c r="E135" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="136" spans="1:5">
@@ -3467,16 +3455,16 @@
         <v>15</v>
       </c>
       <c r="B136" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C136" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D136">
         <v>2</v>
       </c>
       <c r="E136" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="137" spans="1:5">
@@ -3484,16 +3472,16 @@
         <v>15</v>
       </c>
       <c r="B137" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C137" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D137">
         <v>4</v>
       </c>
       <c r="E137" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="138" spans="1:5">
@@ -3501,16 +3489,16 @@
         <v>15</v>
       </c>
       <c r="B138" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C138" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D138">
         <v>6</v>
       </c>
       <c r="E138" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="139" spans="1:5">
@@ -3518,16 +3506,16 @@
         <v>15</v>
       </c>
       <c r="B139" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C139" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D139">
         <v>6</v>
       </c>
       <c r="E139" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="140" spans="1:5">
@@ -3535,16 +3523,16 @@
         <v>15</v>
       </c>
       <c r="B140" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C140" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D140">
         <v>2</v>
       </c>
       <c r="E140" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="141" spans="1:5">
@@ -3552,16 +3540,16 @@
         <v>15</v>
       </c>
       <c r="B141" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C141" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D141">
         <v>8</v>
       </c>
       <c r="E141" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="142" spans="1:5">
@@ -3569,16 +3557,16 @@
         <v>15</v>
       </c>
       <c r="B142" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C142" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D142">
         <v>8</v>
       </c>
       <c r="E142" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="143" spans="1:5">
@@ -3586,16 +3574,16 @@
         <v>15</v>
       </c>
       <c r="B143" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C143" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D143">
         <v>2</v>
       </c>
       <c r="E143" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="144" spans="1:5">
@@ -3603,16 +3591,16 @@
         <v>15</v>
       </c>
       <c r="B144" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C144" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D144">
         <v>4</v>
       </c>
       <c r="E144" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="145" spans="1:5">
@@ -3620,16 +3608,16 @@
         <v>15</v>
       </c>
       <c r="B145" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C145" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D145">
         <v>2</v>
       </c>
       <c r="E145" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="146" spans="1:5">
@@ -3637,16 +3625,16 @@
         <v>15</v>
       </c>
       <c r="B146" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C146" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D146">
         <v>6</v>
       </c>
       <c r="E146" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="147" spans="1:5">
@@ -3654,16 +3642,16 @@
         <v>15</v>
       </c>
       <c r="B147" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C147" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D147">
         <v>6</v>
       </c>
       <c r="E147" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="148" spans="1:5">
@@ -3671,16 +3659,16 @@
         <v>15</v>
       </c>
       <c r="B148" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C148" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D148">
         <v>10</v>
       </c>
       <c r="E148" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="149" spans="1:5">
@@ -3688,16 +3676,16 @@
         <v>15</v>
       </c>
       <c r="B149" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C149" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D149">
         <v>6</v>
       </c>
       <c r="E149" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="150" spans="1:5">
@@ -3705,16 +3693,16 @@
         <v>15</v>
       </c>
       <c r="B150" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C150" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D150">
         <v>2</v>
       </c>
       <c r="E150" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="151" spans="1:5">
@@ -3722,16 +3710,16 @@
         <v>15</v>
       </c>
       <c r="B151" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C151" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D151">
         <v>6</v>
       </c>
       <c r="E151" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="152" spans="1:5">
@@ -3739,16 +3727,16 @@
         <v>15</v>
       </c>
       <c r="B152" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C152" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D152">
         <v>2</v>
       </c>
       <c r="E152" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="153" spans="1:5">
@@ -3756,16 +3744,16 @@
         <v>15</v>
       </c>
       <c r="B153" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C153" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D153">
         <v>6</v>
       </c>
       <c r="E153" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="154" spans="1:5">
@@ -3773,16 +3761,16 @@
         <v>15</v>
       </c>
       <c r="B154" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C154" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D154">
         <v>2</v>
       </c>
       <c r="E154" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="155" spans="1:5">
@@ -3790,16 +3778,16 @@
         <v>15</v>
       </c>
       <c r="B155" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C155" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D155">
         <v>9</v>
       </c>
       <c r="E155" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="156" spans="1:5">
@@ -3807,16 +3795,16 @@
         <v>15</v>
       </c>
       <c r="B156" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C156" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D156">
         <v>2</v>
       </c>
       <c r="E156" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="157" spans="1:5">
@@ -3824,16 +3812,16 @@
         <v>15</v>
       </c>
       <c r="B157" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C157" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D157">
         <v>7</v>
       </c>
       <c r="E157" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="158" spans="1:5">
@@ -3841,16 +3829,16 @@
         <v>15</v>
       </c>
       <c r="B158" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C158" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D158">
         <v>2</v>
       </c>
       <c r="E158" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="159" spans="1:5">
@@ -3858,16 +3846,16 @@
         <v>15</v>
       </c>
       <c r="B159" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C159" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D159">
         <v>3</v>
       </c>
       <c r="E159" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="160" spans="1:5">
@@ -3875,16 +3863,16 @@
         <v>15</v>
       </c>
       <c r="B160" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C160" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D160">
         <v>3</v>
       </c>
       <c r="E160" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="161" spans="1:5">
@@ -3892,16 +3880,16 @@
         <v>15</v>
       </c>
       <c r="B161" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C161" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D161">
         <v>6</v>
       </c>
       <c r="E161" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="162" spans="1:5">
@@ -3909,16 +3897,16 @@
         <v>15</v>
       </c>
       <c r="B162" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C162" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D162">
         <v>2</v>
       </c>
       <c r="E162" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="163" spans="1:5">
@@ -3926,16 +3914,16 @@
         <v>15</v>
       </c>
       <c r="B163" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C163" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D163">
         <v>6</v>
       </c>
       <c r="E163" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="164" spans="1:5">
@@ -3943,16 +3931,16 @@
         <v>15</v>
       </c>
       <c r="B164" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C164" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D164">
         <v>2</v>
       </c>
       <c r="E164" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="165" spans="1:5">
@@ -3960,16 +3948,16 @@
         <v>15</v>
       </c>
       <c r="B165" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C165" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D165">
         <v>6</v>
       </c>
       <c r="E165" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="166" spans="1:5">
@@ -3977,16 +3965,16 @@
         <v>15</v>
       </c>
       <c r="B166" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C166" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D166">
         <v>2</v>
       </c>
       <c r="E166" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="167" spans="1:5">
@@ -3994,16 +3982,16 @@
         <v>15</v>
       </c>
       <c r="B167" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C167" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D167">
         <v>4</v>
       </c>
       <c r="E167" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="168" spans="1:5">
@@ -4011,16 +3999,16 @@
         <v>15</v>
       </c>
       <c r="B168" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C168" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D168">
         <v>4</v>
       </c>
       <c r="E168" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="169" spans="1:5">
@@ -4028,16 +4016,16 @@
         <v>15</v>
       </c>
       <c r="B169" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C169" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D169">
         <v>8</v>
       </c>
       <c r="E169" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="170" spans="1:5">
@@ -4045,16 +4033,16 @@
         <v>15</v>
       </c>
       <c r="B170" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C170" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D170">
         <v>8</v>
       </c>
       <c r="E170" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="171" spans="1:5">
@@ -4062,16 +4050,16 @@
         <v>15</v>
       </c>
       <c r="B171" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C171" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D171">
         <v>4</v>
       </c>
       <c r="E171" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="172" spans="1:5">
@@ -4079,16 +4067,16 @@
         <v>15</v>
       </c>
       <c r="B172" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C172" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D172">
         <v>6</v>
       </c>
       <c r="E172" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="173" spans="1:5">
@@ -4096,16 +4084,16 @@
         <v>15</v>
       </c>
       <c r="B173" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C173" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D173">
         <v>6</v>
       </c>
       <c r="E173" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="174" spans="1:5">
@@ -4113,16 +4101,16 @@
         <v>15</v>
       </c>
       <c r="B174" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C174" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D174">
         <v>2</v>
       </c>
       <c r="E174" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="175" spans="1:5">
@@ -4130,16 +4118,16 @@
         <v>15</v>
       </c>
       <c r="B175" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C175" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D175">
         <v>6</v>
       </c>
       <c r="E175" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="176" spans="1:5">
@@ -4147,16 +4135,16 @@
         <v>15</v>
       </c>
       <c r="B176" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C176" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D176">
         <v>2</v>
       </c>
       <c r="E176" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="177" spans="1:5">
@@ -4164,16 +4152,16 @@
         <v>15</v>
       </c>
       <c r="B177" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C177" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D177">
         <v>6</v>
       </c>
       <c r="E177" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="178" spans="1:5">
@@ -4181,16 +4169,16 @@
         <v>15</v>
       </c>
       <c r="B178" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C178" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D178">
         <v>2</v>
       </c>
       <c r="E178" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="179" spans="1:5">
@@ -4198,16 +4186,16 @@
         <v>15</v>
       </c>
       <c r="B179" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C179" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D179">
         <v>4</v>
       </c>
       <c r="E179" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="180" spans="1:5">
@@ -4215,16 +4203,16 @@
         <v>15</v>
       </c>
       <c r="B180" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C180" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D180">
         <v>8</v>
       </c>
       <c r="E180" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="181" spans="1:5">
@@ -4232,16 +4220,16 @@
         <v>15</v>
       </c>
       <c r="B181" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C181" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D181">
         <v>8</v>
       </c>
       <c r="E181" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="182" spans="1:5">
@@ -4249,16 +4237,16 @@
         <v>15</v>
       </c>
       <c r="B182" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C182" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D182">
         <v>6</v>
       </c>
       <c r="E182" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="183" spans="1:5">
@@ -4266,16 +4254,16 @@
         <v>15</v>
       </c>
       <c r="B183" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C183" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D183">
         <v>2</v>
       </c>
       <c r="E183" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="184" spans="1:5">
@@ -4283,16 +4271,16 @@
         <v>15</v>
       </c>
       <c r="B184" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C184" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D184">
         <v>6</v>
       </c>
       <c r="E184" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="185" spans="1:5">
@@ -4300,16 +4288,16 @@
         <v>15</v>
       </c>
       <c r="B185" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C185" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D185">
         <v>2</v>
       </c>
       <c r="E185" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="186" spans="1:5">
@@ -4317,16 +4305,16 @@
         <v>15</v>
       </c>
       <c r="B186" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C186" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D186">
         <v>20</v>
       </c>
       <c r="E186" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="187" spans="1:5">
@@ -4334,16 +4322,16 @@
         <v>15</v>
       </c>
       <c r="B187" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C187" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D187">
         <v>6</v>
       </c>
       <c r="E187" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="188" spans="1:5">
@@ -4351,16 +4339,16 @@
         <v>15</v>
       </c>
       <c r="B188" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C188" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D188">
         <v>2</v>
       </c>
       <c r="E188" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="189" spans="1:5">
@@ -4368,16 +4356,16 @@
         <v>15</v>
       </c>
       <c r="B189" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C189" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D189">
         <v>4</v>
       </c>
       <c r="E189" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="190" spans="1:5">
@@ -4385,16 +4373,16 @@
         <v>15</v>
       </c>
       <c r="B190" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C190" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D190">
         <v>10</v>
       </c>
       <c r="E190" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="191" spans="1:5">
@@ -4402,16 +4390,16 @@
         <v>15</v>
       </c>
       <c r="B191" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C191" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D191">
         <v>8</v>
       </c>
       <c r="E191" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="192" spans="1:5">
@@ -4419,16 +4407,16 @@
         <v>15</v>
       </c>
       <c r="B192" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C192" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D192">
         <v>4</v>
       </c>
       <c r="E192" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="193" spans="1:5">
@@ -4436,16 +4424,16 @@
         <v>15</v>
       </c>
       <c r="B193" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C193" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D193">
         <v>4</v>
       </c>
       <c r="E193" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="194" spans="1:5">
@@ -4453,16 +4441,16 @@
         <v>15</v>
       </c>
       <c r="B194" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C194" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D194">
         <v>2</v>
       </c>
       <c r="E194" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="195" spans="1:5">
@@ -4470,16 +4458,16 @@
         <v>15</v>
       </c>
       <c r="B195" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C195" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D195">
         <v>1</v>
       </c>
       <c r="E195" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="196" spans="1:5">
@@ -4487,16 +4475,16 @@
         <v>15</v>
       </c>
       <c r="B196" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C196" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D196">
         <v>1</v>
       </c>
       <c r="E196" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="197" spans="1:5">
@@ -4504,16 +4492,16 @@
         <v>15</v>
       </c>
       <c r="B197" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C197" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D197">
         <v>18</v>
       </c>
       <c r="E197" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="198" spans="1:5">
@@ -4521,16 +4509,16 @@
         <v>15</v>
       </c>
       <c r="B198" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C198" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D198">
         <v>18</v>
       </c>
       <c r="E198" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="199" spans="1:5">
@@ -4538,16 +4526,16 @@
         <v>15</v>
       </c>
       <c r="B199" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C199" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D199">
         <v>48</v>
       </c>
       <c r="E199" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="200" spans="1:5">
@@ -4555,16 +4543,16 @@
         <v>15</v>
       </c>
       <c r="B200" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C200" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D200">
         <v>1</v>
       </c>
       <c r="E200" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="201" spans="1:5">
@@ -4572,16 +4560,16 @@
         <v>15</v>
       </c>
       <c r="B201" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C201" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D201">
         <v>1</v>
       </c>
       <c r="E201" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="202" spans="1:5">
@@ -4589,16 +4577,16 @@
         <v>15</v>
       </c>
       <c r="B202" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C202" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D202">
         <v>1</v>
       </c>
       <c r="E202" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="203" spans="1:5">
@@ -4606,16 +4594,16 @@
         <v>15</v>
       </c>
       <c r="B203" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C203" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D203">
         <v>1</v>
       </c>
       <c r="E203" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="204" spans="1:5">
@@ -4623,16 +4611,16 @@
         <v>15</v>
       </c>
       <c r="B204" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C204" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D204">
         <v>2</v>
       </c>
       <c r="E204" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="205" spans="1:5">
@@ -4640,16 +4628,16 @@
         <v>15</v>
       </c>
       <c r="B205" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C205" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D205">
         <v>1</v>
       </c>
       <c r="E205" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="206" spans="1:5">
@@ -4657,16 +4645,16 @@
         <v>15</v>
       </c>
       <c r="B206" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C206" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D206">
         <v>1</v>
       </c>
       <c r="E206" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="207" spans="1:5">
@@ -4674,16 +4662,16 @@
         <v>15</v>
       </c>
       <c r="B207" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C207" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D207">
         <v>12</v>
       </c>
       <c r="E207" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="208" spans="1:5">
@@ -4691,16 +4679,16 @@
         <v>15</v>
       </c>
       <c r="B208" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C208" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D208">
         <v>1</v>
       </c>
       <c r="E208" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="209" spans="1:5">
@@ -4708,16 +4696,16 @@
         <v>15</v>
       </c>
       <c r="B209" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C209" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D209">
         <v>3</v>
       </c>
       <c r="E209" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="210" spans="1:5">
@@ -4725,16 +4713,16 @@
         <v>15</v>
       </c>
       <c r="B210" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C210" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D210">
         <v>2</v>
       </c>
       <c r="E210" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="211" spans="1:5">
@@ -4742,16 +4730,16 @@
         <v>15</v>
       </c>
       <c r="B211" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C211" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D211">
         <v>1</v>
       </c>
       <c r="E211" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="212" spans="1:5">
@@ -4759,16 +4747,16 @@
         <v>15</v>
       </c>
       <c r="B212" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C212" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D212">
         <v>1</v>
       </c>
       <c r="E212" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="213" spans="1:5">
@@ -4776,16 +4764,16 @@
         <v>15</v>
       </c>
       <c r="B213" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C213" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D213">
         <v>1</v>
       </c>
       <c r="E213" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="214" spans="1:5">
@@ -4793,16 +4781,16 @@
         <v>15</v>
       </c>
       <c r="B214" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C214" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D214">
         <v>1</v>
       </c>
       <c r="E214" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="215" spans="1:5">
@@ -4810,16 +4798,16 @@
         <v>16</v>
       </c>
       <c r="B215" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C215" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D215">
         <v>16</v>
       </c>
       <c r="E215" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="216" spans="1:5">
@@ -4827,16 +4815,16 @@
         <v>16</v>
       </c>
       <c r="B216" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C216" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D216">
         <v>8</v>
       </c>
       <c r="E216" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="217" spans="1:5">
@@ -4844,16 +4832,16 @@
         <v>16</v>
       </c>
       <c r="B217" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C217" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D217">
         <v>16</v>
       </c>
       <c r="E217" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="218" spans="1:5">
@@ -4861,16 +4849,16 @@
         <v>16</v>
       </c>
       <c r="B218" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C218" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D218">
         <v>16</v>
       </c>
       <c r="E218" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="219" spans="1:5">
@@ -4878,16 +4866,16 @@
         <v>16</v>
       </c>
       <c r="B219" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C219" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D219">
         <v>14</v>
       </c>
       <c r="E219" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="220" spans="1:5">
@@ -4895,16 +4883,16 @@
         <v>16</v>
       </c>
       <c r="B220" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C220" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D220">
         <v>16</v>
       </c>
       <c r="E220" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="221" spans="1:5">
@@ -4912,16 +4900,16 @@
         <v>16</v>
       </c>
       <c r="B221" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C221" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D221">
         <v>8</v>
       </c>
       <c r="E221" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="222" spans="1:5">
@@ -4929,16 +4917,16 @@
         <v>16</v>
       </c>
       <c r="B222" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C222" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D222">
         <v>45</v>
       </c>
       <c r="E222" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="223" spans="1:5">
@@ -4946,16 +4934,16 @@
         <v>16</v>
       </c>
       <c r="B223" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C223" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D223">
         <v>16</v>
       </c>
       <c r="E223" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="224" spans="1:5">
@@ -4963,16 +4951,16 @@
         <v>16</v>
       </c>
       <c r="B224" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C224" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D224">
         <v>8</v>
       </c>
       <c r="E224" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="225" spans="1:5">
@@ -4980,16 +4968,16 @@
         <v>16</v>
       </c>
       <c r="B225" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C225" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D225">
         <v>24</v>
       </c>
       <c r="E225" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="226" spans="1:5">
@@ -4997,16 +4985,16 @@
         <v>16</v>
       </c>
       <c r="B226" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C226" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D226">
         <v>24</v>
       </c>
       <c r="E226" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="227" spans="1:5">
@@ -5014,16 +5002,16 @@
         <v>16</v>
       </c>
       <c r="B227" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C227" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D227">
         <v>15</v>
       </c>
       <c r="E227" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="228" spans="1:5">
@@ -5031,16 +5019,16 @@
         <v>16</v>
       </c>
       <c r="B228" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C228" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D228">
         <v>24</v>
       </c>
       <c r="E228" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="229" spans="1:5">
@@ -5048,16 +5036,16 @@
         <v>16</v>
       </c>
       <c r="B229" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C229" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D229">
         <v>24</v>
       </c>
       <c r="E229" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="230" spans="1:5">
@@ -5065,16 +5053,16 @@
         <v>16</v>
       </c>
       <c r="B230" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C230" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D230">
         <v>16</v>
       </c>
       <c r="E230" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="231" spans="1:5">
@@ -5082,16 +5070,16 @@
         <v>16</v>
       </c>
       <c r="B231" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C231" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D231">
         <v>8</v>
       </c>
       <c r="E231" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="232" spans="1:5">
@@ -5099,16 +5087,16 @@
         <v>16</v>
       </c>
       <c r="B232" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C232" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D232">
         <v>48</v>
       </c>
       <c r="E232" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="233" spans="1:5">
@@ -5116,16 +5104,16 @@
         <v>16</v>
       </c>
       <c r="B233" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C233" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D233">
         <v>24</v>
       </c>
       <c r="E233" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="234" spans="1:5">
@@ -5133,16 +5121,16 @@
         <v>16</v>
       </c>
       <c r="B234" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C234" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D234">
         <v>16</v>
       </c>
       <c r="E234" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="235" spans="1:5">
@@ -5150,16 +5138,16 @@
         <v>16</v>
       </c>
       <c r="B235" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C235" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D235">
         <v>8</v>
       </c>
       <c r="E235" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="236" spans="1:5">
@@ -5167,16 +5155,16 @@
         <v>16</v>
       </c>
       <c r="B236" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C236" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D236">
         <v>7</v>
       </c>
       <c r="E236" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="237" spans="1:5">
@@ -5184,16 +5172,16 @@
         <v>16</v>
       </c>
       <c r="B237" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C237" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D237">
         <v>7</v>
       </c>
       <c r="E237" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="238" spans="1:5">
@@ -5201,16 +5189,16 @@
         <v>16</v>
       </c>
       <c r="B238" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C238" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D238">
         <v>24</v>
       </c>
       <c r="E238" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="239" spans="1:5">
@@ -5218,16 +5206,16 @@
         <v>16</v>
       </c>
       <c r="B239" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C239" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D239">
         <v>24</v>
       </c>
       <c r="E239" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="240" spans="1:5">
@@ -5235,16 +5223,16 @@
         <v>16</v>
       </c>
       <c r="B240" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C240" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D240">
         <v>8</v>
       </c>
       <c r="E240" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="241" spans="1:5">
@@ -5252,16 +5240,16 @@
         <v>16</v>
       </c>
       <c r="B241" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C241" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D241">
         <v>16</v>
       </c>
       <c r="E241" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="242" spans="1:5">
@@ -5269,16 +5257,16 @@
         <v>16</v>
       </c>
       <c r="B242" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C242" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D242">
         <v>8</v>
       </c>
       <c r="E242" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="243" spans="1:5">
@@ -5286,16 +5274,16 @@
         <v>16</v>
       </c>
       <c r="B243" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C243" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D243">
         <v>52</v>
       </c>
       <c r="E243" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="244" spans="1:5">
@@ -5303,16 +5291,16 @@
         <v>16</v>
       </c>
       <c r="B244" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C244" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D244">
         <v>13</v>
       </c>
       <c r="E244" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="245" spans="1:5">
@@ -5320,16 +5308,16 @@
         <v>16</v>
       </c>
       <c r="B245" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C245" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D245">
         <v>13</v>
       </c>
       <c r="E245" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="246" spans="1:5">
@@ -5337,16 +5325,16 @@
         <v>16</v>
       </c>
       <c r="B246" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C246" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D246">
         <v>27</v>
       </c>
       <c r="E246" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="247" spans="1:5">
@@ -5354,16 +5342,16 @@
         <v>16</v>
       </c>
       <c r="B247" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C247" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D247">
         <v>16</v>
       </c>
       <c r="E247" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="248" spans="1:5">
@@ -5371,16 +5359,16 @@
         <v>16</v>
       </c>
       <c r="B248" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C248" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D248">
         <v>8</v>
       </c>
       <c r="E248" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="249" spans="1:5">
@@ -5388,16 +5376,16 @@
         <v>16</v>
       </c>
       <c r="B249" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C249" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D249">
         <v>16</v>
       </c>
       <c r="E249" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="250" spans="1:5">
@@ -5405,16 +5393,16 @@
         <v>16</v>
       </c>
       <c r="B250" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C250" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D250">
         <v>8</v>
       </c>
       <c r="E250" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="251" spans="1:5">
@@ -5422,16 +5410,16 @@
         <v>16</v>
       </c>
       <c r="B251" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C251" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D251">
         <v>16</v>
       </c>
       <c r="E251" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="252" spans="1:5">
@@ -5439,16 +5427,16 @@
         <v>16</v>
       </c>
       <c r="B252" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C252" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D252">
         <v>8</v>
       </c>
       <c r="E252" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="253" spans="1:5">
@@ -5456,16 +5444,16 @@
         <v>16</v>
       </c>
       <c r="B253" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C253" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D253">
         <v>53</v>
       </c>
       <c r="E253" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="254" spans="1:5">
@@ -5473,16 +5461,16 @@
         <v>16</v>
       </c>
       <c r="B254" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C254" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D254">
         <v>8</v>
       </c>
       <c r="E254" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="255" spans="1:5">
@@ -5490,16 +5478,16 @@
         <v>16</v>
       </c>
       <c r="B255" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C255" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D255">
         <v>16</v>
       </c>
       <c r="E255" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="256" spans="1:5">
@@ -5507,16 +5495,16 @@
         <v>16</v>
       </c>
       <c r="B256" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C256" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D256">
         <v>8</v>
       </c>
       <c r="E256" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="257" spans="1:5">
@@ -5524,16 +5512,16 @@
         <v>16</v>
       </c>
       <c r="B257" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C257" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D257">
         <v>16</v>
       </c>
       <c r="E257" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="258" spans="1:5">
@@ -5541,16 +5529,16 @@
         <v>16</v>
       </c>
       <c r="B258" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C258" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D258">
         <v>8</v>
       </c>
       <c r="E258" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="259" spans="1:5">
@@ -5558,16 +5546,16 @@
         <v>16</v>
       </c>
       <c r="B259" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C259" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D259">
         <v>16</v>
       </c>
       <c r="E259" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="260" spans="1:5">
@@ -5575,16 +5563,16 @@
         <v>16</v>
       </c>
       <c r="B260" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C260" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D260">
         <v>8</v>
       </c>
       <c r="E260" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="261" spans="1:5">
@@ -5592,16 +5580,16 @@
         <v>16</v>
       </c>
       <c r="B261" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C261" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D261">
         <v>16</v>
       </c>
       <c r="E261" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="262" spans="1:5">
@@ -5609,16 +5597,16 @@
         <v>16</v>
       </c>
       <c r="B262" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C262" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D262">
         <v>16</v>
       </c>
       <c r="E262" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="263" spans="1:5">
@@ -5626,16 +5614,16 @@
         <v>16</v>
       </c>
       <c r="B263" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C263" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D263">
         <v>24</v>
       </c>
       <c r="E263" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="264" spans="1:5">
@@ -5643,16 +5631,16 @@
         <v>16</v>
       </c>
       <c r="B264" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C264" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D264">
         <v>24</v>
       </c>
       <c r="E264" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="265" spans="1:5">
@@ -5660,16 +5648,16 @@
         <v>16</v>
       </c>
       <c r="B265" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C265" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D265">
         <v>16</v>
       </c>
       <c r="E265" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="266" spans="1:5">
@@ -5677,16 +5665,16 @@
         <v>16</v>
       </c>
       <c r="B266" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C266" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D266">
         <v>13</v>
       </c>
       <c r="E266" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="267" spans="1:5">
@@ -5694,16 +5682,16 @@
         <v>16</v>
       </c>
       <c r="B267" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C267" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D267">
         <v>61</v>
       </c>
       <c r="E267" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="268" spans="1:5">
@@ -5711,16 +5699,16 @@
         <v>16</v>
       </c>
       <c r="B268" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C268" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D268">
         <v>61</v>
       </c>
       <c r="E268" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="269" spans="1:5">
@@ -5728,16 +5716,16 @@
         <v>16</v>
       </c>
       <c r="B269" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C269" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D269">
         <v>2</v>
       </c>
       <c r="E269" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="270" spans="1:5">
@@ -5745,16 +5733,16 @@
         <v>16</v>
       </c>
       <c r="B270" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C270" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D270">
         <v>3</v>
       </c>
       <c r="E270" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="271" spans="1:5">
@@ -5762,16 +5750,16 @@
         <v>16</v>
       </c>
       <c r="B271" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C271" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D271">
         <v>1</v>
       </c>
       <c r="E271" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="272" spans="1:5">
@@ -5779,16 +5767,16 @@
         <v>16</v>
       </c>
       <c r="B272" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C272" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D272">
         <v>9</v>
       </c>
       <c r="E272" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="273" spans="1:5">
@@ -5796,16 +5784,16 @@
         <v>16</v>
       </c>
       <c r="B273" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C273" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D273">
         <v>3</v>
       </c>
       <c r="E273" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="274" spans="1:5">
@@ -5813,16 +5801,16 @@
         <v>16</v>
       </c>
       <c r="B274" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C274" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D274">
         <v>5</v>
       </c>
       <c r="E274" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="275" spans="1:5">
@@ -5830,16 +5818,16 @@
         <v>16</v>
       </c>
       <c r="B275" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C275" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D275">
         <v>3</v>
       </c>
       <c r="E275" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="276" spans="1:5">
@@ -5847,16 +5835,16 @@
         <v>16</v>
       </c>
       <c r="B276" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C276" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D276">
         <v>3</v>
       </c>
       <c r="E276" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="277" spans="1:5">
@@ -5864,16 +5852,16 @@
         <v>17</v>
       </c>
       <c r="B277" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C277" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="D277">
         <v>1</v>
       </c>
       <c r="E277" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="278" spans="1:5">
@@ -5881,16 +5869,16 @@
         <v>17</v>
       </c>
       <c r="B278" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C278" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="D278">
         <v>1</v>
       </c>
       <c r="E278" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="279" spans="1:5">
@@ -5898,16 +5886,16 @@
         <v>17</v>
       </c>
       <c r="B279" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C279" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="D279">
         <v>4</v>
       </c>
       <c r="E279" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="280" spans="1:5">
@@ -5915,16 +5903,16 @@
         <v>17</v>
       </c>
       <c r="B280" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C280" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="D280">
         <v>1</v>
       </c>
       <c r="E280" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="281" spans="1:5">
@@ -5932,16 +5920,16 @@
         <v>17</v>
       </c>
       <c r="B281" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C281" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="D281">
         <v>3</v>
       </c>
       <c r="E281" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="282" spans="1:5">
@@ -5949,50 +5937,16 @@
         <v>17</v>
       </c>
       <c r="B282" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C282" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="D282">
         <v>1</v>
       </c>
       <c r="E282" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="283" spans="1:5">
-      <c r="A283" t="s">
-        <v>18</v>
-      </c>
-      <c r="B283" t="s">
-        <v>260</v>
-      </c>
-      <c r="C283" t="s">
-        <v>271</v>
-      </c>
-      <c r="D283">
-        <v>1</v>
-      </c>
-      <c r="E283" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="284" spans="1:5">
-      <c r="A284" t="s">
-        <v>19</v>
-      </c>
-      <c r="B284" t="s">
-        <v>261</v>
-      </c>
-      <c r="C284" t="s">
-        <v>266</v>
-      </c>
-      <c r="D284">
-        <v>200</v>
-      </c>
-      <c r="E284" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
   </sheetData>

--- a/data/BD_Requerimientos_POs.xlsx
+++ b/data/BD_Requerimientos_POs.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1129" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1137" uniqueCount="273">
   <si>
     <t>PO</t>
   </si>
@@ -70,6 +70,12 @@
     <t>26083382</t>
   </si>
   <si>
+    <t>26083394</t>
+  </si>
+  <si>
+    <t>26083428</t>
+  </si>
+  <si>
     <t>11-D-6165-01</t>
   </si>
   <si>
@@ -788,6 +794,12 @@
   </si>
   <si>
     <t>PP14805-04</t>
+  </si>
+  <si>
+    <t>12-D-6030-10</t>
+  </si>
+  <si>
+    <t>PP9247</t>
   </si>
   <si>
     <t>07/09/2026</t>
@@ -1152,7 +1164,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E282"/>
+  <dimension ref="A1:E284"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1177,16 +1189,16 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D2">
         <v>320</v>
       </c>
       <c r="E2" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1194,16 +1206,16 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D3">
         <v>192</v>
       </c>
       <c r="E3" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1211,16 +1223,16 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D4">
         <v>224</v>
       </c>
       <c r="E4" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1228,16 +1240,16 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D5">
         <v>224</v>
       </c>
       <c r="E5" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1245,16 +1257,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D6">
         <v>160</v>
       </c>
       <c r="E6" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1262,16 +1274,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D7">
         <v>160</v>
       </c>
       <c r="E7" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1279,16 +1291,16 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D8">
         <v>160</v>
       </c>
       <c r="E8" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -1296,16 +1308,16 @@
         <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D9">
         <v>128</v>
       </c>
       <c r="E9" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -1313,16 +1325,16 @@
         <v>5</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D10">
         <v>160</v>
       </c>
       <c r="E10" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -1330,16 +1342,16 @@
         <v>5</v>
       </c>
       <c r="B11" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D11">
         <v>160</v>
       </c>
       <c r="E11" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -1347,16 +1359,16 @@
         <v>5</v>
       </c>
       <c r="B12" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D12">
         <v>96</v>
       </c>
       <c r="E12" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -1364,16 +1376,16 @@
         <v>5</v>
       </c>
       <c r="B13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C13" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D13">
         <v>96</v>
       </c>
       <c r="E13" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -1381,16 +1393,16 @@
         <v>5</v>
       </c>
       <c r="B14" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C14" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D14">
         <v>96</v>
       </c>
       <c r="E14" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -1398,16 +1410,16 @@
         <v>5</v>
       </c>
       <c r="B15" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C15" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D15">
         <v>112</v>
       </c>
       <c r="E15" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -1415,16 +1427,16 @@
         <v>5</v>
       </c>
       <c r="B16" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C16" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D16">
         <v>112</v>
       </c>
       <c r="E16" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1432,16 +1444,16 @@
         <v>5</v>
       </c>
       <c r="B17" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C17" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D17">
         <v>112</v>
       </c>
       <c r="E17" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1449,16 +1461,16 @@
         <v>5</v>
       </c>
       <c r="B18" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C18" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D18">
         <v>80</v>
       </c>
       <c r="E18" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1466,16 +1478,16 @@
         <v>5</v>
       </c>
       <c r="B19" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C19" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D19">
         <v>80</v>
       </c>
       <c r="E19" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1483,16 +1495,16 @@
         <v>5</v>
       </c>
       <c r="B20" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C20" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D20">
         <v>80</v>
       </c>
       <c r="E20" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1500,16 +1512,16 @@
         <v>5</v>
       </c>
       <c r="B21" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C21" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D21">
         <v>64</v>
       </c>
       <c r="E21" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1517,16 +1529,16 @@
         <v>5</v>
       </c>
       <c r="B22" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C22" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D22">
         <v>80</v>
       </c>
       <c r="E22" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1534,16 +1546,16 @@
         <v>5</v>
       </c>
       <c r="B23" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C23" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D23">
         <v>64</v>
       </c>
       <c r="E23" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1551,16 +1563,16 @@
         <v>5</v>
       </c>
       <c r="B24" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C24" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D24">
         <v>64</v>
       </c>
       <c r="E24" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1568,16 +1580,16 @@
         <v>5</v>
       </c>
       <c r="B25" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C25" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D25">
         <v>64</v>
       </c>
       <c r="E25" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1585,16 +1597,16 @@
         <v>5</v>
       </c>
       <c r="B26" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C26" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D26">
         <v>64</v>
       </c>
       <c r="E26" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1602,16 +1614,16 @@
         <v>5</v>
       </c>
       <c r="B27" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C27" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D27">
         <v>64</v>
       </c>
       <c r="E27" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1619,16 +1631,16 @@
         <v>5</v>
       </c>
       <c r="B28" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C28" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D28">
         <v>64</v>
       </c>
       <c r="E28" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -1636,16 +1648,16 @@
         <v>5</v>
       </c>
       <c r="B29" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C29" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D29">
         <v>40</v>
       </c>
       <c r="E29" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -1653,16 +1665,16 @@
         <v>5</v>
       </c>
       <c r="B30" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C30" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D30">
         <v>40</v>
       </c>
       <c r="E30" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -1670,16 +1682,16 @@
         <v>5</v>
       </c>
       <c r="B31" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C31" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D31">
         <v>40</v>
       </c>
       <c r="E31" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -1687,16 +1699,16 @@
         <v>5</v>
       </c>
       <c r="B32" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C32" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D32">
         <v>32</v>
       </c>
       <c r="E32" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -1704,16 +1716,16 @@
         <v>5</v>
       </c>
       <c r="B33" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C33" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D33">
         <v>40</v>
       </c>
       <c r="E33" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -1721,16 +1733,16 @@
         <v>5</v>
       </c>
       <c r="B34" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C34" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D34">
         <v>40</v>
       </c>
       <c r="E34" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -1738,16 +1750,16 @@
         <v>5</v>
       </c>
       <c r="B35" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C35" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D35">
         <v>40</v>
       </c>
       <c r="E35" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -1755,16 +1767,16 @@
         <v>5</v>
       </c>
       <c r="B36" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C36" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D36">
         <v>40</v>
       </c>
       <c r="E36" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -1772,16 +1784,16 @@
         <v>5</v>
       </c>
       <c r="B37" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C37" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D37">
         <v>32</v>
       </c>
       <c r="E37" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -1789,16 +1801,16 @@
         <v>5</v>
       </c>
       <c r="B38" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C38" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D38">
         <v>40</v>
       </c>
       <c r="E38" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -1806,16 +1818,16 @@
         <v>5</v>
       </c>
       <c r="B39" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C39" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D39">
         <v>32</v>
       </c>
       <c r="E39" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -1823,16 +1835,16 @@
         <v>5</v>
       </c>
       <c r="B40" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C40" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D40">
         <v>32</v>
       </c>
       <c r="E40" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -1840,16 +1852,16 @@
         <v>5</v>
       </c>
       <c r="B41" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C41" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D41">
         <v>32</v>
       </c>
       <c r="E41" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -1857,16 +1869,16 @@
         <v>5</v>
       </c>
       <c r="B42" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C42" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D42">
         <v>32</v>
       </c>
       <c r="E42" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -1874,16 +1886,16 @@
         <v>5</v>
       </c>
       <c r="B43" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C43" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D43">
         <v>32</v>
       </c>
       <c r="E43" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -1891,16 +1903,16 @@
         <v>5</v>
       </c>
       <c r="B44" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C44" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D44">
         <v>40</v>
       </c>
       <c r="E44" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -1908,16 +1920,16 @@
         <v>5</v>
       </c>
       <c r="B45" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C45" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D45">
         <v>32</v>
       </c>
       <c r="E45" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -1925,16 +1937,16 @@
         <v>5</v>
       </c>
       <c r="B46" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C46" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D46">
         <v>32</v>
       </c>
       <c r="E46" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -1942,16 +1954,16 @@
         <v>6</v>
       </c>
       <c r="B47" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C47" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D47">
         <v>4</v>
       </c>
       <c r="E47" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -1959,16 +1971,16 @@
         <v>6</v>
       </c>
       <c r="B48" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C48" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D48">
         <v>73</v>
       </c>
       <c r="E48" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -1976,16 +1988,16 @@
         <v>7</v>
       </c>
       <c r="B49" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C49" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D49">
         <v>32</v>
       </c>
       <c r="E49" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -1993,16 +2005,16 @@
         <v>7</v>
       </c>
       <c r="B50" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C50" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D50">
         <v>32</v>
       </c>
       <c r="E50" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -2010,16 +2022,16 @@
         <v>7</v>
       </c>
       <c r="B51" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C51" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D51">
         <v>81</v>
       </c>
       <c r="E51" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -2027,16 +2039,16 @@
         <v>7</v>
       </c>
       <c r="B52" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C52" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D52">
         <v>85</v>
       </c>
       <c r="E52" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -2044,16 +2056,16 @@
         <v>7</v>
       </c>
       <c r="B53" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C53" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D53">
         <v>85</v>
       </c>
       <c r="E53" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -2061,16 +2073,16 @@
         <v>7</v>
       </c>
       <c r="B54" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C54" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D54">
         <v>4</v>
       </c>
       <c r="E54" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -2078,16 +2090,16 @@
         <v>7</v>
       </c>
       <c r="B55" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C55" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D55">
         <v>4</v>
       </c>
       <c r="E55" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -2095,16 +2107,16 @@
         <v>7</v>
       </c>
       <c r="B56" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C56" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D56">
         <v>16</v>
       </c>
       <c r="E56" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -2112,16 +2124,16 @@
         <v>7</v>
       </c>
       <c r="B57" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C57" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D57">
         <v>154</v>
       </c>
       <c r="E57" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -2129,16 +2141,16 @@
         <v>7</v>
       </c>
       <c r="B58" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C58" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D58">
         <v>8</v>
       </c>
       <c r="E58" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -2146,16 +2158,16 @@
         <v>7</v>
       </c>
       <c r="B59" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C59" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D59">
         <v>8</v>
       </c>
       <c r="E59" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -2163,16 +2175,16 @@
         <v>7</v>
       </c>
       <c r="B60" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C60" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D60">
         <v>73</v>
       </c>
       <c r="E60" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -2180,16 +2192,16 @@
         <v>7</v>
       </c>
       <c r="B61" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C61" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D61">
         <v>16</v>
       </c>
       <c r="E61" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -2197,16 +2209,16 @@
         <v>7</v>
       </c>
       <c r="B62" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C62" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D62">
         <v>8</v>
       </c>
       <c r="E62" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -2214,16 +2226,16 @@
         <v>7</v>
       </c>
       <c r="B63" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C63" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D63">
         <v>4</v>
       </c>
       <c r="E63" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -2231,16 +2243,16 @@
         <v>7</v>
       </c>
       <c r="B64" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C64" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D64">
         <v>73</v>
       </c>
       <c r="E64" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -2248,16 +2260,16 @@
         <v>7</v>
       </c>
       <c r="B65" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C65" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D65">
         <v>73</v>
       </c>
       <c r="E65" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -2265,16 +2277,16 @@
         <v>7</v>
       </c>
       <c r="B66" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C66" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D66">
         <v>73</v>
       </c>
       <c r="E66" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -2282,16 +2294,16 @@
         <v>7</v>
       </c>
       <c r="B67" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C67" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D67">
         <v>4</v>
       </c>
       <c r="E67" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -2299,16 +2311,16 @@
         <v>7</v>
       </c>
       <c r="B68" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C68" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D68">
         <v>8</v>
       </c>
       <c r="E68" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -2316,16 +2328,16 @@
         <v>7</v>
       </c>
       <c r="B69" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C69" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D69">
         <v>8</v>
       </c>
       <c r="E69" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -2333,16 +2345,16 @@
         <v>7</v>
       </c>
       <c r="B70" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C70" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D70">
         <v>73</v>
       </c>
       <c r="E70" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="71" spans="1:5">
@@ -2350,16 +2362,16 @@
         <v>7</v>
       </c>
       <c r="B71" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C71" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D71">
         <v>150</v>
       </c>
       <c r="E71" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -2367,16 +2379,16 @@
         <v>8</v>
       </c>
       <c r="B72" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C72" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D72">
         <v>32</v>
       </c>
       <c r="E72" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="73" spans="1:5">
@@ -2384,16 +2396,16 @@
         <v>9</v>
       </c>
       <c r="B73" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C73" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D73">
         <v>8</v>
       </c>
       <c r="E73" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="74" spans="1:5">
@@ -2401,16 +2413,16 @@
         <v>10</v>
       </c>
       <c r="B74" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C74" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D74">
         <v>40</v>
       </c>
       <c r="E74" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -2418,16 +2430,16 @@
         <v>11</v>
       </c>
       <c r="B75" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C75" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D75">
         <v>1</v>
       </c>
       <c r="E75" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="76" spans="1:5">
@@ -2435,16 +2447,16 @@
         <v>12</v>
       </c>
       <c r="B76" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C76" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D76">
         <v>128</v>
       </c>
       <c r="E76" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="77" spans="1:5">
@@ -2452,16 +2464,16 @@
         <v>12</v>
       </c>
       <c r="B77" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C77" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D77">
         <v>32</v>
       </c>
       <c r="E77" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="78" spans="1:5">
@@ -2469,16 +2481,16 @@
         <v>12</v>
       </c>
       <c r="B78" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C78" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D78">
         <v>40</v>
       </c>
       <c r="E78" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="79" spans="1:5">
@@ -2486,16 +2498,16 @@
         <v>12</v>
       </c>
       <c r="B79" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C79" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D79">
         <v>40</v>
       </c>
       <c r="E79" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="80" spans="1:5">
@@ -2503,16 +2515,16 @@
         <v>12</v>
       </c>
       <c r="B80" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C80" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D80">
         <v>64</v>
       </c>
       <c r="E80" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="81" spans="1:5">
@@ -2520,16 +2532,16 @@
         <v>12</v>
       </c>
       <c r="B81" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C81" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D81">
         <v>64</v>
       </c>
       <c r="E81" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="82" spans="1:5">
@@ -2537,16 +2549,16 @@
         <v>13</v>
       </c>
       <c r="B82" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C82" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="D82">
         <v>32</v>
       </c>
       <c r="E82" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="83" spans="1:5">
@@ -2554,16 +2566,16 @@
         <v>13</v>
       </c>
       <c r="B83" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C83" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="D83">
         <v>40</v>
       </c>
       <c r="E83" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="84" spans="1:5">
@@ -2571,16 +2583,16 @@
         <v>13</v>
       </c>
       <c r="B84" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C84" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="D84">
         <v>40</v>
       </c>
       <c r="E84" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="85" spans="1:5">
@@ -2588,16 +2600,16 @@
         <v>14</v>
       </c>
       <c r="B85" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C85" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="D85">
         <v>20</v>
       </c>
       <c r="E85" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="86" spans="1:5">
@@ -2605,16 +2617,16 @@
         <v>14</v>
       </c>
       <c r="B86" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C86" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="D86">
         <v>32</v>
       </c>
       <c r="E86" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="87" spans="1:5">
@@ -2622,16 +2634,16 @@
         <v>14</v>
       </c>
       <c r="B87" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C87" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="D87">
         <v>64</v>
       </c>
       <c r="E87" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="88" spans="1:5">
@@ -2639,16 +2651,16 @@
         <v>15</v>
       </c>
       <c r="B88" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C88" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D88">
         <v>2</v>
       </c>
       <c r="E88" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="89" spans="1:5">
@@ -2656,16 +2668,16 @@
         <v>15</v>
       </c>
       <c r="B89" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C89" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D89">
         <v>2</v>
       </c>
       <c r="E89" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="90" spans="1:5">
@@ -2673,16 +2685,16 @@
         <v>15</v>
       </c>
       <c r="B90" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C90" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D90">
         <v>2</v>
       </c>
       <c r="E90" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="91" spans="1:5">
@@ -2690,16 +2702,16 @@
         <v>15</v>
       </c>
       <c r="B91" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C91" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D91">
         <v>6</v>
       </c>
       <c r="E91" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="92" spans="1:5">
@@ -2707,16 +2719,16 @@
         <v>15</v>
       </c>
       <c r="B92" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C92" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D92">
         <v>2</v>
       </c>
       <c r="E92" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="93" spans="1:5">
@@ -2724,16 +2736,16 @@
         <v>15</v>
       </c>
       <c r="B93" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C93" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D93">
         <v>9</v>
       </c>
       <c r="E93" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="94" spans="1:5">
@@ -2741,16 +2753,16 @@
         <v>15</v>
       </c>
       <c r="B94" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C94" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D94">
         <v>8</v>
       </c>
       <c r="E94" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="95" spans="1:5">
@@ -2758,16 +2770,16 @@
         <v>15</v>
       </c>
       <c r="B95" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C95" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D95">
         <v>8</v>
       </c>
       <c r="E95" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="96" spans="1:5">
@@ -2775,16 +2787,16 @@
         <v>15</v>
       </c>
       <c r="B96" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C96" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D96">
         <v>2</v>
       </c>
       <c r="E96" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="97" spans="1:5">
@@ -2792,16 +2804,16 @@
         <v>15</v>
       </c>
       <c r="B97" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C97" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D97">
         <v>2</v>
       </c>
       <c r="E97" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="98" spans="1:5">
@@ -2809,16 +2821,16 @@
         <v>15</v>
       </c>
       <c r="B98" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C98" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D98">
         <v>2</v>
       </c>
       <c r="E98" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="99" spans="1:5">
@@ -2826,16 +2838,16 @@
         <v>15</v>
       </c>
       <c r="B99" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C99" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D99">
         <v>2</v>
       </c>
       <c r="E99" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="100" spans="1:5">
@@ -2843,16 +2855,16 @@
         <v>15</v>
       </c>
       <c r="B100" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C100" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D100">
         <v>1</v>
       </c>
       <c r="E100" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="101" spans="1:5">
@@ -2860,16 +2872,16 @@
         <v>15</v>
       </c>
       <c r="B101" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C101" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D101">
         <v>1</v>
       </c>
       <c r="E101" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="102" spans="1:5">
@@ -2877,16 +2889,16 @@
         <v>15</v>
       </c>
       <c r="B102" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C102" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D102">
         <v>1</v>
       </c>
       <c r="E102" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="103" spans="1:5">
@@ -2894,16 +2906,16 @@
         <v>15</v>
       </c>
       <c r="B103" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C103" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D103">
         <v>2</v>
       </c>
       <c r="E103" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="104" spans="1:5">
@@ -2911,16 +2923,16 @@
         <v>15</v>
       </c>
       <c r="B104" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C104" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D104">
         <v>6</v>
       </c>
       <c r="E104" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="105" spans="1:5">
@@ -2928,16 +2940,16 @@
         <v>15</v>
       </c>
       <c r="B105" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C105" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D105">
         <v>2</v>
       </c>
       <c r="E105" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="106" spans="1:5">
@@ -2945,16 +2957,16 @@
         <v>15</v>
       </c>
       <c r="B106" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C106" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D106">
         <v>1</v>
       </c>
       <c r="E106" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="107" spans="1:5">
@@ -2962,16 +2974,16 @@
         <v>15</v>
       </c>
       <c r="B107" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C107" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D107">
         <v>1</v>
       </c>
       <c r="E107" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="108" spans="1:5">
@@ -2979,16 +2991,16 @@
         <v>15</v>
       </c>
       <c r="B108" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C108" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D108">
         <v>1</v>
       </c>
       <c r="E108" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="109" spans="1:5">
@@ -2996,16 +3008,16 @@
         <v>15</v>
       </c>
       <c r="B109" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C109" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D109">
         <v>1</v>
       </c>
       <c r="E109" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="110" spans="1:5">
@@ -3013,16 +3025,16 @@
         <v>15</v>
       </c>
       <c r="B110" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C110" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D110">
         <v>1</v>
       </c>
       <c r="E110" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="111" spans="1:5">
@@ -3030,16 +3042,16 @@
         <v>15</v>
       </c>
       <c r="B111" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C111" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D111">
         <v>18</v>
       </c>
       <c r="E111" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="112" spans="1:5">
@@ -3047,16 +3059,16 @@
         <v>15</v>
       </c>
       <c r="B112" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C112" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D112">
         <v>6</v>
       </c>
       <c r="E112" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="113" spans="1:5">
@@ -3064,16 +3076,16 @@
         <v>15</v>
       </c>
       <c r="B113" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C113" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D113">
         <v>2</v>
       </c>
       <c r="E113" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="114" spans="1:5">
@@ -3081,16 +3093,16 @@
         <v>15</v>
       </c>
       <c r="B114" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C114" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D114">
         <v>2</v>
       </c>
       <c r="E114" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="115" spans="1:5">
@@ -3098,16 +3110,16 @@
         <v>15</v>
       </c>
       <c r="B115" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C115" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D115">
         <v>2</v>
       </c>
       <c r="E115" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="116" spans="1:5">
@@ -3115,16 +3127,16 @@
         <v>15</v>
       </c>
       <c r="B116" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C116" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D116">
         <v>6</v>
       </c>
       <c r="E116" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="117" spans="1:5">
@@ -3132,16 +3144,16 @@
         <v>15</v>
       </c>
       <c r="B117" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C117" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D117">
         <v>6</v>
       </c>
       <c r="E117" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="118" spans="1:5">
@@ -3149,16 +3161,16 @@
         <v>15</v>
       </c>
       <c r="B118" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C118" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D118">
         <v>2</v>
       </c>
       <c r="E118" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="119" spans="1:5">
@@ -3166,16 +3178,16 @@
         <v>15</v>
       </c>
       <c r="B119" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C119" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D119">
         <v>156</v>
       </c>
       <c r="E119" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="120" spans="1:5">
@@ -3183,16 +3195,16 @@
         <v>15</v>
       </c>
       <c r="B120" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C120" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D120">
         <v>52</v>
       </c>
       <c r="E120" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="121" spans="1:5">
@@ -3200,16 +3212,16 @@
         <v>15</v>
       </c>
       <c r="B121" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C121" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D121">
         <v>24</v>
       </c>
       <c r="E121" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="122" spans="1:5">
@@ -3217,16 +3229,16 @@
         <v>15</v>
       </c>
       <c r="B122" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C122" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D122">
         <v>8</v>
       </c>
       <c r="E122" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="123" spans="1:5">
@@ -3234,16 +3246,16 @@
         <v>15</v>
       </c>
       <c r="B123" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C123" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D123">
         <v>16</v>
       </c>
       <c r="E123" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="124" spans="1:5">
@@ -3251,16 +3263,16 @@
         <v>15</v>
       </c>
       <c r="B124" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C124" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D124">
         <v>16</v>
       </c>
       <c r="E124" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="125" spans="1:5">
@@ -3268,16 +3280,16 @@
         <v>15</v>
       </c>
       <c r="B125" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C125" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D125">
         <v>6</v>
       </c>
       <c r="E125" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="126" spans="1:5">
@@ -3285,16 +3297,16 @@
         <v>15</v>
       </c>
       <c r="B126" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C126" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D126">
         <v>6</v>
       </c>
       <c r="E126" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="127" spans="1:5">
@@ -3302,16 +3314,16 @@
         <v>15</v>
       </c>
       <c r="B127" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C127" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D127">
         <v>16</v>
       </c>
       <c r="E127" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="128" spans="1:5">
@@ -3319,16 +3331,16 @@
         <v>15</v>
       </c>
       <c r="B128" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C128" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D128">
         <v>16</v>
       </c>
       <c r="E128" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="129" spans="1:5">
@@ -3336,16 +3348,16 @@
         <v>15</v>
       </c>
       <c r="B129" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C129" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D129">
         <v>2</v>
       </c>
       <c r="E129" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="130" spans="1:5">
@@ -3353,16 +3365,16 @@
         <v>15</v>
       </c>
       <c r="B130" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C130" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D130">
         <v>2</v>
       </c>
       <c r="E130" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="131" spans="1:5">
@@ -3370,16 +3382,16 @@
         <v>15</v>
       </c>
       <c r="B131" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C131" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D131">
         <v>6</v>
       </c>
       <c r="E131" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="132" spans="1:5">
@@ -3387,16 +3399,16 @@
         <v>15</v>
       </c>
       <c r="B132" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C132" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D132">
         <v>10</v>
       </c>
       <c r="E132" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="133" spans="1:5">
@@ -3404,16 +3416,16 @@
         <v>15</v>
       </c>
       <c r="B133" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C133" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D133">
         <v>8</v>
       </c>
       <c r="E133" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="134" spans="1:5">
@@ -3421,16 +3433,16 @@
         <v>15</v>
       </c>
       <c r="B134" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C134" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D134">
         <v>6</v>
       </c>
       <c r="E134" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="135" spans="1:5">
@@ -3438,16 +3450,16 @@
         <v>15</v>
       </c>
       <c r="B135" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C135" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D135">
         <v>6</v>
       </c>
       <c r="E135" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="136" spans="1:5">
@@ -3455,16 +3467,16 @@
         <v>15</v>
       </c>
       <c r="B136" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C136" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D136">
         <v>2</v>
       </c>
       <c r="E136" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="137" spans="1:5">
@@ -3472,16 +3484,16 @@
         <v>15</v>
       </c>
       <c r="B137" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C137" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D137">
         <v>4</v>
       </c>
       <c r="E137" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="138" spans="1:5">
@@ -3489,16 +3501,16 @@
         <v>15</v>
       </c>
       <c r="B138" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C138" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D138">
         <v>6</v>
       </c>
       <c r="E138" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="139" spans="1:5">
@@ -3506,16 +3518,16 @@
         <v>15</v>
       </c>
       <c r="B139" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C139" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D139">
         <v>6</v>
       </c>
       <c r="E139" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="140" spans="1:5">
@@ -3523,16 +3535,16 @@
         <v>15</v>
       </c>
       <c r="B140" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C140" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D140">
         <v>2</v>
       </c>
       <c r="E140" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="141" spans="1:5">
@@ -3540,16 +3552,16 @@
         <v>15</v>
       </c>
       <c r="B141" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C141" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D141">
         <v>8</v>
       </c>
       <c r="E141" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="142" spans="1:5">
@@ -3557,16 +3569,16 @@
         <v>15</v>
       </c>
       <c r="B142" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C142" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D142">
         <v>8</v>
       </c>
       <c r="E142" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="143" spans="1:5">
@@ -3574,16 +3586,16 @@
         <v>15</v>
       </c>
       <c r="B143" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C143" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D143">
         <v>2</v>
       </c>
       <c r="E143" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="144" spans="1:5">
@@ -3591,16 +3603,16 @@
         <v>15</v>
       </c>
       <c r="B144" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C144" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D144">
         <v>4</v>
       </c>
       <c r="E144" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="145" spans="1:5">
@@ -3608,16 +3620,16 @@
         <v>15</v>
       </c>
       <c r="B145" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C145" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D145">
         <v>2</v>
       </c>
       <c r="E145" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="146" spans="1:5">
@@ -3625,16 +3637,16 @@
         <v>15</v>
       </c>
       <c r="B146" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C146" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D146">
         <v>6</v>
       </c>
       <c r="E146" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="147" spans="1:5">
@@ -3642,16 +3654,16 @@
         <v>15</v>
       </c>
       <c r="B147" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C147" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D147">
         <v>6</v>
       </c>
       <c r="E147" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="148" spans="1:5">
@@ -3659,16 +3671,16 @@
         <v>15</v>
       </c>
       <c r="B148" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C148" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D148">
         <v>10</v>
       </c>
       <c r="E148" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="149" spans="1:5">
@@ -3676,16 +3688,16 @@
         <v>15</v>
       </c>
       <c r="B149" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C149" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D149">
         <v>6</v>
       </c>
       <c r="E149" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="150" spans="1:5">
@@ -3693,16 +3705,16 @@
         <v>15</v>
       </c>
       <c r="B150" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C150" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D150">
         <v>2</v>
       </c>
       <c r="E150" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="151" spans="1:5">
@@ -3710,16 +3722,16 @@
         <v>15</v>
       </c>
       <c r="B151" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C151" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D151">
         <v>6</v>
       </c>
       <c r="E151" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="152" spans="1:5">
@@ -3727,16 +3739,16 @@
         <v>15</v>
       </c>
       <c r="B152" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C152" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D152">
         <v>2</v>
       </c>
       <c r="E152" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="153" spans="1:5">
@@ -3744,16 +3756,16 @@
         <v>15</v>
       </c>
       <c r="B153" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C153" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D153">
         <v>6</v>
       </c>
       <c r="E153" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="154" spans="1:5">
@@ -3761,16 +3773,16 @@
         <v>15</v>
       </c>
       <c r="B154" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C154" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D154">
         <v>2</v>
       </c>
       <c r="E154" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="155" spans="1:5">
@@ -3778,16 +3790,16 @@
         <v>15</v>
       </c>
       <c r="B155" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C155" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D155">
         <v>9</v>
       </c>
       <c r="E155" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="156" spans="1:5">
@@ -3795,16 +3807,16 @@
         <v>15</v>
       </c>
       <c r="B156" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C156" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D156">
         <v>2</v>
       </c>
       <c r="E156" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="157" spans="1:5">
@@ -3812,16 +3824,16 @@
         <v>15</v>
       </c>
       <c r="B157" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C157" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D157">
         <v>7</v>
       </c>
       <c r="E157" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="158" spans="1:5">
@@ -3829,16 +3841,16 @@
         <v>15</v>
       </c>
       <c r="B158" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C158" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D158">
         <v>2</v>
       </c>
       <c r="E158" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="159" spans="1:5">
@@ -3846,16 +3858,16 @@
         <v>15</v>
       </c>
       <c r="B159" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C159" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D159">
         <v>3</v>
       </c>
       <c r="E159" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="160" spans="1:5">
@@ -3863,16 +3875,16 @@
         <v>15</v>
       </c>
       <c r="B160" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C160" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D160">
         <v>3</v>
       </c>
       <c r="E160" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="161" spans="1:5">
@@ -3880,16 +3892,16 @@
         <v>15</v>
       </c>
       <c r="B161" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C161" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D161">
         <v>6</v>
       </c>
       <c r="E161" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="162" spans="1:5">
@@ -3897,16 +3909,16 @@
         <v>15</v>
       </c>
       <c r="B162" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C162" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D162">
         <v>2</v>
       </c>
       <c r="E162" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="163" spans="1:5">
@@ -3914,16 +3926,16 @@
         <v>15</v>
       </c>
       <c r="B163" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C163" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D163">
         <v>6</v>
       </c>
       <c r="E163" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="164" spans="1:5">
@@ -3931,16 +3943,16 @@
         <v>15</v>
       </c>
       <c r="B164" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C164" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D164">
         <v>2</v>
       </c>
       <c r="E164" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="165" spans="1:5">
@@ -3948,16 +3960,16 @@
         <v>15</v>
       </c>
       <c r="B165" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C165" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D165">
         <v>6</v>
       </c>
       <c r="E165" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="166" spans="1:5">
@@ -3965,16 +3977,16 @@
         <v>15</v>
       </c>
       <c r="B166" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C166" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D166">
         <v>2</v>
       </c>
       <c r="E166" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="167" spans="1:5">
@@ -3982,16 +3994,16 @@
         <v>15</v>
       </c>
       <c r="B167" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C167" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D167">
         <v>4</v>
       </c>
       <c r="E167" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="168" spans="1:5">
@@ -3999,16 +4011,16 @@
         <v>15</v>
       </c>
       <c r="B168" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C168" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D168">
         <v>4</v>
       </c>
       <c r="E168" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="169" spans="1:5">
@@ -4016,16 +4028,16 @@
         <v>15</v>
       </c>
       <c r="B169" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C169" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D169">
         <v>8</v>
       </c>
       <c r="E169" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="170" spans="1:5">
@@ -4033,16 +4045,16 @@
         <v>15</v>
       </c>
       <c r="B170" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C170" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D170">
         <v>8</v>
       </c>
       <c r="E170" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="171" spans="1:5">
@@ -4050,16 +4062,16 @@
         <v>15</v>
       </c>
       <c r="B171" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C171" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D171">
         <v>4</v>
       </c>
       <c r="E171" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="172" spans="1:5">
@@ -4067,16 +4079,16 @@
         <v>15</v>
       </c>
       <c r="B172" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C172" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D172">
         <v>6</v>
       </c>
       <c r="E172" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="173" spans="1:5">
@@ -4084,16 +4096,16 @@
         <v>15</v>
       </c>
       <c r="B173" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C173" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D173">
         <v>6</v>
       </c>
       <c r="E173" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="174" spans="1:5">
@@ -4101,16 +4113,16 @@
         <v>15</v>
       </c>
       <c r="B174" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C174" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D174">
         <v>2</v>
       </c>
       <c r="E174" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="175" spans="1:5">
@@ -4118,16 +4130,16 @@
         <v>15</v>
       </c>
       <c r="B175" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C175" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D175">
         <v>6</v>
       </c>
       <c r="E175" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="176" spans="1:5">
@@ -4135,16 +4147,16 @@
         <v>15</v>
       </c>
       <c r="B176" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C176" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D176">
         <v>2</v>
       </c>
       <c r="E176" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="177" spans="1:5">
@@ -4152,16 +4164,16 @@
         <v>15</v>
       </c>
       <c r="B177" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C177" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D177">
         <v>6</v>
       </c>
       <c r="E177" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="178" spans="1:5">
@@ -4169,16 +4181,16 @@
         <v>15</v>
       </c>
       <c r="B178" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C178" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D178">
         <v>2</v>
       </c>
       <c r="E178" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="179" spans="1:5">
@@ -4186,16 +4198,16 @@
         <v>15</v>
       </c>
       <c r="B179" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C179" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D179">
         <v>4</v>
       </c>
       <c r="E179" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="180" spans="1:5">
@@ -4203,16 +4215,16 @@
         <v>15</v>
       </c>
       <c r="B180" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C180" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D180">
         <v>8</v>
       </c>
       <c r="E180" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="181" spans="1:5">
@@ -4220,16 +4232,16 @@
         <v>15</v>
       </c>
       <c r="B181" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C181" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D181">
         <v>8</v>
       </c>
       <c r="E181" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="182" spans="1:5">
@@ -4237,16 +4249,16 @@
         <v>15</v>
       </c>
       <c r="B182" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C182" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D182">
         <v>6</v>
       </c>
       <c r="E182" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="183" spans="1:5">
@@ -4254,16 +4266,16 @@
         <v>15</v>
       </c>
       <c r="B183" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C183" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D183">
         <v>2</v>
       </c>
       <c r="E183" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="184" spans="1:5">
@@ -4271,16 +4283,16 @@
         <v>15</v>
       </c>
       <c r="B184" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C184" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D184">
         <v>6</v>
       </c>
       <c r="E184" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="185" spans="1:5">
@@ -4288,16 +4300,16 @@
         <v>15</v>
       </c>
       <c r="B185" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C185" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D185">
         <v>2</v>
       </c>
       <c r="E185" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="186" spans="1:5">
@@ -4305,16 +4317,16 @@
         <v>15</v>
       </c>
       <c r="B186" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C186" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D186">
         <v>20</v>
       </c>
       <c r="E186" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="187" spans="1:5">
@@ -4322,16 +4334,16 @@
         <v>15</v>
       </c>
       <c r="B187" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C187" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D187">
         <v>6</v>
       </c>
       <c r="E187" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="188" spans="1:5">
@@ -4339,16 +4351,16 @@
         <v>15</v>
       </c>
       <c r="B188" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C188" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D188">
         <v>2</v>
       </c>
       <c r="E188" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="189" spans="1:5">
@@ -4356,16 +4368,16 @@
         <v>15</v>
       </c>
       <c r="B189" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C189" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D189">
         <v>4</v>
       </c>
       <c r="E189" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="190" spans="1:5">
@@ -4373,16 +4385,16 @@
         <v>15</v>
       </c>
       <c r="B190" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C190" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D190">
         <v>10</v>
       </c>
       <c r="E190" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="191" spans="1:5">
@@ -4390,16 +4402,16 @@
         <v>15</v>
       </c>
       <c r="B191" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C191" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D191">
         <v>8</v>
       </c>
       <c r="E191" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="192" spans="1:5">
@@ -4407,16 +4419,16 @@
         <v>15</v>
       </c>
       <c r="B192" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C192" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D192">
         <v>4</v>
       </c>
       <c r="E192" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="193" spans="1:5">
@@ -4424,16 +4436,16 @@
         <v>15</v>
       </c>
       <c r="B193" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C193" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D193">
         <v>4</v>
       </c>
       <c r="E193" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="194" spans="1:5">
@@ -4441,16 +4453,16 @@
         <v>15</v>
       </c>
       <c r="B194" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C194" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D194">
         <v>2</v>
       </c>
       <c r="E194" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="195" spans="1:5">
@@ -4458,16 +4470,16 @@
         <v>15</v>
       </c>
       <c r="B195" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C195" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D195">
         <v>1</v>
       </c>
       <c r="E195" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="196" spans="1:5">
@@ -4475,16 +4487,16 @@
         <v>15</v>
       </c>
       <c r="B196" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C196" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D196">
         <v>1</v>
       </c>
       <c r="E196" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="197" spans="1:5">
@@ -4492,16 +4504,16 @@
         <v>15</v>
       </c>
       <c r="B197" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C197" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D197">
         <v>18</v>
       </c>
       <c r="E197" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="198" spans="1:5">
@@ -4509,16 +4521,16 @@
         <v>15</v>
       </c>
       <c r="B198" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C198" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D198">
         <v>18</v>
       </c>
       <c r="E198" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="199" spans="1:5">
@@ -4526,16 +4538,16 @@
         <v>15</v>
       </c>
       <c r="B199" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C199" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D199">
         <v>48</v>
       </c>
       <c r="E199" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="200" spans="1:5">
@@ -4543,16 +4555,16 @@
         <v>15</v>
       </c>
       <c r="B200" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C200" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D200">
         <v>1</v>
       </c>
       <c r="E200" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="201" spans="1:5">
@@ -4560,16 +4572,16 @@
         <v>15</v>
       </c>
       <c r="B201" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C201" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D201">
         <v>1</v>
       </c>
       <c r="E201" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="202" spans="1:5">
@@ -4577,16 +4589,16 @@
         <v>15</v>
       </c>
       <c r="B202" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C202" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D202">
         <v>1</v>
       </c>
       <c r="E202" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="203" spans="1:5">
@@ -4594,16 +4606,16 @@
         <v>15</v>
       </c>
       <c r="B203" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C203" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D203">
         <v>1</v>
       </c>
       <c r="E203" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="204" spans="1:5">
@@ -4611,16 +4623,16 @@
         <v>15</v>
       </c>
       <c r="B204" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C204" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D204">
         <v>2</v>
       </c>
       <c r="E204" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="205" spans="1:5">
@@ -4628,16 +4640,16 @@
         <v>15</v>
       </c>
       <c r="B205" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C205" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D205">
         <v>1</v>
       </c>
       <c r="E205" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="206" spans="1:5">
@@ -4645,16 +4657,16 @@
         <v>15</v>
       </c>
       <c r="B206" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C206" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D206">
         <v>1</v>
       </c>
       <c r="E206" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="207" spans="1:5">
@@ -4662,16 +4674,16 @@
         <v>15</v>
       </c>
       <c r="B207" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C207" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D207">
         <v>12</v>
       </c>
       <c r="E207" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="208" spans="1:5">
@@ -4679,16 +4691,16 @@
         <v>15</v>
       </c>
       <c r="B208" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C208" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D208">
         <v>1</v>
       </c>
       <c r="E208" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="209" spans="1:5">
@@ -4696,16 +4708,16 @@
         <v>15</v>
       </c>
       <c r="B209" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C209" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D209">
         <v>3</v>
       </c>
       <c r="E209" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="210" spans="1:5">
@@ -4713,16 +4725,16 @@
         <v>15</v>
       </c>
       <c r="B210" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C210" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D210">
         <v>2</v>
       </c>
       <c r="E210" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="211" spans="1:5">
@@ -4730,16 +4742,16 @@
         <v>15</v>
       </c>
       <c r="B211" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C211" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D211">
         <v>1</v>
       </c>
       <c r="E211" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="212" spans="1:5">
@@ -4747,16 +4759,16 @@
         <v>15</v>
       </c>
       <c r="B212" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C212" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D212">
         <v>1</v>
       </c>
       <c r="E212" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="213" spans="1:5">
@@ -4764,16 +4776,16 @@
         <v>15</v>
       </c>
       <c r="B213" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C213" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D213">
         <v>1</v>
       </c>
       <c r="E213" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="214" spans="1:5">
@@ -4781,16 +4793,16 @@
         <v>15</v>
       </c>
       <c r="B214" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C214" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D214">
         <v>1</v>
       </c>
       <c r="E214" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="215" spans="1:5">
@@ -4798,16 +4810,16 @@
         <v>16</v>
       </c>
       <c r="B215" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C215" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D215">
         <v>16</v>
       </c>
       <c r="E215" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="216" spans="1:5">
@@ -4815,16 +4827,16 @@
         <v>16</v>
       </c>
       <c r="B216" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C216" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D216">
         <v>8</v>
       </c>
       <c r="E216" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="217" spans="1:5">
@@ -4832,16 +4844,16 @@
         <v>16</v>
       </c>
       <c r="B217" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C217" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D217">
         <v>16</v>
       </c>
       <c r="E217" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="218" spans="1:5">
@@ -4849,16 +4861,16 @@
         <v>16</v>
       </c>
       <c r="B218" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C218" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D218">
         <v>16</v>
       </c>
       <c r="E218" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="219" spans="1:5">
@@ -4866,16 +4878,16 @@
         <v>16</v>
       </c>
       <c r="B219" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C219" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D219">
         <v>14</v>
       </c>
       <c r="E219" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="220" spans="1:5">
@@ -4883,16 +4895,16 @@
         <v>16</v>
       </c>
       <c r="B220" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C220" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D220">
         <v>16</v>
       </c>
       <c r="E220" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="221" spans="1:5">
@@ -4900,16 +4912,16 @@
         <v>16</v>
       </c>
       <c r="B221" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C221" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D221">
         <v>8</v>
       </c>
       <c r="E221" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="222" spans="1:5">
@@ -4917,16 +4929,16 @@
         <v>16</v>
       </c>
       <c r="B222" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C222" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D222">
         <v>45</v>
       </c>
       <c r="E222" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="223" spans="1:5">
@@ -4934,16 +4946,16 @@
         <v>16</v>
       </c>
       <c r="B223" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C223" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D223">
         <v>16</v>
       </c>
       <c r="E223" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="224" spans="1:5">
@@ -4951,16 +4963,16 @@
         <v>16</v>
       </c>
       <c r="B224" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C224" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D224">
         <v>8</v>
       </c>
       <c r="E224" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="225" spans="1:5">
@@ -4968,16 +4980,16 @@
         <v>16</v>
       </c>
       <c r="B225" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C225" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D225">
         <v>24</v>
       </c>
       <c r="E225" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="226" spans="1:5">
@@ -4985,16 +4997,16 @@
         <v>16</v>
       </c>
       <c r="B226" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C226" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D226">
         <v>24</v>
       </c>
       <c r="E226" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="227" spans="1:5">
@@ -5002,16 +5014,16 @@
         <v>16</v>
       </c>
       <c r="B227" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C227" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D227">
         <v>15</v>
       </c>
       <c r="E227" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="228" spans="1:5">
@@ -5019,16 +5031,16 @@
         <v>16</v>
       </c>
       <c r="B228" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C228" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D228">
         <v>24</v>
       </c>
       <c r="E228" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="229" spans="1:5">
@@ -5036,16 +5048,16 @@
         <v>16</v>
       </c>
       <c r="B229" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C229" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D229">
         <v>24</v>
       </c>
       <c r="E229" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="230" spans="1:5">
@@ -5053,16 +5065,16 @@
         <v>16</v>
       </c>
       <c r="B230" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C230" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D230">
         <v>16</v>
       </c>
       <c r="E230" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="231" spans="1:5">
@@ -5070,16 +5082,16 @@
         <v>16</v>
       </c>
       <c r="B231" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C231" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D231">
         <v>8</v>
       </c>
       <c r="E231" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="232" spans="1:5">
@@ -5087,16 +5099,16 @@
         <v>16</v>
       </c>
       <c r="B232" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C232" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D232">
         <v>48</v>
       </c>
       <c r="E232" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="233" spans="1:5">
@@ -5104,16 +5116,16 @@
         <v>16</v>
       </c>
       <c r="B233" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C233" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D233">
         <v>24</v>
       </c>
       <c r="E233" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="234" spans="1:5">
@@ -5121,16 +5133,16 @@
         <v>16</v>
       </c>
       <c r="B234" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C234" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D234">
         <v>16</v>
       </c>
       <c r="E234" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="235" spans="1:5">
@@ -5138,16 +5150,16 @@
         <v>16</v>
       </c>
       <c r="B235" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C235" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D235">
         <v>8</v>
       </c>
       <c r="E235" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="236" spans="1:5">
@@ -5155,16 +5167,16 @@
         <v>16</v>
       </c>
       <c r="B236" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C236" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D236">
         <v>7</v>
       </c>
       <c r="E236" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="237" spans="1:5">
@@ -5172,16 +5184,16 @@
         <v>16</v>
       </c>
       <c r="B237" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C237" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D237">
         <v>7</v>
       </c>
       <c r="E237" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="238" spans="1:5">
@@ -5189,16 +5201,16 @@
         <v>16</v>
       </c>
       <c r="B238" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C238" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D238">
         <v>24</v>
       </c>
       <c r="E238" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="239" spans="1:5">
@@ -5206,16 +5218,16 @@
         <v>16</v>
       </c>
       <c r="B239" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C239" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D239">
         <v>24</v>
       </c>
       <c r="E239" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="240" spans="1:5">
@@ -5223,16 +5235,16 @@
         <v>16</v>
       </c>
       <c r="B240" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C240" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D240">
         <v>8</v>
       </c>
       <c r="E240" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="241" spans="1:5">
@@ -5240,16 +5252,16 @@
         <v>16</v>
       </c>
       <c r="B241" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C241" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D241">
         <v>16</v>
       </c>
       <c r="E241" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="242" spans="1:5">
@@ -5257,16 +5269,16 @@
         <v>16</v>
       </c>
       <c r="B242" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C242" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D242">
         <v>8</v>
       </c>
       <c r="E242" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="243" spans="1:5">
@@ -5274,16 +5286,16 @@
         <v>16</v>
       </c>
       <c r="B243" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C243" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D243">
         <v>52</v>
       </c>
       <c r="E243" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="244" spans="1:5">
@@ -5291,16 +5303,16 @@
         <v>16</v>
       </c>
       <c r="B244" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C244" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D244">
         <v>13</v>
       </c>
       <c r="E244" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="245" spans="1:5">
@@ -5308,16 +5320,16 @@
         <v>16</v>
       </c>
       <c r="B245" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C245" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D245">
         <v>13</v>
       </c>
       <c r="E245" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="246" spans="1:5">
@@ -5325,16 +5337,16 @@
         <v>16</v>
       </c>
       <c r="B246" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C246" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D246">
         <v>27</v>
       </c>
       <c r="E246" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="247" spans="1:5">
@@ -5342,16 +5354,16 @@
         <v>16</v>
       </c>
       <c r="B247" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C247" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D247">
         <v>16</v>
       </c>
       <c r="E247" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="248" spans="1:5">
@@ -5359,16 +5371,16 @@
         <v>16</v>
       </c>
       <c r="B248" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C248" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D248">
         <v>8</v>
       </c>
       <c r="E248" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="249" spans="1:5">
@@ -5376,16 +5388,16 @@
         <v>16</v>
       </c>
       <c r="B249" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C249" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D249">
         <v>16</v>
       </c>
       <c r="E249" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="250" spans="1:5">
@@ -5393,16 +5405,16 @@
         <v>16</v>
       </c>
       <c r="B250" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C250" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D250">
         <v>8</v>
       </c>
       <c r="E250" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="251" spans="1:5">
@@ -5410,16 +5422,16 @@
         <v>16</v>
       </c>
       <c r="B251" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C251" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D251">
         <v>16</v>
       </c>
       <c r="E251" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="252" spans="1:5">
@@ -5427,16 +5439,16 @@
         <v>16</v>
       </c>
       <c r="B252" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C252" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D252">
         <v>8</v>
       </c>
       <c r="E252" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="253" spans="1:5">
@@ -5444,16 +5456,16 @@
         <v>16</v>
       </c>
       <c r="B253" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C253" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D253">
         <v>53</v>
       </c>
       <c r="E253" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="254" spans="1:5">
@@ -5461,16 +5473,16 @@
         <v>16</v>
       </c>
       <c r="B254" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C254" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D254">
         <v>8</v>
       </c>
       <c r="E254" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="255" spans="1:5">
@@ -5478,16 +5490,16 @@
         <v>16</v>
       </c>
       <c r="B255" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C255" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D255">
         <v>16</v>
       </c>
       <c r="E255" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="256" spans="1:5">
@@ -5495,16 +5507,16 @@
         <v>16</v>
       </c>
       <c r="B256" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C256" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D256">
         <v>8</v>
       </c>
       <c r="E256" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="257" spans="1:5">
@@ -5512,16 +5524,16 @@
         <v>16</v>
       </c>
       <c r="B257" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C257" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D257">
         <v>16</v>
       </c>
       <c r="E257" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="258" spans="1:5">
@@ -5529,16 +5541,16 @@
         <v>16</v>
       </c>
       <c r="B258" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C258" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D258">
         <v>8</v>
       </c>
       <c r="E258" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="259" spans="1:5">
@@ -5546,16 +5558,16 @@
         <v>16</v>
       </c>
       <c r="B259" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C259" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D259">
         <v>16</v>
       </c>
       <c r="E259" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="260" spans="1:5">
@@ -5563,16 +5575,16 @@
         <v>16</v>
       </c>
       <c r="B260" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C260" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D260">
         <v>8</v>
       </c>
       <c r="E260" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="261" spans="1:5">
@@ -5580,16 +5592,16 @@
         <v>16</v>
       </c>
       <c r="B261" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C261" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D261">
         <v>16</v>
       </c>
       <c r="E261" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="262" spans="1:5">
@@ -5597,16 +5609,16 @@
         <v>16</v>
       </c>
       <c r="B262" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C262" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D262">
         <v>16</v>
       </c>
       <c r="E262" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="263" spans="1:5">
@@ -5614,16 +5626,16 @@
         <v>16</v>
       </c>
       <c r="B263" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C263" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D263">
         <v>24</v>
       </c>
       <c r="E263" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="264" spans="1:5">
@@ -5631,16 +5643,16 @@
         <v>16</v>
       </c>
       <c r="B264" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C264" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D264">
         <v>24</v>
       </c>
       <c r="E264" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="265" spans="1:5">
@@ -5648,16 +5660,16 @@
         <v>16</v>
       </c>
       <c r="B265" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C265" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D265">
         <v>16</v>
       </c>
       <c r="E265" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="266" spans="1:5">
@@ -5665,16 +5677,16 @@
         <v>16</v>
       </c>
       <c r="B266" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C266" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D266">
         <v>13</v>
       </c>
       <c r="E266" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="267" spans="1:5">
@@ -5682,16 +5694,16 @@
         <v>16</v>
       </c>
       <c r="B267" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C267" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D267">
         <v>61</v>
       </c>
       <c r="E267" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="268" spans="1:5">
@@ -5699,16 +5711,16 @@
         <v>16</v>
       </c>
       <c r="B268" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C268" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D268">
         <v>61</v>
       </c>
       <c r="E268" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="269" spans="1:5">
@@ -5716,16 +5728,16 @@
         <v>16</v>
       </c>
       <c r="B269" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C269" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D269">
         <v>2</v>
       </c>
       <c r="E269" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="270" spans="1:5">
@@ -5733,16 +5745,16 @@
         <v>16</v>
       </c>
       <c r="B270" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C270" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D270">
         <v>3</v>
       </c>
       <c r="E270" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="271" spans="1:5">
@@ -5750,16 +5762,16 @@
         <v>16</v>
       </c>
       <c r="B271" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C271" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D271">
         <v>1</v>
       </c>
       <c r="E271" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="272" spans="1:5">
@@ -5767,16 +5779,16 @@
         <v>16</v>
       </c>
       <c r="B272" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C272" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D272">
         <v>9</v>
       </c>
       <c r="E272" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="273" spans="1:5">
@@ -5784,16 +5796,16 @@
         <v>16</v>
       </c>
       <c r="B273" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C273" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D273">
         <v>3</v>
       </c>
       <c r="E273" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="274" spans="1:5">
@@ -5801,16 +5813,16 @@
         <v>16</v>
       </c>
       <c r="B274" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C274" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D274">
         <v>5</v>
       </c>
       <c r="E274" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="275" spans="1:5">
@@ -5818,16 +5830,16 @@
         <v>16</v>
       </c>
       <c r="B275" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C275" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D275">
         <v>3</v>
       </c>
       <c r="E275" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="276" spans="1:5">
@@ -5835,16 +5847,16 @@
         <v>16</v>
       </c>
       <c r="B276" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C276" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D276">
         <v>3</v>
       </c>
       <c r="E276" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="277" spans="1:5">
@@ -5852,16 +5864,16 @@
         <v>17</v>
       </c>
       <c r="B277" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C277" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="D277">
         <v>1</v>
       </c>
       <c r="E277" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="278" spans="1:5">
@@ -5869,16 +5881,16 @@
         <v>17</v>
       </c>
       <c r="B278" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C278" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="D278">
         <v>1</v>
       </c>
       <c r="E278" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="279" spans="1:5">
@@ -5886,16 +5898,16 @@
         <v>17</v>
       </c>
       <c r="B279" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C279" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="D279">
         <v>4</v>
       </c>
       <c r="E279" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="280" spans="1:5">
@@ -5903,16 +5915,16 @@
         <v>17</v>
       </c>
       <c r="B280" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C280" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="D280">
         <v>1</v>
       </c>
       <c r="E280" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="281" spans="1:5">
@@ -5920,16 +5932,16 @@
         <v>17</v>
       </c>
       <c r="B281" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C281" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="D281">
         <v>3</v>
       </c>
       <c r="E281" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="282" spans="1:5">
@@ -5937,16 +5949,50 @@
         <v>17</v>
       </c>
       <c r="B282" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C282" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="D282">
         <v>1</v>
       </c>
       <c r="E282" t="s">
-        <v>268</v>
+        <v>272</v>
+      </c>
+    </row>
+    <row r="283" spans="1:5">
+      <c r="A283" t="s">
+        <v>18</v>
+      </c>
+      <c r="B283" t="s">
+        <v>260</v>
+      </c>
+      <c r="C283" t="s">
+        <v>271</v>
+      </c>
+      <c r="D283">
+        <v>1</v>
+      </c>
+      <c r="E283" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="284" spans="1:5">
+      <c r="A284" t="s">
+        <v>19</v>
+      </c>
+      <c r="B284" t="s">
+        <v>261</v>
+      </c>
+      <c r="C284" t="s">
+        <v>266</v>
+      </c>
+      <c r="D284">
+        <v>200</v>
+      </c>
+      <c r="E284" t="s">
+        <v>272</v>
       </c>
     </row>
   </sheetData>

--- a/data/BD_Requerimientos_POs.xlsx
+++ b/data/BD_Requerimientos_POs.xlsx
@@ -1480,7 +1480,7 @@
     <t>11-E-9851-01</t>
   </si>
   <si>
-    <t>11-E-9851-02 - COMPARTIMIENTO AUXILIAR</t>
+    <t>11-E-9851-02</t>
   </si>
   <si>
     <t>11-E-9870-02</t>
